--- a/JoinQuant/profit.xlsx
+++ b/JoinQuant/profit.xlsx
@@ -898,6 +898,982 @@
 </styleSheet>
 </file>
 
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:date1904 val="0"/>
+  <c:lang val="zh-CN"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr defTabSz="914400">
+              <a:defRPr lang="zh-CN" sz="1400" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="75000"/>
+                    <a:lumOff val="25000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:t>除</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" altLang="zh-CN"/>
+              <a:t>15</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr altLang="en-US"/>
+              <a:t>年收益</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-US" altLang="zh-CN"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.0971767810026385"/>
+          <c:y val="0.169698365185356"/>
+          <c:w val="0.874722955145119"/>
+          <c:h val="0.669122726226111"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:delete val="1"/>
+          </c:dLbls>
+          <c:cat>
+            <c:numRef>
+              <c:f>(Sheet3!$A$2:$A$6,Sheet3!$A$8:$A$17)</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="15"/>
+                <c:pt idx="0">
+                  <c:v>2010</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2011</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2012</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2013</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2014</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2016</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2017</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2018</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2019</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2020</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2021</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>2022</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>2023</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>2024</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2025</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>(Sheet3!$N$2:$N$6,Sheet3!$N$8:$N$17)</c:f>
+              <c:numCache>
+                <c:formatCode>0.000_ </c:formatCode>
+                <c:ptCount val="15"/>
+                <c:pt idx="0">
+                  <c:v>0.653614174322446</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-0.0855664203647523</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.0384573958480514</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.765405002524292</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1.19935720490706</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1.09694188883488</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.0775695328691113</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.472825224873327</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.745848408003567</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.501877778017195</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.660960857965097</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>1.99686467587207</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.495057586521658</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>2.14431144891796</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.721324876500654</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="246"/>
+        <c:overlap val="-28"/>
+        <c:axId val="141393639"/>
+        <c:axId val="114272973"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="141393639"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr lang="zh-CN" sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="114272973"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="114272973"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="lt1">
+                  <a:lumMod val="90200"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0.000_ " sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr lang="zh-CN" sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="141393639"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr lang="zh-CN" sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr lang="zh-CN"/>
+      </a:pPr>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="10001">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+      <a:effectLst/>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="90200"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="1" kern="1200" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>272415</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>69215</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>107950</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame>
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="11" name="图表 10"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="9779635" y="384175"/>
+        <a:ext cx="4826000" cy="2746375"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="WPS">
   <a:themeElements>
@@ -6001,5 +6977,6 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/JoinQuant/profit.xlsx
+++ b/JoinQuant/profit.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="20">
   <si>
     <t>Jan</t>
   </si>
@@ -92,6 +92,9 @@
     <t>当年收益</t>
   </si>
   <si>
+    <t>当年收益%</t>
+  </si>
+  <si>
     <t>月度累计收益</t>
   </si>
   <si>
@@ -99,6 +102,15 @@
   </si>
   <si>
     <t>盈利&gt;10%月份数</t>
+  </si>
+  <si>
+    <t>最近几年</t>
+  </si>
+  <si>
+    <t>总收益率</t>
+  </si>
+  <si>
+    <t>年化收益率</t>
   </si>
 </sst>
 </file>
@@ -113,7 +125,7 @@
     <numFmt numFmtId="176" formatCode="0.0000_ "/>
     <numFmt numFmtId="177" formatCode="0.000_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -126,6 +138,13 @@
       <color rgb="FF222222"/>
       <name val="Verdana"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="10.5"/>
@@ -278,7 +297,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="36">
+  <fills count="38">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -300,6 +319,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -636,16 +667,13 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -654,58 +682,55 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="9" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="11" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -714,10 +739,10 @@
     <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -726,22 +751,22 @@
     <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -750,10 +775,10 @@
     <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -762,11 +787,17 @@
     <xf numFmtId="0" fontId="21" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -782,7 +813,19 @@
     <xf numFmtId="176" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="2" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1">
@@ -794,10 +837,10 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="17" fontId="2" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="17" fontId="3" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1256,6 +1299,355 @@
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
     <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext uri="{0b15fc19-7d7d-44ad-8c2d-2c3a37ce22c3}">
+        <chartProps xmlns="https://web.wps.cn/et/2018/main" chartId="{2ebeccb4-77f5-4e44-a78a-07d1884e056f}"/>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr lang="zh-CN"/>
+      </a:pPr>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:date1904 val="0"/>
+  <c:lang val="zh-CN"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr defTabSz="914400">
+              <a:defRPr lang="zh-CN" sz="1400" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="75000"/>
+                    <a:lumOff val="25000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" altLang="zh-CN"/>
+              <a:t>N</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr altLang="en-US"/>
+              <a:t>年前买入后</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" altLang="zh-CN"/>
+              <a:t> </a:t>
+            </a:r>
+            <a:r>
+              <a:rPr altLang="en-US"/>
+              <a:t>年化收益率</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-US" altLang="zh-CN"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout>
+        <c:manualLayout>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.30778364116095"/>
+          <c:y val="0.0163443830570902"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:dLbls>
+            <c:delete val="1"/>
+          </c:dLbls>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet3!$B$28:$Q$28</c:f>
+              <c:numCache>
+                <c:formatCode>0.00%</c:formatCode>
+                <c:ptCount val="16"/>
+                <c:pt idx="0">
+                  <c:v>0.721324876500654</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.32645256054971</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.00762274723281</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.21910761645483</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1.09418271565768</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.98130456845761</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.945817014845787</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.879243898263695</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.766630037947978</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.797172187425214</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>1.03317706479</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>1.04653220237664</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>1.02340166712687</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.929255363746949</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.835582377705406</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0.823644364105827</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:marker val="0"/>
+        <c:smooth val="0"/>
+        <c:axId val="604726011"/>
+        <c:axId val="769988795"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="604726011"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr lang="zh-CN" sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="769988795"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="769988795"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="lt1">
+                  <a:lumMod val="90200"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0.00%" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr lang="zh-CN" sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="604726011"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr lang="zh-CN" sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -1290,6 +1682,46 @@
 </file>
 
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
   <a:schemeClr val="accent2"/>
@@ -1839,17 +2271,522 @@
 </cs:chartStyle>
 </file>
 
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="10028">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+      <a:effectLst/>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="90200"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="1" kern="1200" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>15</xdr:col>
+      <xdr:col>16</xdr:col>
       <xdr:colOff>272415</xdr:colOff>
       <xdr:row>2</xdr:row>
       <xdr:rowOff>28575</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>23</xdr:col>
+      <xdr:col>24</xdr:col>
       <xdr:colOff>69215</xdr:colOff>
       <xdr:row>17</xdr:row>
       <xdr:rowOff>107950</xdr:rowOff>
@@ -1860,12 +2797,42 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="9779635" y="384175"/>
+        <a:off x="10772140" y="384175"/>
+        <a:ext cx="4864100" cy="2746375"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>41910</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>31115</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>92710</xdr:colOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>110490</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame>
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="6" name="图表 5"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="917575" y="5019040"/>
         <a:ext cx="4826000" cy="2746375"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2124,17 +3091,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A2:V193"/>
+  <dimension ref="A1:V193"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="2" max="3" width="10"/>
   </cols>
   <sheetData>
+    <row r="1" ht="14.75"/>
     <row r="2" ht="14.75" spans="1:22">
       <c r="A2" s="1">
         <v>40179</v>
       </c>
-      <c r="B2" s="8">
+      <c r="B2" s="12">
         <v>0</v>
       </c>
       <c r="C2">
@@ -2214,7 +3182,7 @@
       <c r="A3" s="1">
         <v>40210</v>
       </c>
-      <c r="B3" s="8">
+      <c r="B3" s="12">
         <v>0.0651</v>
       </c>
       <c r="C3">
@@ -2294,7 +3262,7 @@
       <c r="A4" s="1">
         <v>40238</v>
       </c>
-      <c r="B4" s="8">
+      <c r="B4" s="12">
         <v>0.0813</v>
       </c>
       <c r="C4">
@@ -2374,7 +3342,7 @@
       <c r="A5" s="1">
         <v>40269</v>
       </c>
-      <c r="B5" s="8">
+      <c r="B5" s="12">
         <v>0.0008</v>
       </c>
       <c r="C5">
@@ -2454,7 +3422,7 @@
       <c r="A6" s="1">
         <v>40299</v>
       </c>
-      <c r="B6" s="8">
+      <c r="B6" s="12">
         <v>-0.0608</v>
       </c>
       <c r="C6">
@@ -2534,7 +3502,7 @@
       <c r="A7" s="1">
         <v>40330</v>
       </c>
-      <c r="B7" s="8">
+      <c r="B7" s="12">
         <v>-0.073</v>
       </c>
       <c r="C7">
@@ -2614,7 +3582,7 @@
       <c r="A8" s="1">
         <v>40360</v>
       </c>
-      <c r="B8" s="8">
+      <c r="B8" s="12">
         <v>0.1977</v>
       </c>
       <c r="C8">
@@ -2694,7 +3662,7 @@
       <c r="A9" s="1">
         <v>40391</v>
       </c>
-      <c r="B9" s="8">
+      <c r="B9" s="12">
         <v>0.1303</v>
       </c>
       <c r="C9">
@@ -2774,7 +3742,7 @@
       <c r="A10" s="1">
         <v>40422</v>
       </c>
-      <c r="B10" s="8">
+      <c r="B10" s="12">
         <v>0.11</v>
       </c>
       <c r="C10">
@@ -2854,7 +3822,7 @@
       <c r="A11" s="1">
         <v>40452</v>
       </c>
-      <c r="B11" s="8">
+      <c r="B11" s="12">
         <v>0.1099</v>
       </c>
       <c r="C11">
@@ -2934,7 +3902,7 @@
       <c r="A12" s="1">
         <v>40483</v>
       </c>
-      <c r="B12" s="8">
+      <c r="B12" s="12">
         <v>0.0089</v>
       </c>
       <c r="C12">
@@ -3014,7 +3982,7 @@
       <c r="A13" s="1">
         <v>40513</v>
       </c>
-      <c r="B13" s="8">
+      <c r="B13" s="12">
         <v>-0.0207</v>
       </c>
       <c r="C13">
@@ -3094,1801 +4062,1801 @@
       <c r="A14" s="1">
         <v>40544</v>
       </c>
-      <c r="B14" s="8">
+      <c r="B14" s="12">
         <v>-0.0016</v>
       </c>
-      <c r="C14" s="8"/>
-      <c r="D14" s="8"/>
+      <c r="C14" s="12"/>
+      <c r="D14" s="12"/>
     </row>
     <row r="15" ht="14.75" spans="1:4">
       <c r="A15" s="1">
         <v>40575</v>
       </c>
-      <c r="B15" s="8">
+      <c r="B15" s="12">
         <v>0.1456</v>
       </c>
-      <c r="C15" s="8"/>
-      <c r="D15" s="8"/>
+      <c r="C15" s="12"/>
+      <c r="D15" s="12"/>
     </row>
     <row r="16" ht="14.75" spans="1:4">
       <c r="A16" s="1">
         <v>40603</v>
       </c>
-      <c r="B16" s="8">
+      <c r="B16" s="12">
         <v>0.0526</v>
       </c>
-      <c r="C16" s="8"/>
-      <c r="D16" s="8"/>
+      <c r="C16" s="12"/>
+      <c r="D16" s="12"/>
     </row>
     <row r="17" ht="14.75" spans="1:4">
       <c r="A17" s="1">
         <v>40634</v>
       </c>
-      <c r="B17" s="8">
+      <c r="B17" s="12">
         <v>-0.0008</v>
       </c>
-      <c r="C17" s="8"/>
-      <c r="D17" s="8"/>
+      <c r="C17" s="12"/>
+      <c r="D17" s="12"/>
     </row>
     <row r="18" ht="14.75" spans="1:4">
       <c r="A18" s="1">
         <v>40664</v>
       </c>
-      <c r="B18" s="8">
+      <c r="B18" s="12">
         <v>-0.0644</v>
       </c>
-      <c r="C18" s="8"/>
-      <c r="D18" s="8"/>
+      <c r="C18" s="12"/>
+      <c r="D18" s="12"/>
     </row>
     <row r="19" ht="14.75" spans="1:4">
       <c r="A19" s="1">
         <v>40695</v>
       </c>
-      <c r="B19" s="8">
+      <c r="B19" s="12">
         <v>0.0828</v>
       </c>
-      <c r="C19" s="8"/>
-      <c r="D19" s="8"/>
+      <c r="C19" s="12"/>
+      <c r="D19" s="12"/>
     </row>
     <row r="20" ht="14.75" spans="1:4">
       <c r="A20" s="1">
         <v>40725</v>
       </c>
-      <c r="B20" s="8">
+      <c r="B20" s="12">
         <v>-0.0211</v>
       </c>
-      <c r="C20" s="8"/>
-      <c r="D20" s="8"/>
+      <c r="C20" s="12"/>
+      <c r="D20" s="12"/>
     </row>
     <row r="21" ht="14.75" spans="1:4">
       <c r="A21" s="1">
         <v>40756</v>
       </c>
-      <c r="B21" s="8">
+      <c r="B21" s="12">
         <v>-0.0006</v>
       </c>
-      <c r="C21" s="8"/>
-      <c r="D21" s="8"/>
+      <c r="C21" s="12"/>
+      <c r="D21" s="12"/>
     </row>
     <row r="22" ht="14.75" spans="1:4">
       <c r="A22" s="1">
         <v>40787</v>
       </c>
-      <c r="B22" s="8">
+      <c r="B22" s="12">
         <v>-0.0886</v>
       </c>
-      <c r="C22" s="8"/>
-      <c r="D22" s="8"/>
+      <c r="C22" s="12"/>
+      <c r="D22" s="12"/>
     </row>
     <row r="23" ht="14.75" spans="1:4">
       <c r="A23" s="1">
         <v>40817</v>
       </c>
-      <c r="B23" s="8">
+      <c r="B23" s="12">
         <v>0.0186</v>
       </c>
-      <c r="C23" s="8"/>
-      <c r="D23" s="8"/>
+      <c r="C23" s="12"/>
+      <c r="D23" s="12"/>
     </row>
     <row r="24" ht="14.75" spans="1:4">
       <c r="A24" s="1">
         <v>40848</v>
       </c>
-      <c r="B24" s="8">
+      <c r="B24" s="12">
         <v>-0.0239</v>
       </c>
-      <c r="C24" s="8"/>
-      <c r="D24" s="8"/>
+      <c r="C24" s="12"/>
+      <c r="D24" s="12"/>
     </row>
     <row r="25" ht="14.75" spans="1:4">
       <c r="A25" s="1">
         <v>40878</v>
       </c>
-      <c r="B25" s="8">
+      <c r="B25" s="12">
         <v>-0.1536</v>
       </c>
-      <c r="C25" s="8"/>
-      <c r="D25" s="8"/>
+      <c r="C25" s="12"/>
+      <c r="D25" s="12"/>
     </row>
     <row r="26" ht="14.75" spans="1:4">
       <c r="A26" s="1">
         <v>40909</v>
       </c>
-      <c r="B26" s="8">
+      <c r="B26" s="12">
         <v>0.0301</v>
       </c>
-      <c r="C26" s="8"/>
-      <c r="D26" s="8"/>
+      <c r="C26" s="12"/>
+      <c r="D26" s="12"/>
     </row>
     <row r="27" ht="14.75" spans="1:4">
       <c r="A27" s="1">
         <v>40940</v>
       </c>
-      <c r="B27" s="8">
+      <c r="B27" s="12">
         <v>0.0984</v>
       </c>
-      <c r="C27" s="8"/>
-      <c r="D27" s="8"/>
+      <c r="C27" s="12"/>
+      <c r="D27" s="12"/>
     </row>
     <row r="28" ht="14.75" spans="1:4">
       <c r="A28" s="1">
         <v>40969</v>
       </c>
-      <c r="B28" s="8">
+      <c r="B28" s="12">
         <v>-0.065</v>
       </c>
-      <c r="C28" s="8"/>
-      <c r="D28" s="8"/>
+      <c r="C28" s="12"/>
+      <c r="D28" s="12"/>
     </row>
     <row r="29" ht="14.75" spans="1:4">
       <c r="A29" s="1">
         <v>41000</v>
       </c>
-      <c r="B29" s="8">
+      <c r="B29" s="12">
         <v>0.0104</v>
       </c>
-      <c r="C29" s="8"/>
-      <c r="D29" s="8"/>
+      <c r="C29" s="12"/>
+      <c r="D29" s="12"/>
     </row>
     <row r="30" ht="14.75" spans="1:4">
       <c r="A30" s="1">
         <v>41030</v>
       </c>
-      <c r="B30" s="8">
+      <c r="B30" s="12">
         <v>0.0008</v>
       </c>
-      <c r="C30" s="8"/>
-      <c r="D30" s="8"/>
+      <c r="C30" s="12"/>
+      <c r="D30" s="12"/>
     </row>
     <row r="31" ht="14.75" spans="1:4">
       <c r="A31" s="1">
         <v>41061</v>
       </c>
-      <c r="B31" s="8">
+      <c r="B31" s="12">
         <v>-0.0436</v>
       </c>
-      <c r="C31" s="8"/>
-      <c r="D31" s="8"/>
+      <c r="C31" s="12"/>
+      <c r="D31" s="12"/>
     </row>
     <row r="32" ht="14.75" spans="1:4">
       <c r="A32" s="1">
         <v>41091</v>
       </c>
-      <c r="B32" s="8">
+      <c r="B32" s="12">
         <v>-0.1551</v>
       </c>
-      <c r="C32" s="8"/>
-      <c r="D32" s="8"/>
+      <c r="C32" s="12"/>
+      <c r="D32" s="12"/>
     </row>
     <row r="33" ht="14.75" spans="1:4">
       <c r="A33" s="1">
         <v>41122</v>
       </c>
-      <c r="B33" s="8">
+      <c r="B33" s="12">
         <v>0.0543</v>
       </c>
-      <c r="C33" s="8"/>
-      <c r="D33" s="8"/>
+      <c r="C33" s="12"/>
+      <c r="D33" s="12"/>
     </row>
     <row r="34" ht="14.75" spans="1:4">
       <c r="A34" s="1">
         <v>41153</v>
       </c>
-      <c r="B34" s="8">
+      <c r="B34" s="12">
         <v>0.019</v>
       </c>
-      <c r="C34" s="8"/>
-      <c r="D34" s="8"/>
+      <c r="C34" s="12"/>
+      <c r="D34" s="12"/>
     </row>
     <row r="35" ht="14.75" spans="1:4">
       <c r="A35" s="1">
         <v>41183</v>
       </c>
-      <c r="B35" s="8">
+      <c r="B35" s="12">
         <v>0.0012</v>
       </c>
-      <c r="C35" s="8"/>
-      <c r="D35" s="8"/>
+      <c r="C35" s="12"/>
+      <c r="D35" s="12"/>
     </row>
     <row r="36" ht="14.75" spans="1:4">
       <c r="A36" s="1">
         <v>41214</v>
       </c>
-      <c r="B36" s="8">
+      <c r="B36" s="12">
         <v>-0.0975</v>
       </c>
-      <c r="C36" s="8"/>
-      <c r="D36" s="8"/>
+      <c r="C36" s="12"/>
+      <c r="D36" s="12"/>
     </row>
     <row r="37" ht="14.75" spans="1:4">
       <c r="A37" s="1">
         <v>41244</v>
       </c>
-      <c r="B37" s="8">
+      <c r="B37" s="12">
         <v>0.2375</v>
       </c>
-      <c r="C37" s="8"/>
-      <c r="D37" s="8"/>
+      <c r="C37" s="12"/>
+      <c r="D37" s="12"/>
     </row>
     <row r="38" ht="14.75" spans="1:4">
       <c r="A38" s="1">
         <v>41275</v>
       </c>
-      <c r="B38" s="8">
+      <c r="B38" s="12">
         <v>0.0057</v>
       </c>
-      <c r="C38" s="8"/>
-      <c r="D38" s="8"/>
+      <c r="C38" s="12"/>
+      <c r="D38" s="12"/>
     </row>
     <row r="39" ht="14.75" spans="1:4">
       <c r="A39" s="1">
         <v>41306</v>
       </c>
-      <c r="B39" s="8">
+      <c r="B39" s="12">
         <v>0.0547</v>
       </c>
-      <c r="C39" s="8"/>
-      <c r="D39" s="8"/>
+      <c r="C39" s="12"/>
+      <c r="D39" s="12"/>
     </row>
     <row r="40" ht="14.75" spans="1:4">
       <c r="A40" s="1">
         <v>41334</v>
       </c>
-      <c r="B40" s="8">
+      <c r="B40" s="12">
         <v>-0.0189</v>
       </c>
-      <c r="C40" s="8"/>
-      <c r="D40" s="8"/>
+      <c r="C40" s="12"/>
+      <c r="D40" s="12"/>
     </row>
     <row r="41" ht="14.75" spans="1:4">
       <c r="A41" s="1">
         <v>41365</v>
       </c>
-      <c r="B41" s="8">
+      <c r="B41" s="12">
         <v>-0.0003</v>
       </c>
-      <c r="C41" s="8"/>
-      <c r="D41" s="8"/>
+      <c r="C41" s="12"/>
+      <c r="D41" s="12"/>
     </row>
     <row r="42" ht="14.75" spans="1:4">
       <c r="A42" s="1">
         <v>41395</v>
       </c>
-      <c r="B42" s="8">
+      <c r="B42" s="12">
         <v>0.1792</v>
       </c>
-      <c r="C42" s="8"/>
-      <c r="D42" s="8"/>
+      <c r="C42" s="12"/>
+      <c r="D42" s="12"/>
     </row>
     <row r="43" ht="14.75" spans="1:4">
       <c r="A43" s="1">
         <v>41426</v>
       </c>
-      <c r="B43" s="8">
+      <c r="B43" s="12">
         <v>-0.1098</v>
       </c>
-      <c r="C43" s="8"/>
-      <c r="D43" s="8"/>
+      <c r="C43" s="12"/>
+      <c r="D43" s="12"/>
     </row>
     <row r="44" ht="14.75" spans="1:4">
       <c r="A44" s="1">
         <v>41456</v>
       </c>
-      <c r="B44" s="8">
+      <c r="B44" s="12">
         <v>0.1573</v>
       </c>
-      <c r="C44" s="8"/>
-      <c r="D44" s="8"/>
+      <c r="C44" s="12"/>
+      <c r="D44" s="12"/>
     </row>
     <row r="45" ht="14.75" spans="1:4">
       <c r="A45" s="1">
         <v>41487</v>
       </c>
-      <c r="B45" s="8">
+      <c r="B45" s="12">
         <v>0.1024</v>
       </c>
-      <c r="C45" s="8"/>
-      <c r="D45" s="8"/>
+      <c r="C45" s="12"/>
+      <c r="D45" s="12"/>
     </row>
     <row r="46" ht="14.75" spans="1:4">
       <c r="A46" s="1">
         <v>41518</v>
       </c>
-      <c r="B46" s="8">
+      <c r="B46" s="12">
         <v>0.0868</v>
       </c>
-      <c r="C46" s="8"/>
-      <c r="D46" s="8"/>
+      <c r="C46" s="12"/>
+      <c r="D46" s="12"/>
     </row>
     <row r="47" ht="14.75" spans="1:4">
       <c r="A47" s="1">
         <v>41548</v>
       </c>
-      <c r="B47" s="8">
+      <c r="B47" s="12">
         <v>-0.0176</v>
       </c>
-      <c r="C47" s="8"/>
-      <c r="D47" s="8"/>
+      <c r="C47" s="12"/>
+      <c r="D47" s="12"/>
     </row>
     <row r="48" ht="14.75" spans="1:4">
       <c r="A48" s="1">
         <v>41579</v>
       </c>
-      <c r="B48" s="8">
+      <c r="B48" s="12">
         <v>0.1627</v>
       </c>
-      <c r="C48" s="8"/>
-      <c r="D48" s="8"/>
+      <c r="C48" s="12"/>
+      <c r="D48" s="12"/>
     </row>
     <row r="49" ht="14.75" spans="1:4">
       <c r="A49" s="1">
         <v>41609</v>
       </c>
-      <c r="B49" s="8">
+      <c r="B49" s="12">
         <v>0.0207</v>
       </c>
-      <c r="C49" s="8"/>
-      <c r="D49" s="8"/>
+      <c r="C49" s="12"/>
+      <c r="D49" s="12"/>
     </row>
     <row r="50" ht="14.75" spans="1:4">
       <c r="A50" s="1">
         <v>41640</v>
       </c>
-      <c r="B50" s="8">
+      <c r="B50" s="12">
         <v>-0.0057</v>
       </c>
-      <c r="C50" s="8"/>
-      <c r="D50" s="8"/>
+      <c r="C50" s="12"/>
+      <c r="D50" s="12"/>
     </row>
     <row r="51" ht="14.75" spans="1:4">
       <c r="A51" s="1">
         <v>41671</v>
       </c>
-      <c r="B51" s="8">
+      <c r="B51" s="12">
         <v>0.0822</v>
       </c>
-      <c r="C51" s="8"/>
-      <c r="D51" s="8"/>
+      <c r="C51" s="12"/>
+      <c r="D51" s="12"/>
     </row>
     <row r="52" ht="14.75" spans="1:4">
       <c r="A52" s="1">
         <v>41699</v>
       </c>
-      <c r="B52" s="8">
+      <c r="B52" s="12">
         <v>0.0133</v>
       </c>
-      <c r="C52" s="8"/>
-      <c r="D52" s="8"/>
+      <c r="C52" s="12"/>
+      <c r="D52" s="12"/>
     </row>
     <row r="53" ht="14.75" spans="1:4">
       <c r="A53" s="1">
         <v>41730</v>
       </c>
-      <c r="B53" s="8">
+      <c r="B53" s="12">
         <v>0.0346</v>
       </c>
-      <c r="C53" s="8"/>
-      <c r="D53" s="8"/>
+      <c r="C53" s="12"/>
+      <c r="D53" s="12"/>
     </row>
     <row r="54" ht="14.75" spans="1:4">
       <c r="A54" s="1">
         <v>41760</v>
       </c>
-      <c r="B54" s="8">
+      <c r="B54" s="12">
         <v>0.0267</v>
       </c>
-      <c r="C54" s="8"/>
-      <c r="D54" s="8"/>
+      <c r="C54" s="12"/>
+      <c r="D54" s="12"/>
     </row>
     <row r="55" ht="14.75" spans="1:4">
       <c r="A55" s="1">
         <v>41791</v>
       </c>
-      <c r="B55" s="8">
+      <c r="B55" s="12">
         <v>0.2214</v>
       </c>
-      <c r="C55" s="8"/>
-      <c r="D55" s="8"/>
+      <c r="C55" s="12"/>
+      <c r="D55" s="12"/>
     </row>
     <row r="56" ht="14.75" spans="1:4">
       <c r="A56" s="1">
         <v>41821</v>
       </c>
-      <c r="B56" s="8">
+      <c r="B56" s="12">
         <v>0.1535</v>
       </c>
-      <c r="C56" s="8"/>
-      <c r="D56" s="8"/>
+      <c r="C56" s="12"/>
+      <c r="D56" s="12"/>
     </row>
     <row r="57" ht="14.75" spans="1:4">
       <c r="A57" s="1">
         <v>41852</v>
       </c>
-      <c r="B57" s="8">
+      <c r="B57" s="12">
         <v>0.1294</v>
       </c>
-      <c r="C57" s="8"/>
-      <c r="D57" s="8"/>
+      <c r="C57" s="12"/>
+      <c r="D57" s="12"/>
     </row>
     <row r="58" ht="14.75" spans="1:4">
       <c r="A58" s="1">
         <v>41883</v>
       </c>
-      <c r="B58" s="8">
+      <c r="B58" s="12">
         <v>0.2618</v>
       </c>
-      <c r="C58" s="8"/>
-      <c r="D58" s="8"/>
+      <c r="C58" s="12"/>
+      <c r="D58" s="12"/>
     </row>
     <row r="59" ht="14.75" spans="1:4">
       <c r="A59" s="1">
         <v>41913</v>
       </c>
-      <c r="B59" s="8">
+      <c r="B59" s="12">
         <v>0.044</v>
       </c>
-      <c r="C59" s="8"/>
-      <c r="D59" s="8"/>
+      <c r="C59" s="12"/>
+      <c r="D59" s="12"/>
     </row>
     <row r="60" ht="14.75" spans="1:4">
       <c r="A60" s="1">
         <v>41944</v>
       </c>
-      <c r="B60" s="8">
+      <c r="B60" s="12">
         <v>0.0477</v>
       </c>
-      <c r="C60" s="8"/>
-      <c r="D60" s="8"/>
+      <c r="C60" s="12"/>
+      <c r="D60" s="12"/>
     </row>
     <row r="61" ht="14.75" spans="1:4">
       <c r="A61" s="1">
         <v>41974</v>
       </c>
-      <c r="B61" s="8">
+      <c r="B61" s="12">
         <v>-0.1353</v>
       </c>
-      <c r="C61" s="8"/>
-      <c r="D61" s="8"/>
+      <c r="C61" s="12"/>
+      <c r="D61" s="12"/>
     </row>
     <row r="62" ht="14.75" spans="1:4">
       <c r="A62" s="1">
         <v>42005</v>
       </c>
-      <c r="B62" s="8">
+      <c r="B62" s="12">
         <v>0.0227</v>
       </c>
-      <c r="C62" s="8"/>
-      <c r="D62" s="8"/>
+      <c r="C62" s="12"/>
+      <c r="D62" s="12"/>
     </row>
     <row r="63" ht="14.75" spans="1:4">
       <c r="A63" s="1">
         <v>42036</v>
       </c>
-      <c r="B63" s="8">
+      <c r="B63" s="12">
         <v>0.0675</v>
       </c>
-      <c r="C63" s="8"/>
-      <c r="D63" s="8"/>
+      <c r="C63" s="12"/>
+      <c r="D63" s="12"/>
     </row>
     <row r="64" ht="14.75" spans="1:4">
-      <c r="A64" s="9">
+      <c r="A64" s="13">
         <v>42064</v>
       </c>
-      <c r="B64" s="10">
+      <c r="B64" s="14">
         <v>0.2462</v>
       </c>
-      <c r="C64" s="10"/>
-      <c r="D64" s="10"/>
+      <c r="C64" s="14"/>
+      <c r="D64" s="14"/>
     </row>
     <row r="65" ht="14.75" spans="1:4">
       <c r="A65" s="1">
         <v>42095</v>
       </c>
-      <c r="B65" s="8">
+      <c r="B65" s="12">
         <v>0.079</v>
       </c>
-      <c r="C65" s="8"/>
-      <c r="D65" s="8"/>
+      <c r="C65" s="12"/>
+      <c r="D65" s="12"/>
     </row>
     <row r="66" ht="14.75" spans="1:4">
       <c r="A66" s="1">
         <v>42125</v>
       </c>
-      <c r="B66" s="8">
+      <c r="B66" s="12">
         <v>0.415</v>
       </c>
-      <c r="C66" s="8"/>
-      <c r="D66" s="8"/>
+      <c r="C66" s="12"/>
+      <c r="D66" s="12"/>
     </row>
     <row r="67" ht="14.75" spans="1:4">
       <c r="A67" s="1">
         <v>42156</v>
       </c>
-      <c r="B67" s="8">
+      <c r="B67" s="12">
         <v>0.0212</v>
       </c>
-      <c r="C67" s="8"/>
-      <c r="D67" s="8"/>
+      <c r="C67" s="12"/>
+      <c r="D67" s="12"/>
     </row>
     <row r="68" ht="14.75" spans="1:4">
       <c r="A68" s="1">
         <v>42186</v>
       </c>
-      <c r="B68" s="8">
+      <c r="B68" s="12">
         <v>0.3626</v>
       </c>
-      <c r="C68" s="8"/>
-      <c r="D68" s="8"/>
+      <c r="C68" s="12"/>
+      <c r="D68" s="12"/>
     </row>
     <row r="69" ht="14.75" spans="1:4">
       <c r="A69" s="1">
         <v>42217</v>
       </c>
-      <c r="B69" s="8">
+      <c r="B69" s="12">
         <v>0.283</v>
       </c>
-      <c r="C69" s="8"/>
-      <c r="D69" s="8"/>
+      <c r="C69" s="12"/>
+      <c r="D69" s="12"/>
     </row>
     <row r="70" ht="14.75" spans="1:4">
       <c r="A70" s="1">
         <v>42248</v>
       </c>
-      <c r="B70" s="8">
+      <c r="B70" s="12">
         <v>-0.0678</v>
       </c>
-      <c r="C70" s="8"/>
-      <c r="D70" s="8"/>
+      <c r="C70" s="12"/>
+      <c r="D70" s="12"/>
     </row>
     <row r="71" ht="14.75" spans="1:4">
       <c r="A71" s="1">
         <v>42278</v>
       </c>
-      <c r="B71" s="8">
+      <c r="B71" s="12">
         <v>0.2277</v>
       </c>
-      <c r="C71" s="8"/>
-      <c r="D71" s="8"/>
+      <c r="C71" s="12"/>
+      <c r="D71" s="12"/>
     </row>
     <row r="72" ht="14.75" spans="1:4">
       <c r="A72" s="1">
         <v>42309</v>
       </c>
-      <c r="B72" s="8">
+      <c r="B72" s="12">
         <v>0.3277</v>
       </c>
-      <c r="C72" s="8"/>
-      <c r="D72" s="8"/>
+      <c r="C72" s="12"/>
+      <c r="D72" s="12"/>
     </row>
     <row r="73" ht="14.75" spans="1:4">
       <c r="A73" s="1">
         <v>42339</v>
       </c>
-      <c r="B73" s="8">
+      <c r="B73" s="12">
         <v>0.2392</v>
       </c>
-      <c r="C73" s="8"/>
-      <c r="D73" s="8"/>
+      <c r="C73" s="12"/>
+      <c r="D73" s="12"/>
     </row>
     <row r="74" ht="14.75" spans="1:4">
-      <c r="A74" s="9">
+      <c r="A74" s="13">
         <v>42370</v>
       </c>
-      <c r="B74" s="10">
+      <c r="B74" s="14">
         <v>-0.0084</v>
       </c>
-      <c r="C74" s="10"/>
-      <c r="D74" s="10"/>
+      <c r="C74" s="14"/>
+      <c r="D74" s="14"/>
     </row>
     <row r="75" ht="14.75" spans="1:4">
       <c r="A75" s="1">
         <v>42401</v>
       </c>
-      <c r="B75" s="8">
+      <c r="B75" s="12">
         <v>0.0011</v>
       </c>
-      <c r="C75" s="8"/>
-      <c r="D75" s="8"/>
+      <c r="C75" s="12"/>
+      <c r="D75" s="12"/>
     </row>
     <row r="76" ht="14.75" spans="1:4">
       <c r="A76" s="1">
         <v>42430</v>
       </c>
-      <c r="B76" s="8">
+      <c r="B76" s="12">
         <v>0.4005</v>
       </c>
-      <c r="C76" s="8"/>
-      <c r="D76" s="8"/>
+      <c r="C76" s="12"/>
+      <c r="D76" s="12"/>
     </row>
     <row r="77" ht="14.75" spans="1:4">
       <c r="A77" s="1">
         <v>42461</v>
       </c>
-      <c r="B77" s="8">
+      <c r="B77" s="12">
         <v>0.0084</v>
       </c>
-      <c r="C77" s="8"/>
-      <c r="D77" s="8"/>
+      <c r="C77" s="12"/>
+      <c r="D77" s="12"/>
     </row>
     <row r="78" ht="14.75" spans="1:4">
       <c r="A78" s="1">
         <v>42491</v>
       </c>
-      <c r="B78" s="8">
+      <c r="B78" s="12">
         <v>-0.0213</v>
       </c>
-      <c r="C78" s="8"/>
-      <c r="D78" s="8"/>
+      <c r="C78" s="12"/>
+      <c r="D78" s="12"/>
     </row>
     <row r="79" ht="14.75" spans="1:4">
       <c r="A79" s="1">
         <v>42522</v>
       </c>
-      <c r="B79" s="8">
+      <c r="B79" s="12">
         <v>0.1059</v>
       </c>
-      <c r="C79" s="8"/>
-      <c r="D79" s="8"/>
+      <c r="C79" s="12"/>
+      <c r="D79" s="12"/>
     </row>
     <row r="80" ht="14.75" spans="1:4">
       <c r="A80" s="1">
         <v>42552</v>
       </c>
-      <c r="B80" s="8">
+      <c r="B80" s="12">
         <v>0.0296</v>
       </c>
-      <c r="C80" s="8"/>
-      <c r="D80" s="8"/>
+      <c r="C80" s="12"/>
+      <c r="D80" s="12"/>
     </row>
     <row r="81" ht="14.75" spans="1:4">
       <c r="A81" s="1">
         <v>42583</v>
       </c>
-      <c r="B81" s="8">
+      <c r="B81" s="12">
         <v>0.0412</v>
       </c>
-      <c r="C81" s="8"/>
-      <c r="D81" s="8"/>
+      <c r="C81" s="12"/>
+      <c r="D81" s="12"/>
     </row>
     <row r="82" ht="14.75" spans="1:4">
       <c r="A82" s="1">
         <v>42614</v>
       </c>
-      <c r="B82" s="8">
+      <c r="B82" s="12">
         <v>0.0455</v>
       </c>
-      <c r="C82" s="8"/>
-      <c r="D82" s="8"/>
+      <c r="C82" s="12"/>
+      <c r="D82" s="12"/>
     </row>
     <row r="83" ht="14.75" spans="1:4">
       <c r="A83" s="1">
         <v>42644</v>
       </c>
-      <c r="B83" s="8">
+      <c r="B83" s="12">
         <v>0.0609</v>
       </c>
-      <c r="C83" s="8"/>
-      <c r="D83" s="8"/>
+      <c r="C83" s="12"/>
+      <c r="D83" s="12"/>
     </row>
     <row r="84" ht="14.75" spans="1:4">
       <c r="A84" s="1">
         <v>42675</v>
       </c>
-      <c r="B84" s="8">
+      <c r="B84" s="12">
         <v>0.0377</v>
       </c>
-      <c r="C84" s="8"/>
-      <c r="D84" s="8"/>
+      <c r="C84" s="12"/>
+      <c r="D84" s="12"/>
     </row>
     <row r="85" ht="14.75" spans="1:4">
       <c r="A85" s="1">
         <v>42705</v>
       </c>
-      <c r="B85" s="8">
+      <c r="B85" s="12">
         <v>0.12</v>
       </c>
-      <c r="C85" s="8"/>
-      <c r="D85" s="8"/>
+      <c r="C85" s="12"/>
+      <c r="D85" s="12"/>
     </row>
     <row r="86" ht="14.75" spans="1:4">
       <c r="A86" s="1">
         <v>42736</v>
       </c>
-      <c r="B86" s="8">
+      <c r="B86" s="12">
         <v>0.0177</v>
       </c>
-      <c r="C86" s="8"/>
-      <c r="D86" s="8"/>
+      <c r="C86" s="12"/>
+      <c r="D86" s="12"/>
     </row>
     <row r="87" ht="14.75" spans="1:4">
       <c r="A87" s="1">
         <v>42767</v>
       </c>
-      <c r="B87" s="8">
+      <c r="B87" s="12">
         <v>0.0514</v>
       </c>
-      <c r="C87" s="8"/>
-      <c r="D87" s="8"/>
+      <c r="C87" s="12"/>
+      <c r="D87" s="12"/>
     </row>
     <row r="88" ht="14.75" spans="1:4">
       <c r="A88" s="1">
         <v>42795</v>
       </c>
-      <c r="B88" s="8">
+      <c r="B88" s="12">
         <v>-0.0782</v>
       </c>
-      <c r="C88" s="8"/>
-      <c r="D88" s="8"/>
+      <c r="C88" s="12"/>
+      <c r="D88" s="12"/>
     </row>
     <row r="89" ht="14.75" spans="1:4">
       <c r="A89" s="1">
         <v>42826</v>
       </c>
-      <c r="B89" s="8">
+      <c r="B89" s="12">
         <v>0.0085</v>
       </c>
-      <c r="C89" s="8"/>
-      <c r="D89" s="8"/>
+      <c r="C89" s="12"/>
+      <c r="D89" s="12"/>
     </row>
     <row r="90" ht="14.75" spans="1:4">
       <c r="A90" s="1">
         <v>42856</v>
       </c>
-      <c r="B90" s="8">
+      <c r="B90" s="12">
         <v>-0.0614</v>
       </c>
-      <c r="C90" s="8"/>
-      <c r="D90" s="8"/>
+      <c r="C90" s="12"/>
+      <c r="D90" s="12"/>
     </row>
     <row r="91" ht="14.75" spans="1:4">
       <c r="A91" s="1">
         <v>42887</v>
       </c>
-      <c r="B91" s="8">
+      <c r="B91" s="12">
         <v>0.0901</v>
       </c>
-      <c r="C91" s="8"/>
-      <c r="D91" s="8"/>
+      <c r="C91" s="12"/>
+      <c r="D91" s="12"/>
     </row>
     <row r="92" ht="14.75" spans="1:4">
       <c r="A92" s="1">
         <v>42917</v>
       </c>
-      <c r="B92" s="8">
+      <c r="B92" s="12">
         <v>-0.0132</v>
       </c>
-      <c r="C92" s="8"/>
-      <c r="D92" s="8"/>
+      <c r="C92" s="12"/>
+      <c r="D92" s="12"/>
     </row>
     <row r="93" ht="14.75" spans="1:4">
       <c r="A93" s="1">
         <v>42948</v>
       </c>
-      <c r="B93" s="8">
+      <c r="B93" s="12">
         <v>0.1779</v>
       </c>
-      <c r="C93" s="8"/>
-      <c r="D93" s="8"/>
+      <c r="C93" s="12"/>
+      <c r="D93" s="12"/>
     </row>
     <row r="94" ht="14.75" spans="1:4">
       <c r="A94" s="1">
         <v>42979</v>
       </c>
-      <c r="B94" s="8">
+      <c r="B94" s="12">
         <v>0.0209</v>
       </c>
-      <c r="C94" s="8"/>
-      <c r="D94" s="8"/>
+      <c r="C94" s="12"/>
+      <c r="D94" s="12"/>
     </row>
     <row r="95" ht="14.75" spans="1:4">
       <c r="A95" s="1">
         <v>43009</v>
       </c>
-      <c r="B95" s="8">
+      <c r="B95" s="12">
         <v>-0.0084</v>
       </c>
-      <c r="C95" s="8"/>
-      <c r="D95" s="8"/>
+      <c r="C95" s="12"/>
+      <c r="D95" s="12"/>
     </row>
     <row r="96" ht="14.75" spans="1:4">
       <c r="A96" s="1">
         <v>43040</v>
       </c>
-      <c r="B96" s="8">
+      <c r="B96" s="12">
         <v>-0.0635</v>
       </c>
-      <c r="C96" s="8"/>
-      <c r="D96" s="8"/>
+      <c r="C96" s="12"/>
+      <c r="D96" s="12"/>
     </row>
     <row r="97" ht="14.75" spans="1:4">
       <c r="A97" s="1">
         <v>43070</v>
       </c>
-      <c r="B97" s="8">
+      <c r="B97" s="12">
         <v>-0.0392</v>
       </c>
-      <c r="C97" s="8"/>
-      <c r="D97" s="8"/>
+      <c r="C97" s="12"/>
+      <c r="D97" s="12"/>
     </row>
     <row r="98" ht="14.75" spans="1:4">
       <c r="A98" s="1">
         <v>43101</v>
       </c>
-      <c r="B98" s="8">
+      <c r="B98" s="12">
         <v>0.0243</v>
       </c>
-      <c r="C98" s="8"/>
-      <c r="D98" s="8"/>
+      <c r="C98" s="12"/>
+      <c r="D98" s="12"/>
     </row>
     <row r="99" ht="14.75" spans="1:4">
       <c r="A99" s="1">
         <v>43132</v>
       </c>
-      <c r="B99" s="8">
+      <c r="B99" s="12">
         <v>0.0119</v>
       </c>
-      <c r="C99" s="8"/>
-      <c r="D99" s="8"/>
+      <c r="C99" s="12"/>
+      <c r="D99" s="12"/>
     </row>
     <row r="100" ht="14.75" spans="1:4">
       <c r="A100" s="1">
         <v>43160</v>
       </c>
-      <c r="B100" s="8">
+      <c r="B100" s="12">
         <v>0.1099</v>
       </c>
-      <c r="C100" s="8"/>
-      <c r="D100" s="8"/>
+      <c r="C100" s="12"/>
+      <c r="D100" s="12"/>
     </row>
     <row r="101" ht="14.75" spans="1:4">
       <c r="A101" s="1">
         <v>43191</v>
       </c>
-      <c r="B101" s="8">
+      <c r="B101" s="12">
         <v>0.0021</v>
       </c>
-      <c r="C101" s="8"/>
-      <c r="D101" s="8"/>
+      <c r="C101" s="12"/>
+      <c r="D101" s="12"/>
     </row>
     <row r="102" ht="14.75" spans="1:4">
       <c r="A102" s="1">
         <v>43221</v>
       </c>
-      <c r="B102" s="8">
+      <c r="B102" s="12">
         <v>0.0257</v>
       </c>
-      <c r="C102" s="8"/>
-      <c r="D102" s="8"/>
+      <c r="C102" s="12"/>
+      <c r="D102" s="12"/>
     </row>
     <row r="103" ht="14.75" spans="1:4">
       <c r="A103" s="1">
         <v>43252</v>
       </c>
-      <c r="B103" s="8">
+      <c r="B103" s="12">
         <v>-0.0844</v>
       </c>
-      <c r="C103" s="8"/>
-      <c r="D103" s="8"/>
+      <c r="C103" s="12"/>
+      <c r="D103" s="12"/>
     </row>
     <row r="104" ht="14.75" spans="1:4">
       <c r="A104" s="1">
         <v>43282</v>
       </c>
-      <c r="B104" s="8">
+      <c r="B104" s="12">
         <v>0.1728</v>
       </c>
-      <c r="C104" s="8"/>
-      <c r="D104" s="8"/>
+      <c r="C104" s="12"/>
+      <c r="D104" s="12"/>
     </row>
     <row r="105" ht="14.75" spans="1:4">
       <c r="A105" s="1">
         <v>43313</v>
       </c>
-      <c r="B105" s="8">
+      <c r="B105" s="12">
         <v>-0.071</v>
       </c>
-      <c r="C105" s="8"/>
-      <c r="D105" s="8"/>
+      <c r="C105" s="12"/>
+      <c r="D105" s="12"/>
     </row>
     <row r="106" ht="14.75" spans="1:4">
       <c r="A106" s="1">
         <v>43344</v>
       </c>
-      <c r="B106" s="8">
+      <c r="B106" s="12">
         <v>0.0614</v>
       </c>
-      <c r="C106" s="8"/>
-      <c r="D106" s="8"/>
+      <c r="C106" s="12"/>
+      <c r="D106" s="12"/>
     </row>
     <row r="107" ht="14.75" spans="1:4">
       <c r="A107" s="1">
         <v>43374</v>
       </c>
-      <c r="B107" s="8">
+      <c r="B107" s="12">
         <v>0.0711</v>
       </c>
-      <c r="C107" s="8"/>
-      <c r="D107" s="8"/>
+      <c r="C107" s="12"/>
+      <c r="D107" s="12"/>
     </row>
     <row r="108" ht="14.75" spans="1:4">
       <c r="A108" s="1">
         <v>43405</v>
       </c>
-      <c r="B108" s="8">
+      <c r="B108" s="12">
         <v>0.1498</v>
       </c>
-      <c r="C108" s="8"/>
-      <c r="D108" s="8"/>
+      <c r="C108" s="12"/>
+      <c r="D108" s="12"/>
     </row>
     <row r="109" ht="14.75" spans="1:4">
       <c r="A109" s="1">
         <v>43435</v>
       </c>
-      <c r="B109" s="8">
+      <c r="B109" s="12">
         <v>-0.0448</v>
       </c>
-      <c r="C109" s="8"/>
-      <c r="D109" s="8"/>
+      <c r="C109" s="12"/>
+      <c r="D109" s="12"/>
     </row>
     <row r="110" ht="14.75" spans="1:4">
       <c r="A110" s="1">
         <v>43466</v>
       </c>
-      <c r="B110" s="8">
+      <c r="B110" s="12">
         <v>0.0143</v>
       </c>
-      <c r="C110" s="8"/>
-      <c r="D110" s="8"/>
+      <c r="C110" s="12"/>
+      <c r="D110" s="12"/>
     </row>
     <row r="111" ht="14.75" spans="1:4">
       <c r="A111" s="1">
         <v>43497</v>
       </c>
-      <c r="B111" s="8">
+      <c r="B111" s="12">
         <v>0.1369</v>
       </c>
-      <c r="C111" s="8"/>
-      <c r="D111" s="8"/>
+      <c r="C111" s="12"/>
+      <c r="D111" s="12"/>
     </row>
     <row r="112" ht="14.75" spans="1:4">
       <c r="A112" s="1">
         <v>43525</v>
       </c>
-      <c r="B112" s="8">
+      <c r="B112" s="12">
         <v>0.1862</v>
       </c>
-      <c r="C112" s="8"/>
-      <c r="D112" s="8"/>
+      <c r="C112" s="12"/>
+      <c r="D112" s="12"/>
     </row>
     <row r="113" ht="14.75" spans="1:4">
       <c r="A113" s="1">
         <v>43556</v>
       </c>
-      <c r="B113" s="8">
+      <c r="B113" s="12">
         <v>0.0276</v>
       </c>
-      <c r="C113" s="8"/>
-      <c r="D113" s="8"/>
+      <c r="C113" s="12"/>
+      <c r="D113" s="12"/>
     </row>
     <row r="114" ht="14.75" spans="1:4">
       <c r="A114" s="1">
         <v>43586</v>
       </c>
-      <c r="B114" s="8">
+      <c r="B114" s="12">
         <v>0.0582</v>
       </c>
-      <c r="C114" s="8"/>
-      <c r="D114" s="8"/>
+      <c r="C114" s="12"/>
+      <c r="D114" s="12"/>
     </row>
     <row r="115" ht="14.75" spans="1:4">
       <c r="A115" s="1">
         <v>43617</v>
       </c>
-      <c r="B115" s="8">
+      <c r="B115" s="12">
         <v>0.0329</v>
       </c>
-      <c r="C115" s="8"/>
-      <c r="D115" s="8"/>
+      <c r="C115" s="12"/>
+      <c r="D115" s="12"/>
     </row>
     <row r="116" ht="14.75" spans="1:4">
       <c r="A116" s="1">
         <v>43647</v>
       </c>
-      <c r="B116" s="8">
+      <c r="B116" s="12">
         <v>-0.0096</v>
       </c>
-      <c r="C116" s="8"/>
-      <c r="D116" s="8"/>
+      <c r="C116" s="12"/>
+      <c r="D116" s="12"/>
     </row>
     <row r="117" ht="14.75" spans="1:4">
       <c r="A117" s="1">
         <v>43678</v>
       </c>
-      <c r="B117" s="8">
+      <c r="B117" s="12">
         <v>-0.0119</v>
       </c>
-      <c r="C117" s="8"/>
-      <c r="D117" s="8"/>
+      <c r="C117" s="12"/>
+      <c r="D117" s="12"/>
     </row>
     <row r="118" ht="14.75" spans="1:4">
       <c r="A118" s="1">
         <v>43709</v>
       </c>
-      <c r="B118" s="8">
+      <c r="B118" s="12">
         <v>0.0449</v>
       </c>
-      <c r="C118" s="8"/>
-      <c r="D118" s="8"/>
+      <c r="C118" s="12"/>
+      <c r="D118" s="12"/>
     </row>
     <row r="119" ht="14.75" spans="1:4">
       <c r="A119" s="1">
         <v>43739</v>
       </c>
-      <c r="B119" s="8">
+      <c r="B119" s="12">
         <v>-0.0117</v>
       </c>
-      <c r="C119" s="8"/>
-      <c r="D119" s="8"/>
+      <c r="C119" s="12"/>
+      <c r="D119" s="12"/>
     </row>
     <row r="120" ht="14.75" spans="1:4">
       <c r="A120" s="1">
         <v>43770</v>
       </c>
-      <c r="B120" s="8">
+      <c r="B120" s="12">
         <v>-0.0051</v>
       </c>
-      <c r="C120" s="8"/>
-      <c r="D120" s="8"/>
+      <c r="C120" s="12"/>
+      <c r="D120" s="12"/>
     </row>
     <row r="121" ht="14.75" spans="1:4">
       <c r="A121" s="1">
         <v>43800</v>
       </c>
-      <c r="B121" s="8">
+      <c r="B121" s="12">
         <v>0.1302</v>
       </c>
-      <c r="C121" s="8"/>
-      <c r="D121" s="8"/>
+      <c r="C121" s="12"/>
+      <c r="D121" s="12"/>
     </row>
     <row r="122" ht="14.75" spans="1:4">
       <c r="A122" s="1">
         <v>43831</v>
       </c>
-      <c r="B122" s="8">
+      <c r="B122" s="12">
         <v>0.0099</v>
       </c>
-      <c r="C122" s="8"/>
-      <c r="D122" s="8"/>
+      <c r="C122" s="12"/>
+      <c r="D122" s="12"/>
     </row>
     <row r="123" ht="14.75" spans="1:4">
       <c r="A123" s="1">
         <v>43862</v>
       </c>
-      <c r="B123" s="8">
+      <c r="B123" s="12">
         <v>0.0369</v>
       </c>
-      <c r="C123" s="8"/>
-      <c r="D123" s="8"/>
+      <c r="C123" s="12"/>
+      <c r="D123" s="12"/>
     </row>
     <row r="124" ht="14.75" spans="1:4">
       <c r="A124" s="1">
         <v>43891</v>
       </c>
-      <c r="B124" s="8">
+      <c r="B124" s="12">
         <v>0.0595</v>
       </c>
-      <c r="C124" s="8"/>
-      <c r="D124" s="8"/>
+      <c r="C124" s="12"/>
+      <c r="D124" s="12"/>
     </row>
     <row r="125" ht="14.75" spans="1:4">
       <c r="A125" s="1">
         <v>43922</v>
       </c>
-      <c r="B125" s="8">
+      <c r="B125" s="12">
         <v>0.0314</v>
       </c>
-      <c r="C125" s="8"/>
-      <c r="D125" s="8"/>
+      <c r="C125" s="12"/>
+      <c r="D125" s="12"/>
     </row>
     <row r="126" ht="14.75" spans="1:4">
       <c r="A126" s="1">
         <v>43952</v>
       </c>
-      <c r="B126" s="8">
+      <c r="B126" s="12">
         <v>0.0684</v>
       </c>
-      <c r="C126" s="8"/>
-      <c r="D126" s="8"/>
+      <c r="C126" s="12"/>
+      <c r="D126" s="12"/>
     </row>
     <row r="127" ht="14.75" spans="1:4">
       <c r="A127" s="1">
         <v>43983</v>
       </c>
-      <c r="B127" s="8">
+      <c r="B127" s="12">
         <v>0.0866</v>
       </c>
-      <c r="C127" s="8"/>
-      <c r="D127" s="8"/>
+      <c r="C127" s="12"/>
+      <c r="D127" s="12"/>
     </row>
     <row r="128" ht="14.75" spans="1:4">
       <c r="A128" s="1">
         <v>44013</v>
       </c>
-      <c r="B128" s="8">
+      <c r="B128" s="12">
         <v>0.0961</v>
       </c>
-      <c r="C128" s="8"/>
-      <c r="D128" s="8"/>
+      <c r="C128" s="12"/>
+      <c r="D128" s="12"/>
     </row>
     <row r="129" ht="14.75" spans="1:4">
       <c r="A129" s="1">
         <v>44044</v>
       </c>
-      <c r="B129" s="8">
+      <c r="B129" s="12">
         <v>0.1462</v>
       </c>
-      <c r="C129" s="8"/>
-      <c r="D129" s="8"/>
+      <c r="C129" s="12"/>
+      <c r="D129" s="12"/>
     </row>
     <row r="130" ht="14.75" spans="1:4">
       <c r="A130" s="1">
         <v>44075</v>
       </c>
-      <c r="B130" s="8">
+      <c r="B130" s="12">
         <v>-0.0312</v>
       </c>
-      <c r="C130" s="8"/>
-      <c r="D130" s="8"/>
+      <c r="C130" s="12"/>
+      <c r="D130" s="12"/>
     </row>
     <row r="131" ht="14.75" spans="1:4">
       <c r="A131" s="1">
         <v>44105</v>
       </c>
-      <c r="B131" s="8">
+      <c r="B131" s="12">
         <v>0.0274</v>
       </c>
-      <c r="C131" s="8"/>
-      <c r="D131" s="8"/>
+      <c r="C131" s="12"/>
+      <c r="D131" s="12"/>
     </row>
     <row r="132" ht="14.75" spans="1:4">
       <c r="A132" s="1">
         <v>44136</v>
       </c>
-      <c r="B132" s="8">
+      <c r="B132" s="12">
         <v>0.0181</v>
       </c>
-      <c r="C132" s="8"/>
-      <c r="D132" s="8"/>
-    </row>
-    <row r="133" spans="1:4">
+      <c r="C132" s="12"/>
+      <c r="D132" s="12"/>
+    </row>
+    <row r="133" ht="14.75" spans="1:4">
       <c r="A133" s="1">
         <v>44166</v>
       </c>
-      <c r="B133" s="8">
+      <c r="B133" s="12">
         <v>-0.112</v>
       </c>
-      <c r="C133" s="8"/>
-      <c r="D133" s="8"/>
-    </row>
-    <row r="134" spans="1:4">
+      <c r="C133" s="12"/>
+      <c r="D133" s="12"/>
+    </row>
+    <row r="134" ht="14.75" spans="1:4">
       <c r="A134" s="1">
         <v>44197</v>
       </c>
-      <c r="B134" s="8">
+      <c r="B134" s="12">
         <v>0.0077</v>
       </c>
-      <c r="C134" s="8"/>
-      <c r="D134" s="8"/>
-    </row>
-    <row r="135" spans="1:4">
+      <c r="C134" s="12"/>
+      <c r="D134" s="12"/>
+    </row>
+    <row r="135" ht="14.75" spans="1:4">
       <c r="A135" s="1">
         <v>44228</v>
       </c>
-      <c r="B135" s="8">
+      <c r="B135" s="12">
         <v>0.1271</v>
       </c>
-      <c r="C135" s="8"/>
-      <c r="D135" s="8"/>
+      <c r="C135" s="12"/>
+      <c r="D135" s="12"/>
     </row>
     <row r="136" ht="14.75" spans="1:4">
       <c r="A136" s="1">
         <v>44256</v>
       </c>
-      <c r="B136" s="8">
+      <c r="B136" s="12">
         <v>0.1564</v>
       </c>
-      <c r="C136" s="8"/>
-      <c r="D136" s="8"/>
+      <c r="C136" s="12"/>
+      <c r="D136" s="12"/>
     </row>
     <row r="137" ht="14.75" spans="1:4">
       <c r="A137" s="1">
         <v>44287</v>
       </c>
-      <c r="B137" s="8">
+      <c r="B137" s="12">
         <v>-0.0061</v>
       </c>
-      <c r="C137" s="8"/>
-      <c r="D137" s="8"/>
+      <c r="C137" s="12"/>
+      <c r="D137" s="12"/>
     </row>
     <row r="138" ht="14.75" spans="1:4">
       <c r="A138" s="1">
         <v>44317</v>
       </c>
-      <c r="B138" s="8">
+      <c r="B138" s="12">
         <v>0.0562</v>
       </c>
-      <c r="C138" s="8"/>
-      <c r="D138" s="8"/>
+      <c r="C138" s="12"/>
+      <c r="D138" s="12"/>
     </row>
     <row r="139" ht="14.75" spans="1:4">
       <c r="A139" s="1">
         <v>44348</v>
       </c>
-      <c r="B139" s="8">
+      <c r="B139" s="12">
         <v>0.0235</v>
       </c>
-      <c r="C139" s="8"/>
-      <c r="D139" s="8"/>
+      <c r="C139" s="12"/>
+      <c r="D139" s="12"/>
     </row>
     <row r="140" ht="14.75" spans="1:4">
       <c r="A140" s="1">
         <v>44378</v>
       </c>
-      <c r="B140" s="8">
+      <c r="B140" s="12">
         <v>-0.0538</v>
       </c>
-      <c r="C140" s="8"/>
-      <c r="D140" s="8"/>
+      <c r="C140" s="12"/>
+      <c r="D140" s="12"/>
     </row>
     <row r="141" ht="14.75" spans="1:4">
       <c r="A141" s="1">
         <v>44409</v>
       </c>
-      <c r="B141" s="8">
+      <c r="B141" s="12">
         <v>0.0861</v>
       </c>
-      <c r="C141" s="8"/>
-      <c r="D141" s="8"/>
+      <c r="C141" s="12"/>
+      <c r="D141" s="12"/>
     </row>
     <row r="142" ht="14.75" spans="1:4">
       <c r="A142" s="1">
         <v>44440</v>
       </c>
-      <c r="B142" s="8">
+      <c r="B142" s="12">
         <v>-0.0215</v>
       </c>
-      <c r="C142" s="8"/>
-      <c r="D142" s="8"/>
+      <c r="C142" s="12"/>
+      <c r="D142" s="12"/>
     </row>
     <row r="143" ht="14.75" spans="1:4">
       <c r="A143" s="1">
         <v>44470</v>
       </c>
-      <c r="B143" s="8">
+      <c r="B143" s="12">
         <v>-0.0512</v>
       </c>
-      <c r="C143" s="8"/>
-      <c r="D143" s="8"/>
+      <c r="C143" s="12"/>
+      <c r="D143" s="12"/>
     </row>
     <row r="144" ht="14.75" spans="1:4">
       <c r="A144" s="1">
         <v>44501</v>
       </c>
-      <c r="B144" s="8">
+      <c r="B144" s="12">
         <v>0.1091</v>
       </c>
-      <c r="C144" s="8"/>
-      <c r="D144" s="8"/>
+      <c r="C144" s="12"/>
+      <c r="D144" s="12"/>
     </row>
     <row r="145" ht="14.75" spans="1:4">
       <c r="A145" s="1">
         <v>44531</v>
       </c>
-      <c r="B145" s="8">
+      <c r="B145" s="12">
         <v>0.1123</v>
       </c>
-      <c r="C145" s="8"/>
-      <c r="D145" s="8"/>
+      <c r="C145" s="12"/>
+      <c r="D145" s="12"/>
     </row>
     <row r="146" ht="14.75" spans="1:4">
       <c r="A146" s="1">
         <v>44562</v>
       </c>
-      <c r="B146" s="8">
+      <c r="B146" s="12">
         <v>-0.0016</v>
       </c>
-      <c r="C146" s="8"/>
-      <c r="D146" s="8"/>
+      <c r="C146" s="12"/>
+      <c r="D146" s="12"/>
     </row>
     <row r="147" ht="14.75" spans="1:4">
       <c r="A147" s="1">
         <v>44593</v>
       </c>
-      <c r="B147" s="8">
+      <c r="B147" s="12">
         <v>0.0797</v>
       </c>
-      <c r="C147" s="8"/>
-      <c r="D147" s="8"/>
+      <c r="C147" s="12"/>
+      <c r="D147" s="12"/>
     </row>
     <row r="148" ht="14.75" spans="1:4">
       <c r="A148" s="1">
         <v>44621</v>
       </c>
-      <c r="B148" s="8">
+      <c r="B148" s="12">
         <v>0.0547</v>
       </c>
-      <c r="C148" s="8"/>
-      <c r="D148" s="8"/>
+      <c r="C148" s="12"/>
+      <c r="D148" s="12"/>
     </row>
     <row r="149" ht="14.75" spans="1:4">
       <c r="A149" s="1">
         <v>44652</v>
       </c>
-      <c r="B149" s="8">
+      <c r="B149" s="12">
         <v>-0.0187</v>
       </c>
-      <c r="C149" s="8"/>
-      <c r="D149" s="8"/>
+      <c r="C149" s="12"/>
+      <c r="D149" s="12"/>
     </row>
     <row r="150" ht="14.75" spans="1:4">
       <c r="A150" s="1">
         <v>44682</v>
       </c>
-      <c r="B150" s="8">
+      <c r="B150" s="12">
         <v>0.2725</v>
       </c>
-      <c r="C150" s="8"/>
-      <c r="D150" s="8"/>
+      <c r="C150" s="12"/>
+      <c r="D150" s="12"/>
     </row>
     <row r="151" ht="14.75" spans="1:4">
       <c r="A151" s="1">
         <v>44713</v>
       </c>
-      <c r="B151" s="8">
+      <c r="B151" s="12">
         <v>0.1417</v>
       </c>
-      <c r="C151" s="8"/>
-      <c r="D151" s="8"/>
+      <c r="C151" s="12"/>
+      <c r="D151" s="12"/>
     </row>
     <row r="152" ht="14.75" spans="1:4">
       <c r="A152" s="1">
         <v>44743</v>
       </c>
-      <c r="B152" s="8">
+      <c r="B152" s="12">
         <v>0.2166</v>
       </c>
-      <c r="C152" s="8"/>
-      <c r="D152" s="8"/>
+      <c r="C152" s="12"/>
+      <c r="D152" s="12"/>
     </row>
     <row r="153" ht="14.75" spans="1:4">
       <c r="A153" s="1">
         <v>44774</v>
       </c>
-      <c r="B153" s="8">
+      <c r="B153" s="12">
         <v>0.1873</v>
       </c>
-      <c r="C153" s="8"/>
-      <c r="D153" s="8"/>
+      <c r="C153" s="12"/>
+      <c r="D153" s="12"/>
     </row>
     <row r="154" ht="14.75" spans="1:4">
       <c r="A154" s="1">
         <v>44805</v>
       </c>
-      <c r="B154" s="8">
+      <c r="B154" s="12">
         <v>0.0367</v>
       </c>
-      <c r="C154" s="8"/>
-      <c r="D154" s="8"/>
+      <c r="C154" s="12"/>
+      <c r="D154" s="12"/>
     </row>
     <row r="155" ht="14.75" spans="1:4">
       <c r="A155" s="1">
         <v>44835</v>
       </c>
-      <c r="B155" s="8">
+      <c r="B155" s="12">
         <v>0.0711</v>
       </c>
-      <c r="C155" s="8"/>
-      <c r="D155" s="8"/>
+      <c r="C155" s="12"/>
+      <c r="D155" s="12"/>
     </row>
     <row r="156" ht="14.75" spans="1:4">
       <c r="A156" s="1">
         <v>44866</v>
       </c>
-      <c r="B156" s="8">
+      <c r="B156" s="12">
         <v>0.1051</v>
       </c>
-      <c r="C156" s="8"/>
-      <c r="D156" s="8"/>
+      <c r="C156" s="12"/>
+      <c r="D156" s="12"/>
     </row>
     <row r="157" ht="14.75" spans="1:4">
       <c r="A157" s="1">
         <v>44896</v>
       </c>
-      <c r="B157" s="8">
+      <c r="B157" s="12">
         <v>0.0431</v>
       </c>
-      <c r="C157" s="8"/>
-      <c r="D157" s="8"/>
+      <c r="C157" s="12"/>
+      <c r="D157" s="12"/>
     </row>
     <row r="158" ht="14.75" spans="1:4">
       <c r="A158" s="1">
         <v>44927</v>
       </c>
-      <c r="B158" s="8">
+      <c r="B158" s="12">
         <v>0.0148</v>
       </c>
-      <c r="C158" s="8"/>
-      <c r="D158" s="8"/>
+      <c r="C158" s="12"/>
+      <c r="D158" s="12"/>
     </row>
     <row r="159" ht="14.75" spans="1:4">
       <c r="A159" s="1">
         <v>44958</v>
       </c>
-      <c r="B159" s="8">
+      <c r="B159" s="12">
         <v>0.0113</v>
       </c>
-      <c r="C159" s="8"/>
-      <c r="D159" s="8"/>
+      <c r="C159" s="12"/>
+      <c r="D159" s="12"/>
     </row>
     <row r="160" ht="14.75" spans="1:4">
       <c r="A160" s="1">
         <v>44986</v>
       </c>
-      <c r="B160" s="8">
+      <c r="B160" s="12">
         <v>-0.0182</v>
       </c>
-      <c r="C160" s="8"/>
-      <c r="D160" s="8"/>
+      <c r="C160" s="12"/>
+      <c r="D160" s="12"/>
     </row>
     <row r="161" ht="14.75" spans="1:4">
       <c r="A161" s="1">
         <v>45017</v>
       </c>
-      <c r="B161" s="8">
+      <c r="B161" s="12">
         <v>0.0234</v>
       </c>
-      <c r="C161" s="8"/>
-      <c r="D161" s="8"/>
+      <c r="C161" s="12"/>
+      <c r="D161" s="12"/>
     </row>
     <row r="162" ht="14.75" spans="1:4">
       <c r="A162" s="1">
         <v>45047</v>
       </c>
-      <c r="B162" s="8">
+      <c r="B162" s="12">
         <v>0.0327</v>
       </c>
-      <c r="C162" s="8"/>
-      <c r="D162" s="8"/>
+      <c r="C162" s="12"/>
+      <c r="D162" s="12"/>
     </row>
     <row r="163" ht="14.75" spans="1:4">
       <c r="A163" s="1">
         <v>45078</v>
       </c>
-      <c r="B163" s="8">
+      <c r="B163" s="12">
         <v>0.047</v>
       </c>
-      <c r="C163" s="8"/>
-      <c r="D163" s="8"/>
+      <c r="C163" s="12"/>
+      <c r="D163" s="12"/>
     </row>
     <row r="164" ht="14.75" spans="1:4">
       <c r="A164" s="1">
         <v>45108</v>
       </c>
-      <c r="B164" s="8">
+      <c r="B164" s="12">
         <v>0.1586</v>
       </c>
-      <c r="C164" s="8"/>
-      <c r="D164" s="8"/>
+      <c r="C164" s="12"/>
+      <c r="D164" s="12"/>
     </row>
     <row r="165" ht="14.75" spans="1:4">
       <c r="A165" s="1">
         <v>45139</v>
       </c>
-      <c r="B165" s="8">
+      <c r="B165" s="12">
         <v>-0.021</v>
       </c>
-      <c r="C165" s="8"/>
-      <c r="D165" s="8"/>
+      <c r="C165" s="12"/>
+      <c r="D165" s="12"/>
     </row>
     <row r="166" ht="14.75" spans="1:4">
       <c r="A166" s="1">
         <v>45170</v>
       </c>
-      <c r="B166" s="8">
+      <c r="B166" s="12">
         <v>0.024</v>
       </c>
-      <c r="C166" s="8"/>
-      <c r="D166" s="8"/>
+      <c r="C166" s="12"/>
+      <c r="D166" s="12"/>
     </row>
     <row r="167" ht="14.75" spans="1:4">
       <c r="A167" s="1">
         <v>45200</v>
       </c>
-      <c r="B167" s="8">
+      <c r="B167" s="12">
         <v>0.0474</v>
       </c>
-      <c r="C167" s="8"/>
-      <c r="D167" s="8"/>
+      <c r="C167" s="12"/>
+      <c r="D167" s="12"/>
     </row>
     <row r="168" ht="14.75" spans="1:4">
       <c r="A168" s="1">
         <v>45231</v>
       </c>
-      <c r="B168" s="8">
+      <c r="B168" s="12">
         <v>0.1049</v>
       </c>
-      <c r="C168" s="8"/>
-      <c r="D168" s="8"/>
+      <c r="C168" s="12"/>
+      <c r="D168" s="12"/>
     </row>
     <row r="169" ht="14.75" spans="1:4">
       <c r="A169" s="1">
         <v>45261</v>
       </c>
-      <c r="B169" s="8">
+      <c r="B169" s="12">
         <v>-0.0024</v>
       </c>
-      <c r="C169" s="8"/>
-      <c r="D169" s="8"/>
+      <c r="C169" s="12"/>
+      <c r="D169" s="12"/>
     </row>
     <row r="170" ht="14.75" spans="1:4">
       <c r="A170" s="1">
         <v>45292</v>
       </c>
-      <c r="B170" s="8">
+      <c r="B170" s="12">
         <v>0.0587</v>
       </c>
-      <c r="C170" s="8"/>
-      <c r="D170" s="8"/>
+      <c r="C170" s="12"/>
+      <c r="D170" s="12"/>
     </row>
     <row r="171" ht="14.75" spans="1:4">
       <c r="A171" s="1">
         <v>45323</v>
       </c>
-      <c r="B171" s="8">
+      <c r="B171" s="12">
         <v>0.1895</v>
       </c>
-      <c r="C171" s="8"/>
-      <c r="D171" s="8"/>
+      <c r="C171" s="12"/>
+      <c r="D171" s="12"/>
     </row>
     <row r="172" ht="14.75" spans="1:4">
       <c r="A172" s="1">
         <v>45352</v>
       </c>
-      <c r="B172" s="8">
+      <c r="B172" s="12">
         <v>0.2207</v>
       </c>
-      <c r="C172" s="8"/>
-      <c r="D172" s="8"/>
+      <c r="C172" s="12"/>
+      <c r="D172" s="12"/>
     </row>
     <row r="173" ht="14.75" spans="1:4">
       <c r="A173" s="1">
         <v>45383</v>
       </c>
-      <c r="B173" s="8">
+      <c r="B173" s="12">
         <v>0.0343</v>
       </c>
-      <c r="C173" s="8"/>
-      <c r="D173" s="8"/>
+      <c r="C173" s="12"/>
+      <c r="D173" s="12"/>
     </row>
     <row r="174" ht="14.75" spans="1:4">
       <c r="A174" s="1">
         <v>45413</v>
       </c>
-      <c r="B174" s="8">
+      <c r="B174" s="12">
         <v>-0.0156</v>
       </c>
-      <c r="C174" s="8"/>
-      <c r="D174" s="8"/>
+      <c r="C174" s="12"/>
+      <c r="D174" s="12"/>
     </row>
     <row r="175" ht="14.75" spans="1:4">
       <c r="A175" s="1">
         <v>45444</v>
       </c>
-      <c r="B175" s="8">
+      <c r="B175" s="12">
         <v>-0.1354</v>
       </c>
-      <c r="C175" s="8"/>
-      <c r="D175" s="8"/>
+      <c r="C175" s="12"/>
+      <c r="D175" s="12"/>
     </row>
     <row r="176" ht="14.75" spans="1:4">
       <c r="A176" s="1">
         <v>45474</v>
       </c>
-      <c r="B176" s="8">
+      <c r="B176" s="12">
         <v>0.1169</v>
       </c>
-      <c r="C176" s="8"/>
-      <c r="D176" s="8"/>
+      <c r="C176" s="12"/>
+      <c r="D176" s="12"/>
     </row>
     <row r="177" ht="14.75" spans="1:4">
       <c r="A177" s="1">
         <v>45505</v>
       </c>
-      <c r="B177" s="8">
+      <c r="B177" s="12">
         <v>0.1481</v>
       </c>
-      <c r="C177" s="8"/>
-      <c r="D177" s="8"/>
+      <c r="C177" s="12"/>
+      <c r="D177" s="12"/>
     </row>
     <row r="178" ht="14.75" spans="1:4">
       <c r="A178" s="1">
         <v>45536</v>
       </c>
-      <c r="B178" s="8">
+      <c r="B178" s="12">
         <v>0.2549</v>
       </c>
-      <c r="C178" s="8"/>
-      <c r="D178" s="8"/>
+      <c r="C178" s="12"/>
+      <c r="D178" s="12"/>
     </row>
     <row r="179" ht="14.75" spans="1:4">
       <c r="A179" s="1">
         <v>45566</v>
       </c>
-      <c r="B179" s="8">
+      <c r="B179" s="12">
         <v>0.2231</v>
       </c>
-      <c r="C179" s="8"/>
-      <c r="D179" s="8"/>
+      <c r="C179" s="12"/>
+      <c r="D179" s="12"/>
     </row>
     <row r="180" ht="14.75" spans="1:4">
       <c r="A180" s="1">
         <v>45597</v>
       </c>
-      <c r="B180" s="8">
+      <c r="B180" s="12">
         <v>0.1335</v>
       </c>
-      <c r="C180" s="8"/>
-      <c r="D180" s="8"/>
+      <c r="C180" s="12"/>
+      <c r="D180" s="12"/>
     </row>
     <row r="181" ht="14.75" spans="1:4">
       <c r="A181" s="1">
         <v>45627</v>
       </c>
-      <c r="B181" s="8">
+      <c r="B181" s="12">
         <v>0.0415</v>
       </c>
-      <c r="C181" s="8"/>
-      <c r="D181" s="8"/>
+      <c r="C181" s="12"/>
+      <c r="D181" s="12"/>
     </row>
     <row r="182" ht="14.75" spans="1:4">
       <c r="A182" s="1">
         <v>45658</v>
       </c>
-      <c r="B182" s="8">
+      <c r="B182" s="12">
         <v>-0.0074</v>
       </c>
-      <c r="C182" s="8"/>
-      <c r="D182" s="8"/>
+      <c r="C182" s="12"/>
+      <c r="D182" s="12"/>
     </row>
     <row r="183" ht="14.75" spans="1:4">
       <c r="A183" s="1">
         <v>45689</v>
       </c>
-      <c r="B183" s="8">
+      <c r="B183" s="12">
         <v>0.2489</v>
       </c>
-      <c r="C183" s="8"/>
-      <c r="D183" s="8"/>
+      <c r="C183" s="12"/>
+      <c r="D183" s="12"/>
     </row>
     <row r="184" ht="14.75" spans="1:4">
       <c r="A184" s="1">
         <v>45717</v>
       </c>
-      <c r="B184" s="8">
+      <c r="B184" s="12">
         <v>-0.0711</v>
       </c>
-      <c r="C184" s="8"/>
-      <c r="D184" s="8"/>
+      <c r="C184" s="12"/>
+      <c r="D184" s="12"/>
     </row>
     <row r="185" ht="14.75" spans="1:4">
       <c r="A185" s="1">
         <v>45748</v>
       </c>
-      <c r="B185" s="8">
+      <c r="B185" s="12">
         <v>0.0526</v>
       </c>
-      <c r="C185" s="8"/>
-      <c r="D185" s="8"/>
+      <c r="C185" s="12"/>
+      <c r="D185" s="12"/>
     </row>
     <row r="186" ht="14.75" spans="1:4">
       <c r="A186" s="1">
         <v>45778</v>
       </c>
-      <c r="B186" s="8">
+      <c r="B186" s="12">
         <v>0.0431</v>
       </c>
-      <c r="C186" s="8"/>
-      <c r="D186" s="8"/>
+      <c r="C186" s="12"/>
+      <c r="D186" s="12"/>
     </row>
     <row r="187" ht="14.75" spans="1:4">
       <c r="A187" s="1">
         <v>45809</v>
       </c>
-      <c r="B187" s="8">
+      <c r="B187" s="12">
         <v>0.1423</v>
       </c>
-      <c r="C187" s="8"/>
-      <c r="D187" s="8"/>
+      <c r="C187" s="12"/>
+      <c r="D187" s="12"/>
     </row>
     <row r="188" ht="14.75" spans="1:4">
       <c r="A188" s="1">
         <v>45839</v>
       </c>
-      <c r="B188" s="8">
+      <c r="B188" s="12">
         <v>0.0876</v>
       </c>
-      <c r="C188" s="8"/>
-      <c r="D188" s="8"/>
+      <c r="C188" s="12"/>
+      <c r="D188" s="12"/>
     </row>
     <row r="189" ht="14.75" spans="1:4">
       <c r="A189" s="1">
         <v>45870</v>
       </c>
-      <c r="B189" s="8">
+      <c r="B189" s="12">
         <v>-0.0326</v>
       </c>
-      <c r="C189" s="8"/>
-      <c r="D189" s="8"/>
+      <c r="C189" s="12"/>
+      <c r="D189" s="12"/>
     </row>
     <row r="190" ht="14.75" spans="1:4">
       <c r="A190" s="1">
         <v>45901</v>
       </c>
-      <c r="B190" s="8">
+      <c r="B190" s="12">
         <v>0.1218</v>
       </c>
-      <c r="C190" s="8"/>
-      <c r="D190" s="8"/>
+      <c r="C190" s="12"/>
+      <c r="D190" s="12"/>
     </row>
     <row r="191" ht="14.75" spans="1:4">
       <c r="A191" s="1">
         <v>45931</v>
       </c>
-      <c r="B191" s="8">
+      <c r="B191" s="12">
         <v>0.0044</v>
       </c>
-      <c r="C191" s="8"/>
-      <c r="D191" s="8"/>
+      <c r="C191" s="12"/>
+      <c r="D191" s="12"/>
     </row>
     <row r="192" ht="14.75" spans="1:4">
       <c r="A192" s="1">
         <v>45962</v>
       </c>
-      <c r="B192" s="8">
+      <c r="B192" s="12">
         <v>0.0793</v>
       </c>
-      <c r="C192" s="8"/>
-      <c r="D192" s="8"/>
+      <c r="C192" s="12"/>
+      <c r="D192" s="12"/>
     </row>
     <row r="193" ht="14.75" spans="1:4">
-      <c r="A193" s="9">
+      <c r="A193" s="13">
         <v>45992</v>
       </c>
-      <c r="B193" s="10">
+      <c r="B193" s="14">
         <v>-0.0685</v>
       </c>
-      <c r="C193" s="10"/>
-      <c r="D193" s="10"/>
+      <c r="C193" s="14"/>
+      <c r="D193" s="14"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5009,7 +5977,7 @@
       <c r="Q2">
         <v>-0.0074</v>
       </c>
-      <c r="R2" s="6" cm="1">
+      <c r="R2" s="10" cm="1">
         <f t="array" ref="R2">PRODUCT(B2:Q2+1)-1</f>
         <v>0.194840242744342</v>
       </c>
@@ -5213,7 +6181,7 @@
       <c r="Q5">
         <v>0.0526</v>
       </c>
-      <c r="R5" s="7" cm="1">
+      <c r="R5" s="11" cm="1">
         <f t="array" ref="R5">PRODUCT(B5:Q5+1)-1</f>
         <v>0.323510793037694</v>
       </c>
@@ -5281,7 +6249,7 @@
       <c r="Q6">
         <v>0.0431</v>
       </c>
-      <c r="R6" s="7" cm="1">
+      <c r="R6" s="11" cm="1">
         <f t="array" ref="R6">PRODUCT(B6:Q6+1)-1</f>
         <v>1.28723547337183</v>
       </c>
@@ -5349,7 +6317,7 @@
       <c r="Q7">
         <v>0.1423</v>
       </c>
-      <c r="R7" s="7" cm="1">
+      <c r="R7" s="11" cm="1">
         <f t="array" ref="R7">PRODUCT(B7:Q7+1)-1</f>
         <v>0.595591661283158</v>
       </c>
@@ -5774,71 +6742,71 @@
       </c>
     </row>
     <row r="14" spans="2:18">
-      <c r="B14" s="5">
+      <c r="B14" s="7">
         <f>(1+B2)*(1+B3)*(1+B4)*(1+B5)*(1+B6)*(1+B7)*(1+B8)*(1+B9)*(1+B10)*(1+B11)*(1+B12)*(1+B13)-1</f>
         <v>0.653614174322446</v>
       </c>
-      <c r="C14" s="5">
+      <c r="C14" s="7">
         <f t="shared" ref="C14:Q14" si="2">(1+C2)*(1+C3)*(1+C4)*(1+C5)*(1+C6)*(1+C7)*(1+C8)*(1+C9)*(1+C10)*(1+C11)*(1+C12)*(1+C13)-1</f>
         <v>-0.0855664203647523</v>
       </c>
-      <c r="D14" s="5">
+      <c r="D14" s="7">
         <f t="shared" si="2"/>
         <v>0.0384573958480514</v>
       </c>
-      <c r="E14" s="5">
+      <c r="E14" s="7">
         <f t="shared" si="2"/>
         <v>0.765405002524292</v>
       </c>
-      <c r="F14" s="5">
+      <c r="F14" s="7">
         <f t="shared" si="2"/>
         <v>1.19935720490706</v>
       </c>
-      <c r="G14" s="5">
+      <c r="G14" s="7">
         <f t="shared" si="2"/>
         <v>5.98281172803228</v>
       </c>
-      <c r="H14" s="5">
+      <c r="H14" s="7">
         <f t="shared" si="2"/>
         <v>1.09694188883488</v>
       </c>
-      <c r="I14" s="5">
+      <c r="I14" s="7">
         <f t="shared" si="2"/>
         <v>0.0775695328691113</v>
       </c>
-      <c r="J14" s="5">
+      <c r="J14" s="7">
         <f t="shared" si="2"/>
         <v>0.472825224873327</v>
       </c>
-      <c r="K14" s="5">
+      <c r="K14" s="7">
         <f t="shared" si="2"/>
         <v>0.745848408003567</v>
       </c>
-      <c r="L14" s="5">
+      <c r="L14" s="7">
         <f t="shared" si="2"/>
         <v>0.501877778017195</v>
       </c>
-      <c r="M14" s="5">
+      <c r="M14" s="7">
         <f t="shared" si="2"/>
         <v>0.660960857965097</v>
       </c>
-      <c r="N14" s="5">
+      <c r="N14" s="7">
         <f t="shared" si="2"/>
         <v>1.99686467587207</v>
       </c>
-      <c r="O14" s="5">
+      <c r="O14" s="7">
         <f t="shared" si="2"/>
         <v>0.495057586521658</v>
       </c>
-      <c r="P14" s="5">
+      <c r="P14" s="7">
         <f t="shared" si="2"/>
         <v>2.14431144891796</v>
       </c>
-      <c r="Q14" s="5">
+      <c r="Q14" s="7">
         <f t="shared" si="2"/>
         <v>0.721324876500654</v>
       </c>
-      <c r="R14" s="5"/>
+      <c r="R14" s="7"/>
     </row>
     <row r="15" spans="2:17">
       <c r="B15">
@@ -5937,15 +6905,17 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:O21"/>
+  <dimension ref="A1:Q28"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="12.5363636363636" customWidth="1"/>
     <col min="2" max="13" width="8.54545454545454" customWidth="1"/>
-    <col min="14" max="14" width="12.0272727272727" customWidth="1"/>
+    <col min="14" max="14" width="13.9636363636364" customWidth="1"/>
+    <col min="15" max="15" width="12.2727272727273" customWidth="1"/>
+    <col min="17" max="17" width="9.54545454545454"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:14">
+    <row r="1" spans="2:15">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5985,8 +6955,11 @@
       <c r="N1" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="2" spans="1:15">
+      <c r="O1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16">
       <c r="A2">
         <v>2010</v>
       </c>
@@ -6026,15 +6999,19 @@
       <c r="M2">
         <v>-0.0207</v>
       </c>
-      <c r="N2" s="5">
+      <c r="N2" s="7">
         <f>(1+B2)*(1+C2)*(1+D2)*(1+E2)*(1+F2)*(1+G2)*(1+H2)*(1+I2)*(1+J2)*(1+K2)*(1+L2)*(1+M2)-1</f>
         <v>0.653614174322446</v>
       </c>
-      <c r="O2">
+      <c r="O2" s="6">
+        <f>N2</f>
+        <v>0.653614174322446</v>
+      </c>
+      <c r="P2">
         <v>2010</v>
       </c>
     </row>
-    <row r="3" spans="1:15">
+    <row r="3" spans="1:16">
       <c r="A3">
         <v>2011</v>
       </c>
@@ -6074,15 +7051,19 @@
       <c r="M3">
         <v>-0.1536</v>
       </c>
-      <c r="N3" s="5">
-        <f t="shared" ref="N2:N17" si="0">(1+B3)*(1+C3)*(1+D3)*(1+E3)*(1+F3)*(1+G3)*(1+H3)*(1+I3)*(1+J3)*(1+K3)*(1+L3)*(1+M3)-1</f>
+      <c r="N3" s="7">
+        <f>(1+B3)*(1+C3)*(1+D3)*(1+E3)*(1+F3)*(1+G3)*(1+H3)*(1+I3)*(1+J3)*(1+K3)*(1+L3)*(1+M3)-1</f>
         <v>-0.0855664203647523</v>
       </c>
-      <c r="O3">
+      <c r="O3" s="6">
+        <f t="shared" ref="O3:O17" si="0">N3</f>
+        <v>-0.0855664203647523</v>
+      </c>
+      <c r="P3">
         <v>2011</v>
       </c>
     </row>
-    <row r="4" spans="1:15">
+    <row r="4" spans="1:16">
       <c r="A4">
         <v>2012</v>
       </c>
@@ -6122,15 +7103,19 @@
       <c r="M4">
         <v>0.2375</v>
       </c>
-      <c r="N4" s="5">
+      <c r="N4" s="7">
+        <f t="shared" ref="N2:N17" si="1">(1+B4)*(1+C4)*(1+D4)*(1+E4)*(1+F4)*(1+G4)*(1+H4)*(1+I4)*(1+J4)*(1+K4)*(1+L4)*(1+M4)-1</f>
+        <v>0.0384573958480514</v>
+      </c>
+      <c r="O4" s="6">
         <f t="shared" si="0"/>
         <v>0.0384573958480514</v>
       </c>
-      <c r="O4">
+      <c r="P4">
         <v>2012</v>
       </c>
     </row>
-    <row r="5" spans="1:15">
+    <row r="5" spans="1:16">
       <c r="A5">
         <v>2013</v>
       </c>
@@ -6170,15 +7155,19 @@
       <c r="M5">
         <v>0.0207</v>
       </c>
-      <c r="N5" s="5">
+      <c r="N5" s="7">
+        <f t="shared" si="1"/>
+        <v>0.765405002524292</v>
+      </c>
+      <c r="O5" s="6">
         <f t="shared" si="0"/>
         <v>0.765405002524292</v>
       </c>
-      <c r="O5">
+      <c r="P5">
         <v>2013</v>
       </c>
     </row>
-    <row r="6" spans="1:15">
+    <row r="6" spans="1:16">
       <c r="A6">
         <v>2014</v>
       </c>
@@ -6218,15 +7207,19 @@
       <c r="M6">
         <v>-0.1353</v>
       </c>
-      <c r="N6" s="5">
+      <c r="N6" s="7">
+        <f t="shared" si="1"/>
+        <v>1.19935720490706</v>
+      </c>
+      <c r="O6" s="6">
         <f t="shared" si="0"/>
         <v>1.19935720490706</v>
       </c>
-      <c r="O6">
+      <c r="P6">
         <v>2014</v>
       </c>
     </row>
-    <row r="7" spans="1:15">
+    <row r="7" spans="1:16">
       <c r="A7">
         <v>2015</v>
       </c>
@@ -6266,15 +7259,19 @@
       <c r="M7">
         <v>0.2392</v>
       </c>
-      <c r="N7" s="5">
-        <f>(1+B7)*(1+C7)*(1+D7)*(1+E7)*(1+F7)*(1+G7)*(1+H7)*(1+I7)*(1+J7)*(1+K7)*(1+L7)*(1+M7)-1</f>
+      <c r="N7" s="7">
+        <f t="shared" si="1"/>
         <v>5.98281172803228</v>
       </c>
-      <c r="O7">
+      <c r="O7" s="6">
+        <f t="shared" si="0"/>
+        <v>5.98281172803228</v>
+      </c>
+      <c r="P7">
         <v>2015</v>
       </c>
     </row>
-    <row r="8" spans="1:15">
+    <row r="8" spans="1:16">
       <c r="A8">
         <v>2016</v>
       </c>
@@ -6314,15 +7311,19 @@
       <c r="M8">
         <v>0.12</v>
       </c>
-      <c r="N8" s="5">
+      <c r="N8" s="7">
+        <f t="shared" si="1"/>
+        <v>1.09694188883488</v>
+      </c>
+      <c r="O8" s="6">
         <f t="shared" si="0"/>
         <v>1.09694188883488</v>
       </c>
-      <c r="O8">
+      <c r="P8">
         <v>2016</v>
       </c>
     </row>
-    <row r="9" spans="1:15">
+    <row r="9" spans="1:16">
       <c r="A9">
         <v>2017</v>
       </c>
@@ -6362,15 +7363,19 @@
       <c r="M9">
         <v>-0.0392</v>
       </c>
-      <c r="N9" s="5">
+      <c r="N9" s="7">
+        <f t="shared" si="1"/>
+        <v>0.0775695328691113</v>
+      </c>
+      <c r="O9" s="6">
         <f t="shared" si="0"/>
         <v>0.0775695328691113</v>
       </c>
-      <c r="O9">
+      <c r="P9">
         <v>2017</v>
       </c>
     </row>
-    <row r="10" spans="1:15">
+    <row r="10" spans="1:16">
       <c r="A10">
         <v>2018</v>
       </c>
@@ -6410,15 +7415,19 @@
       <c r="M10">
         <v>-0.0448</v>
       </c>
-      <c r="N10" s="5">
+      <c r="N10" s="7">
+        <f t="shared" si="1"/>
+        <v>0.472825224873327</v>
+      </c>
+      <c r="O10" s="6">
         <f t="shared" si="0"/>
         <v>0.472825224873327</v>
       </c>
-      <c r="O10">
+      <c r="P10">
         <v>2018</v>
       </c>
     </row>
-    <row r="11" spans="1:15">
+    <row r="11" spans="1:16">
       <c r="A11">
         <v>2019</v>
       </c>
@@ -6458,15 +7467,19 @@
       <c r="M11">
         <v>0.1302</v>
       </c>
-      <c r="N11" s="5">
+      <c r="N11" s="7">
+        <f t="shared" si="1"/>
+        <v>0.745848408003567</v>
+      </c>
+      <c r="O11" s="6">
         <f t="shared" si="0"/>
         <v>0.745848408003567</v>
       </c>
-      <c r="O11">
+      <c r="P11">
         <v>2019</v>
       </c>
     </row>
-    <row r="12" spans="1:15">
+    <row r="12" spans="1:16">
       <c r="A12">
         <v>2020</v>
       </c>
@@ -6506,15 +7519,19 @@
       <c r="M12">
         <v>-0.112</v>
       </c>
-      <c r="N12" s="5">
+      <c r="N12" s="7">
+        <f t="shared" si="1"/>
+        <v>0.501877778017195</v>
+      </c>
+      <c r="O12" s="6">
         <f t="shared" si="0"/>
         <v>0.501877778017195</v>
       </c>
-      <c r="O12">
+      <c r="P12">
         <v>2020</v>
       </c>
     </row>
-    <row r="13" spans="1:15">
+    <row r="13" spans="1:16">
       <c r="A13">
         <v>2021</v>
       </c>
@@ -6554,15 +7571,19 @@
       <c r="M13">
         <v>0.1123</v>
       </c>
-      <c r="N13" s="5">
+      <c r="N13" s="7">
+        <f t="shared" si="1"/>
+        <v>0.660960857965097</v>
+      </c>
+      <c r="O13" s="6">
         <f t="shared" si="0"/>
         <v>0.660960857965097</v>
       </c>
-      <c r="O13">
+      <c r="P13">
         <v>2021</v>
       </c>
     </row>
-    <row r="14" spans="1:15">
+    <row r="14" spans="1:16">
       <c r="A14">
         <v>2022</v>
       </c>
@@ -6602,15 +7623,19 @@
       <c r="M14">
         <v>0.0431</v>
       </c>
-      <c r="N14" s="5">
+      <c r="N14" s="7">
+        <f t="shared" si="1"/>
+        <v>1.99686467587207</v>
+      </c>
+      <c r="O14" s="6">
         <f t="shared" si="0"/>
         <v>1.99686467587207</v>
       </c>
-      <c r="O14">
+      <c r="P14">
         <v>2022</v>
       </c>
     </row>
-    <row r="15" spans="1:15">
+    <row r="15" spans="1:16">
       <c r="A15">
         <v>2023</v>
       </c>
@@ -6650,15 +7675,19 @@
       <c r="M15">
         <v>-0.0024</v>
       </c>
-      <c r="N15" s="5">
+      <c r="N15" s="7">
+        <f t="shared" si="1"/>
+        <v>0.495057586521658</v>
+      </c>
+      <c r="O15" s="6">
         <f t="shared" si="0"/>
         <v>0.495057586521658</v>
       </c>
-      <c r="O15">
+      <c r="P15">
         <v>2023</v>
       </c>
     </row>
-    <row r="16" spans="1:15">
+    <row r="16" spans="1:16">
       <c r="A16">
         <v>2024</v>
       </c>
@@ -6698,15 +7727,19 @@
       <c r="M16">
         <v>0.0415</v>
       </c>
-      <c r="N16" s="5">
+      <c r="N16" s="7">
+        <f t="shared" si="1"/>
+        <v>2.14431144891796</v>
+      </c>
+      <c r="O16" s="6">
         <f t="shared" si="0"/>
         <v>2.14431144891796</v>
       </c>
-      <c r="O16">
+      <c r="P16">
         <v>2024</v>
       </c>
     </row>
-    <row r="17" spans="1:15">
+    <row r="17" spans="1:16">
       <c r="A17">
         <v>2025</v>
       </c>
@@ -6746,17 +7779,21 @@
       <c r="M17">
         <v>-0.0685</v>
       </c>
-      <c r="N17" s="5">
-        <f t="shared" si="0"/>
+      <c r="N17" s="7">
+        <f t="shared" si="1"/>
         <v>0.721324876500654</v>
       </c>
-      <c r="O17">
+      <c r="O17" s="6">
+        <f>N17</f>
+        <v>0.721324876500654</v>
+      </c>
+      <c r="P17">
         <v>2025</v>
       </c>
     </row>
-    <row r="18" ht="14.75" spans="1:14">
+    <row r="18" ht="14.75" spans="1:15">
       <c r="A18" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B18" s="2" cm="1">
         <f t="array" ref="B18">PRODUCT(B2:B17+1)-1</f>
@@ -6806,7 +7843,14 @@
         <f t="array" ref="M18">PRODUCT(M2:M17+1)-1</f>
         <v>0.299575907581825</v>
       </c>
-      <c r="N18" s="5"/>
+      <c r="N18" s="8" cm="1">
+        <f t="array" ref="N18">PRODUCT(N2:N17+1)-1</f>
+        <v>14962.8167474189</v>
+      </c>
+      <c r="O18" s="9">
+        <f>N18</f>
+        <v>14962.8167474189</v>
+      </c>
     </row>
     <row r="19" spans="2:13">
       <c r="B19" s="1" t="s">
@@ -6848,112 +7892,303 @@
     </row>
     <row r="20" spans="1:13">
       <c r="A20" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B20">
         <f>COUNTIF(B2:B17,"&lt;0")</f>
         <v>5</v>
       </c>
       <c r="C20">
-        <f t="shared" ref="B20:M20" si="1">COUNTIF(C2:C17,"&lt;0")</f>
+        <f t="shared" ref="B20:M20" si="2">COUNTIF(C2:C17,"&lt;0")</f>
         <v>0</v>
       </c>
       <c r="D20">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>5</v>
       </c>
       <c r="E20">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>4</v>
       </c>
       <c r="F20">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>5</v>
       </c>
       <c r="G20">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>5</v>
       </c>
       <c r="H20">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>5</v>
       </c>
       <c r="I20">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>5</v>
       </c>
       <c r="J20">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>4</v>
       </c>
       <c r="K20">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>4</v>
       </c>
       <c r="L20">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>4</v>
       </c>
       <c r="M20">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>8</v>
       </c>
     </row>
     <row r="21" spans="1:13">
       <c r="A21" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B21">
         <f>COUNTIF(B2:B17,"&gt;0.1")</f>
         <v>0</v>
       </c>
       <c r="C21">
-        <f t="shared" ref="C21:M21" si="2">COUNTIF(C2:C17,"&gt;0.1")</f>
+        <f t="shared" ref="C21:M21" si="3">COUNTIF(C2:C17,"&gt;0.1")</f>
         <v>5</v>
       </c>
       <c r="D21">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>6</v>
       </c>
       <c r="E21">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="F21">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>3</v>
       </c>
       <c r="G21">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>4</v>
       </c>
       <c r="H21">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>8</v>
       </c>
       <c r="I21">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>8</v>
       </c>
       <c r="J21">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>4</v>
       </c>
       <c r="K21">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>3</v>
       </c>
       <c r="L21">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>7</v>
       </c>
       <c r="M21">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>5</v>
       </c>
     </row>
+    <row r="26" spans="1:17">
+      <c r="A26" t="s">
+        <v>17</v>
+      </c>
+      <c r="B26">
+        <v>1</v>
+      </c>
+      <c r="C26">
+        <v>2</v>
+      </c>
+      <c r="D26">
+        <v>3</v>
+      </c>
+      <c r="E26">
+        <v>4</v>
+      </c>
+      <c r="F26">
+        <v>5</v>
+      </c>
+      <c r="G26">
+        <v>6</v>
+      </c>
+      <c r="H26">
+        <v>7</v>
+      </c>
+      <c r="I26">
+        <v>8</v>
+      </c>
+      <c r="J26">
+        <v>9</v>
+      </c>
+      <c r="K26">
+        <v>10</v>
+      </c>
+      <c r="L26">
+        <v>11</v>
+      </c>
+      <c r="M26">
+        <v>12</v>
+      </c>
+      <c r="N26">
+        <v>13</v>
+      </c>
+      <c r="O26">
+        <v>14</v>
+      </c>
+      <c r="P26">
+        <v>15</v>
+      </c>
+      <c r="Q26">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="27" spans="1:17">
+      <c r="A27" t="s">
+        <v>18</v>
+      </c>
+      <c r="B27" s="5" cm="1">
+        <f ca="1" t="array" ref="B27">PRODUCT(INDEX($N:$N,ROW($N$18)-B26):$N$17+1)-1</f>
+        <v>0.721324876500654</v>
+      </c>
+      <c r="C27" s="5" cm="1">
+        <f ca="1" t="array" ref="C27">PRODUCT(INDEX($N:$N,ROW($N$18)-C26):$N$17+1)-1</f>
+        <v>4.4123815164883</v>
+      </c>
+      <c r="D27" s="5" cm="1">
+        <f ca="1" t="array" ref="D27">PRODUCT(INDEX($N:$N,ROW($N$18)-D26):$N$17+1)-1</f>
+        <v>7.09182204737543</v>
+      </c>
+      <c r="E27" s="5" cm="1">
+        <f ca="1" t="array" ref="E27">PRODUCT(INDEX($N:$N,ROW($N$18)-E26):$N$17+1)-1</f>
+        <v>23.2500956572222</v>
+      </c>
+      <c r="F27" s="5" cm="1">
+        <f ca="1" t="array" ref="F27">PRODUCT(INDEX($N:$N,ROW($N$18)-F26):$N$17+1)-1</f>
+        <v>39.2784596885555</v>
+      </c>
+      <c r="G27" s="5" cm="1">
+        <f ca="1" t="array" ref="G27">PRODUCT(INDEX($N:$N,ROW($N$18)-G26):$N$17+1)-1</f>
+        <v>59.4933235390029</v>
+      </c>
+      <c r="H27" s="5" cm="1">
+        <f ca="1" t="array" ref="H27">PRODUCT(INDEX($N:$N,ROW($N$18)-H26):$N$17+1)-1</f>
+        <v>104.612172595413</v>
+      </c>
+      <c r="I27" s="5" cm="1">
+        <f ca="1" t="array" ref="I27">PRODUCT(INDEX($N:$N,ROW($N$18)-I26):$N$17+1)-1</f>
+        <v>154.5482718522</v>
+      </c>
+      <c r="J27" s="5" cm="1">
+        <f ca="1" t="array" ref="J27">PRODUCT(INDEX($N:$N,ROW($N$18)-J26):$N$17+1)-1</f>
+        <v>166.614078638372</v>
+      </c>
+      <c r="K27" s="5" cm="1">
+        <f ca="1" t="array" ref="K27">PRODUCT(INDEX($N:$N,ROW($N$18)-K26):$N$17+1)-1</f>
+        <v>350.476982655267</v>
+      </c>
+      <c r="L27" s="5" cm="1">
+        <f ca="1" t="array" ref="L27">PRODUCT(INDEX($N:$N,ROW($N$18)-L26):$N$17+1)-1</f>
+        <v>2453.29759661859</v>
+      </c>
+      <c r="M27" s="5" cm="1">
+        <f ca="1" t="array" ref="M27">PRODUCT(INDEX($N:$N,ROW($N$18)-M26):$N$17+1)-1</f>
+        <v>5396.87710210919</v>
+      </c>
+      <c r="N27" s="5" cm="1">
+        <f ca="1" t="array" ref="N27">PRODUCT(INDEX($N:$N,ROW($N$18)-N26):$N$17+1)-1</f>
+        <v>9528.43923907489</v>
+      </c>
+      <c r="O27" s="5" cm="1">
+        <f ca="1" t="array" ref="O27">PRODUCT(INDEX($N:$N,ROW($N$18)-O26):$N$17+1)-1</f>
+        <v>9894.91665610194</v>
+      </c>
+      <c r="P27" s="5" cm="1">
+        <f ca="1" t="array" ref="P27">PRODUCT(INDEX($N:$N,ROW($N$18)-P26):$N$17+1)-1</f>
+        <v>9048.15849161137</v>
+      </c>
+      <c r="Q27" s="5" cm="1">
+        <f ca="1" t="array" ref="Q27">PRODUCT(INDEX($N:$N,ROW($N$18)-Q26):$N$17+1)-1</f>
+        <v>14962.8167474189</v>
+      </c>
+    </row>
+    <row r="28" spans="1:17">
+      <c r="A28" t="s">
+        <v>19</v>
+      </c>
+      <c r="B28" s="6">
+        <f ca="1">POWER(B27+1,1/B26)-1</f>
+        <v>0.721324876500654</v>
+      </c>
+      <c r="C28" s="6">
+        <f ca="1">POWER(C27+1,1/C26)-1</f>
+        <v>1.32645256054971</v>
+      </c>
+      <c r="D28" s="6">
+        <f ca="1" t="shared" ref="D28:Q28" si="4">POWER(D27+1,1/D26)-1</f>
+        <v>1.00762274723281</v>
+      </c>
+      <c r="E28" s="6">
+        <f ca="1" t="shared" si="4"/>
+        <v>1.21910761645483</v>
+      </c>
+      <c r="F28" s="6">
+        <f ca="1" t="shared" si="4"/>
+        <v>1.09418271565768</v>
+      </c>
+      <c r="G28" s="6">
+        <f ca="1" t="shared" si="4"/>
+        <v>0.98130456845761</v>
+      </c>
+      <c r="H28" s="6">
+        <f ca="1" t="shared" si="4"/>
+        <v>0.945817014845787</v>
+      </c>
+      <c r="I28" s="6">
+        <f ca="1" t="shared" si="4"/>
+        <v>0.879243898263695</v>
+      </c>
+      <c r="J28" s="6">
+        <f ca="1" t="shared" si="4"/>
+        <v>0.766630037947978</v>
+      </c>
+      <c r="K28" s="6">
+        <f ca="1" t="shared" si="4"/>
+        <v>0.797172187425214</v>
+      </c>
+      <c r="L28" s="6">
+        <f ca="1" t="shared" si="4"/>
+        <v>1.03317706479</v>
+      </c>
+      <c r="M28" s="6">
+        <f ca="1" t="shared" si="4"/>
+        <v>1.04653220237664</v>
+      </c>
+      <c r="N28" s="6">
+        <f ca="1" t="shared" si="4"/>
+        <v>1.02340166712687</v>
+      </c>
+      <c r="O28" s="6">
+        <f ca="1" t="shared" si="4"/>
+        <v>0.929255363746949</v>
+      </c>
+      <c r="P28" s="6">
+        <f ca="1" t="shared" si="4"/>
+        <v>0.835582377705406</v>
+      </c>
+      <c r="Q28" s="6">
+        <f ca="1" t="shared" si="4"/>
+        <v>0.823644364105827</v>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="B18:M18">
+  <conditionalFormatting sqref="B18:N18">
     <cfRule type="expression" dxfId="0" priority="3">
       <formula>B18&gt;2</formula>
     </cfRule>
@@ -6961,17 +8196,17 @@
       <formula>B18&lt;2</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N18">
-    <cfRule type="expression" dxfId="4" priority="1">
-      <formula>N2&gt;1.5</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B2:M18">
+  <conditionalFormatting sqref="B2:M18 N18">
     <cfRule type="expression" dxfId="3" priority="6">
       <formula>B2&gt;0.1</formula>
     </cfRule>
     <cfRule type="expression" dxfId="2" priority="5">
       <formula>B2&lt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N2:O17 O18">
+    <cfRule type="expression" dxfId="4" priority="1">
+      <formula>N2&gt;1.5</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/JoinQuant/profit.xlsx
+++ b/JoinQuant/profit.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27950" windowHeight="12280" activeTab="2"/>
+    <workbookView windowWidth="24750" windowHeight="10480" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -125,7 +125,7 @@
     <numFmt numFmtId="176" formatCode="0.0000_ "/>
     <numFmt numFmtId="177" formatCode="0.000_ "/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -138,6 +138,14 @@
       <color rgb="FF222222"/>
       <name val="Verdana"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
@@ -306,6 +314,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -319,12 +333,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -521,7 +529,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="11">
+  <borders count="14">
     <border>
       <left/>
       <right/>
@@ -536,6 +544,43 @@
         <color rgb="FFE8ECF0"/>
       </top>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color theme="9" tint="0.4"/>
+      </left>
+      <right/>
+      <top style="thick">
+        <color theme="9" tint="0.4"/>
+      </top>
+      <bottom style="thick">
+        <color theme="9" tint="0.4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thick">
+        <color theme="9" tint="0.4"/>
+      </top>
+      <bottom style="thick">
+        <color theme="9" tint="0.4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thick">
+        <color theme="9" tint="0.4"/>
+      </right>
+      <top style="thick">
+        <color theme="9" tint="0.4"/>
+      </top>
+      <bottom style="thick">
+        <color theme="9" tint="0.4"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -667,16 +712,13 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -685,133 +727,145 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="10" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="10" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="11" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="11" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="17" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+    <xf numFmtId="176" fontId="0" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
@@ -822,25 +876,25 @@
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="2" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
+    <xf numFmtId="176" fontId="3" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="10" fontId="2" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1">
+    <xf numFmtId="10" fontId="3" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="17" fontId="3" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="17" fontId="4" fillId="7" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1433,7 +1487,7 @@
           </c:dLbls>
           <c:val>
             <c:numRef>
-              <c:f>Sheet3!$B$28:$Q$28</c:f>
+              <c:f>Sheet3!$B$29:$Q$29</c:f>
               <c:numCache>
                 <c:formatCode>0.00%</c:formatCode>
                 <c:ptCount val="16"/>
@@ -1441,49 +1495,49 @@
                   <c:v>0.721324876500654</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.32645256054971</c:v>
+                  <c:v>0.3119927120608</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1.00762274723281</c:v>
+                  <c:v>0.75575049992058</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1.21910761645483</c:v>
+                  <c:v>0.686597999377588</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1.09418271565768</c:v>
+                  <c:v>0.892093924562005</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.98130456845761</c:v>
+                  <c:v>0.851450657807452</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.945817014845787</c:v>
+                  <c:v>0.796923693198646</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.879243898263695</c:v>
+                  <c:v>0.790458450087202</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.766630037947978</c:v>
+                  <c:v>0.752026120711281</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.797172187425214</c:v>
+                  <c:v>0.668902823492491</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1.03317706479</c:v>
+                  <c:v>0.703904193500895</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1.04653220237664</c:v>
+                  <c:v>0.916434299972187</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1.02340166712687</c:v>
+                  <c:v>0.936841474732953</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.929255363746949</c:v>
+                  <c:v>0.924062149207631</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0.835582377705406</c:v>
+                  <c:v>0.846561324809914</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>0.823644364105827</c:v>
+                  <c:v>0.767209396894281</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1648,6 +1702,11 @@
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
     <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext uri="{0b15fc19-7d7d-44ad-8c2d-2c3a37ce22c3}">
+        <chartProps xmlns="https://web.wps.cn/et/2018/main" chartId="{e95191c0-124a-46c9-81bf-d026fe1b2a65}"/>
+      </c:ext>
+    </c:extLst>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -2788,7 +2847,7 @@
     <xdr:to>
       <xdr:col>24</xdr:col>
       <xdr:colOff>69215</xdr:colOff>
-      <xdr:row>17</xdr:row>
+      <xdr:row>18</xdr:row>
       <xdr:rowOff>107950</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
@@ -2797,8 +2856,8 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="10772140" y="384175"/>
-        <a:ext cx="4864100" cy="2746375"/>
+        <a:off x="10638155" y="384175"/>
+        <a:ext cx="4864100" cy="2933700"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -2812,13 +2871,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>41910</xdr:colOff>
-      <xdr:row>28</xdr:row>
+      <xdr:row>29</xdr:row>
       <xdr:rowOff>31115</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
       <xdr:colOff>92710</xdr:colOff>
-      <xdr:row>43</xdr:row>
+      <xdr:row>44</xdr:row>
       <xdr:rowOff>110490</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
@@ -2827,7 +2886,7 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="917575" y="5019040"/>
+        <a:off x="917575" y="5333365"/>
         <a:ext cx="4826000" cy="2746375"/>
       </xdr:xfrm>
       <a:graphic>
@@ -3099,10 +3158,10 @@
   <sheetData>
     <row r="1" ht="14.75"/>
     <row r="2" ht="14.75" spans="1:22">
-      <c r="A2" s="1">
+      <c r="A2" s="2">
         <v>40179</v>
       </c>
-      <c r="B2" s="12">
+      <c r="B2" s="15">
         <v>0</v>
       </c>
       <c r="C2">
@@ -3179,10 +3238,10 @@
       </c>
     </row>
     <row r="3" ht="14.75" spans="1:22">
-      <c r="A3" s="1">
+      <c r="A3" s="2">
         <v>40210</v>
       </c>
-      <c r="B3" s="12">
+      <c r="B3" s="15">
         <v>0.0651</v>
       </c>
       <c r="C3">
@@ -3259,10 +3318,10 @@
       </c>
     </row>
     <row r="4" ht="14.75" spans="1:22">
-      <c r="A4" s="1">
+      <c r="A4" s="2">
         <v>40238</v>
       </c>
-      <c r="B4" s="12">
+      <c r="B4" s="15">
         <v>0.0813</v>
       </c>
       <c r="C4">
@@ -3339,10 +3398,10 @@
       </c>
     </row>
     <row r="5" ht="14.75" spans="1:22">
-      <c r="A5" s="1">
+      <c r="A5" s="2">
         <v>40269</v>
       </c>
-      <c r="B5" s="12">
+      <c r="B5" s="15">
         <v>0.0008</v>
       </c>
       <c r="C5">
@@ -3419,10 +3478,10 @@
       </c>
     </row>
     <row r="6" ht="14.75" spans="1:22">
-      <c r="A6" s="1">
+      <c r="A6" s="2">
         <v>40299</v>
       </c>
-      <c r="B6" s="12">
+      <c r="B6" s="15">
         <v>-0.0608</v>
       </c>
       <c r="C6">
@@ -3499,10 +3558,10 @@
       </c>
     </row>
     <row r="7" ht="14.75" spans="1:22">
-      <c r="A7" s="1">
+      <c r="A7" s="2">
         <v>40330</v>
       </c>
-      <c r="B7" s="12">
+      <c r="B7" s="15">
         <v>-0.073</v>
       </c>
       <c r="C7">
@@ -3579,10 +3638,10 @@
       </c>
     </row>
     <row r="8" ht="14.75" spans="1:22">
-      <c r="A8" s="1">
+      <c r="A8" s="2">
         <v>40360</v>
       </c>
-      <c r="B8" s="12">
+      <c r="B8" s="15">
         <v>0.1977</v>
       </c>
       <c r="C8">
@@ -3659,10 +3718,10 @@
       </c>
     </row>
     <row r="9" ht="14.75" spans="1:22">
-      <c r="A9" s="1">
+      <c r="A9" s="2">
         <v>40391</v>
       </c>
-      <c r="B9" s="12">
+      <c r="B9" s="15">
         <v>0.1303</v>
       </c>
       <c r="C9">
@@ -3739,10 +3798,10 @@
       </c>
     </row>
     <row r="10" ht="14.75" spans="1:22">
-      <c r="A10" s="1">
+      <c r="A10" s="2">
         <v>40422</v>
       </c>
-      <c r="B10" s="12">
+      <c r="B10" s="15">
         <v>0.11</v>
       </c>
       <c r="C10">
@@ -3819,10 +3878,10 @@
       </c>
     </row>
     <row r="11" ht="14.75" spans="1:22">
-      <c r="A11" s="1">
+      <c r="A11" s="2">
         <v>40452</v>
       </c>
-      <c r="B11" s="12">
+      <c r="B11" s="15">
         <v>0.1099</v>
       </c>
       <c r="C11">
@@ -3899,10 +3958,10 @@
       </c>
     </row>
     <row r="12" ht="14.75" spans="1:22">
-      <c r="A12" s="1">
+      <c r="A12" s="2">
         <v>40483</v>
       </c>
-      <c r="B12" s="12">
+      <c r="B12" s="15">
         <v>0.0089</v>
       </c>
       <c r="C12">
@@ -3979,10 +4038,10 @@
       </c>
     </row>
     <row r="13" ht="14.75" spans="1:22">
-      <c r="A13" s="1">
+      <c r="A13" s="2">
         <v>40513</v>
       </c>
-      <c r="B13" s="12">
+      <c r="B13" s="15">
         <v>-0.0207</v>
       </c>
       <c r="C13">
@@ -4059,1804 +4118,1804 @@
       </c>
     </row>
     <row r="14" ht="14.75" spans="1:4">
-      <c r="A14" s="1">
+      <c r="A14" s="2">
         <v>40544</v>
       </c>
-      <c r="B14" s="12">
+      <c r="B14" s="15">
         <v>-0.0016</v>
       </c>
-      <c r="C14" s="12"/>
-      <c r="D14" s="12"/>
+      <c r="C14" s="15"/>
+      <c r="D14" s="15"/>
     </row>
     <row r="15" ht="14.75" spans="1:4">
-      <c r="A15" s="1">
+      <c r="A15" s="2">
         <v>40575</v>
       </c>
-      <c r="B15" s="12">
+      <c r="B15" s="15">
         <v>0.1456</v>
       </c>
-      <c r="C15" s="12"/>
-      <c r="D15" s="12"/>
+      <c r="C15" s="15"/>
+      <c r="D15" s="15"/>
     </row>
     <row r="16" ht="14.75" spans="1:4">
-      <c r="A16" s="1">
+      <c r="A16" s="2">
         <v>40603</v>
       </c>
-      <c r="B16" s="12">
+      <c r="B16" s="15">
         <v>0.0526</v>
       </c>
-      <c r="C16" s="12"/>
-      <c r="D16" s="12"/>
+      <c r="C16" s="15"/>
+      <c r="D16" s="15"/>
     </row>
     <row r="17" ht="14.75" spans="1:4">
-      <c r="A17" s="1">
+      <c r="A17" s="2">
         <v>40634</v>
       </c>
-      <c r="B17" s="12">
+      <c r="B17" s="15">
         <v>-0.0008</v>
       </c>
-      <c r="C17" s="12"/>
-      <c r="D17" s="12"/>
+      <c r="C17" s="15"/>
+      <c r="D17" s="15"/>
     </row>
     <row r="18" ht="14.75" spans="1:4">
-      <c r="A18" s="1">
+      <c r="A18" s="2">
         <v>40664</v>
       </c>
-      <c r="B18" s="12">
+      <c r="B18" s="15">
         <v>-0.0644</v>
       </c>
-      <c r="C18" s="12"/>
-      <c r="D18" s="12"/>
+      <c r="C18" s="15"/>
+      <c r="D18" s="15"/>
     </row>
     <row r="19" ht="14.75" spans="1:4">
-      <c r="A19" s="1">
+      <c r="A19" s="2">
         <v>40695</v>
       </c>
-      <c r="B19" s="12">
+      <c r="B19" s="15">
         <v>0.0828</v>
       </c>
-      <c r="C19" s="12"/>
-      <c r="D19" s="12"/>
+      <c r="C19" s="15"/>
+      <c r="D19" s="15"/>
     </row>
     <row r="20" ht="14.75" spans="1:4">
-      <c r="A20" s="1">
+      <c r="A20" s="2">
         <v>40725</v>
       </c>
-      <c r="B20" s="12">
+      <c r="B20" s="15">
         <v>-0.0211</v>
       </c>
-      <c r="C20" s="12"/>
-      <c r="D20" s="12"/>
+      <c r="C20" s="15"/>
+      <c r="D20" s="15"/>
     </row>
     <row r="21" ht="14.75" spans="1:4">
-      <c r="A21" s="1">
+      <c r="A21" s="2">
         <v>40756</v>
       </c>
-      <c r="B21" s="12">
+      <c r="B21" s="15">
         <v>-0.0006</v>
       </c>
-      <c r="C21" s="12"/>
-      <c r="D21" s="12"/>
+      <c r="C21" s="15"/>
+      <c r="D21" s="15"/>
     </row>
     <row r="22" ht="14.75" spans="1:4">
-      <c r="A22" s="1">
+      <c r="A22" s="2">
         <v>40787</v>
       </c>
-      <c r="B22" s="12">
+      <c r="B22" s="15">
         <v>-0.0886</v>
       </c>
-      <c r="C22" s="12"/>
-      <c r="D22" s="12"/>
+      <c r="C22" s="15"/>
+      <c r="D22" s="15"/>
     </row>
     <row r="23" ht="14.75" spans="1:4">
-      <c r="A23" s="1">
+      <c r="A23" s="2">
         <v>40817</v>
       </c>
-      <c r="B23" s="12">
+      <c r="B23" s="15">
         <v>0.0186</v>
       </c>
-      <c r="C23" s="12"/>
-      <c r="D23" s="12"/>
+      <c r="C23" s="15"/>
+      <c r="D23" s="15"/>
     </row>
     <row r="24" ht="14.75" spans="1:4">
-      <c r="A24" s="1">
+      <c r="A24" s="2">
         <v>40848</v>
       </c>
-      <c r="B24" s="12">
+      <c r="B24" s="15">
         <v>-0.0239</v>
       </c>
-      <c r="C24" s="12"/>
-      <c r="D24" s="12"/>
+      <c r="C24" s="15"/>
+      <c r="D24" s="15"/>
     </row>
     <row r="25" ht="14.75" spans="1:4">
-      <c r="A25" s="1">
+      <c r="A25" s="2">
         <v>40878</v>
       </c>
-      <c r="B25" s="12">
+      <c r="B25" s="15">
         <v>-0.1536</v>
       </c>
-      <c r="C25" s="12"/>
-      <c r="D25" s="12"/>
+      <c r="C25" s="15"/>
+      <c r="D25" s="15"/>
     </row>
     <row r="26" ht="14.75" spans="1:4">
-      <c r="A26" s="1">
+      <c r="A26" s="2">
         <v>40909</v>
       </c>
-      <c r="B26" s="12">
+      <c r="B26" s="15">
         <v>0.0301</v>
       </c>
-      <c r="C26" s="12"/>
-      <c r="D26" s="12"/>
+      <c r="C26" s="15"/>
+      <c r="D26" s="15"/>
     </row>
     <row r="27" ht="14.75" spans="1:4">
-      <c r="A27" s="1">
+      <c r="A27" s="2">
         <v>40940</v>
       </c>
-      <c r="B27" s="12">
+      <c r="B27" s="15">
         <v>0.0984</v>
       </c>
-      <c r="C27" s="12"/>
-      <c r="D27" s="12"/>
+      <c r="C27" s="15"/>
+      <c r="D27" s="15"/>
     </row>
     <row r="28" ht="14.75" spans="1:4">
-      <c r="A28" s="1">
+      <c r="A28" s="2">
         <v>40969</v>
       </c>
-      <c r="B28" s="12">
+      <c r="B28" s="15">
         <v>-0.065</v>
       </c>
-      <c r="C28" s="12"/>
-      <c r="D28" s="12"/>
+      <c r="C28" s="15"/>
+      <c r="D28" s="15"/>
     </row>
     <row r="29" ht="14.75" spans="1:4">
-      <c r="A29" s="1">
+      <c r="A29" s="2">
         <v>41000</v>
       </c>
-      <c r="B29" s="12">
+      <c r="B29" s="15">
         <v>0.0104</v>
       </c>
-      <c r="C29" s="12"/>
-      <c r="D29" s="12"/>
+      <c r="C29" s="15"/>
+      <c r="D29" s="15"/>
     </row>
     <row r="30" ht="14.75" spans="1:4">
-      <c r="A30" s="1">
+      <c r="A30" s="2">
         <v>41030</v>
       </c>
-      <c r="B30" s="12">
+      <c r="B30" s="15">
         <v>0.0008</v>
       </c>
-      <c r="C30" s="12"/>
-      <c r="D30" s="12"/>
+      <c r="C30" s="15"/>
+      <c r="D30" s="15"/>
     </row>
     <row r="31" ht="14.75" spans="1:4">
-      <c r="A31" s="1">
+      <c r="A31" s="2">
         <v>41061</v>
       </c>
-      <c r="B31" s="12">
+      <c r="B31" s="15">
         <v>-0.0436</v>
       </c>
-      <c r="C31" s="12"/>
-      <c r="D31" s="12"/>
+      <c r="C31" s="15"/>
+      <c r="D31" s="15"/>
     </row>
     <row r="32" ht="14.75" spans="1:4">
-      <c r="A32" s="1">
+      <c r="A32" s="2">
         <v>41091</v>
       </c>
-      <c r="B32" s="12">
+      <c r="B32" s="15">
         <v>-0.1551</v>
       </c>
-      <c r="C32" s="12"/>
-      <c r="D32" s="12"/>
+      <c r="C32" s="15"/>
+      <c r="D32" s="15"/>
     </row>
     <row r="33" ht="14.75" spans="1:4">
-      <c r="A33" s="1">
+      <c r="A33" s="2">
         <v>41122</v>
       </c>
-      <c r="B33" s="12">
+      <c r="B33" s="15">
         <v>0.0543</v>
       </c>
-      <c r="C33" s="12"/>
-      <c r="D33" s="12"/>
+      <c r="C33" s="15"/>
+      <c r="D33" s="15"/>
     </row>
     <row r="34" ht="14.75" spans="1:4">
-      <c r="A34" s="1">
+      <c r="A34" s="2">
         <v>41153</v>
       </c>
-      <c r="B34" s="12">
+      <c r="B34" s="15">
         <v>0.019</v>
       </c>
-      <c r="C34" s="12"/>
-      <c r="D34" s="12"/>
+      <c r="C34" s="15"/>
+      <c r="D34" s="15"/>
     </row>
     <row r="35" ht="14.75" spans="1:4">
-      <c r="A35" s="1">
+      <c r="A35" s="2">
         <v>41183</v>
       </c>
-      <c r="B35" s="12">
+      <c r="B35" s="15">
         <v>0.0012</v>
       </c>
-      <c r="C35" s="12"/>
-      <c r="D35" s="12"/>
+      <c r="C35" s="15"/>
+      <c r="D35" s="15"/>
     </row>
     <row r="36" ht="14.75" spans="1:4">
-      <c r="A36" s="1">
+      <c r="A36" s="2">
         <v>41214</v>
       </c>
-      <c r="B36" s="12">
+      <c r="B36" s="15">
         <v>-0.0975</v>
       </c>
-      <c r="C36" s="12"/>
-      <c r="D36" s="12"/>
+      <c r="C36" s="15"/>
+      <c r="D36" s="15"/>
     </row>
     <row r="37" ht="14.75" spans="1:4">
-      <c r="A37" s="1">
+      <c r="A37" s="2">
         <v>41244</v>
       </c>
-      <c r="B37" s="12">
+      <c r="B37" s="15">
         <v>0.2375</v>
       </c>
-      <c r="C37" s="12"/>
-      <c r="D37" s="12"/>
+      <c r="C37" s="15"/>
+      <c r="D37" s="15"/>
     </row>
     <row r="38" ht="14.75" spans="1:4">
-      <c r="A38" s="1">
+      <c r="A38" s="2">
         <v>41275</v>
       </c>
-      <c r="B38" s="12">
+      <c r="B38" s="15">
         <v>0.0057</v>
       </c>
-      <c r="C38" s="12"/>
-      <c r="D38" s="12"/>
+      <c r="C38" s="15"/>
+      <c r="D38" s="15"/>
     </row>
     <row r="39" ht="14.75" spans="1:4">
-      <c r="A39" s="1">
+      <c r="A39" s="2">
         <v>41306</v>
       </c>
-      <c r="B39" s="12">
+      <c r="B39" s="15">
         <v>0.0547</v>
       </c>
-      <c r="C39" s="12"/>
-      <c r="D39" s="12"/>
+      <c r="C39" s="15"/>
+      <c r="D39" s="15"/>
     </row>
     <row r="40" ht="14.75" spans="1:4">
-      <c r="A40" s="1">
+      <c r="A40" s="2">
         <v>41334</v>
       </c>
-      <c r="B40" s="12">
+      <c r="B40" s="15">
         <v>-0.0189</v>
       </c>
-      <c r="C40" s="12"/>
-      <c r="D40" s="12"/>
+      <c r="C40" s="15"/>
+      <c r="D40" s="15"/>
     </row>
     <row r="41" ht="14.75" spans="1:4">
-      <c r="A41" s="1">
+      <c r="A41" s="2">
         <v>41365</v>
       </c>
-      <c r="B41" s="12">
+      <c r="B41" s="15">
         <v>-0.0003</v>
       </c>
-      <c r="C41" s="12"/>
-      <c r="D41" s="12"/>
+      <c r="C41" s="15"/>
+      <c r="D41" s="15"/>
     </row>
     <row r="42" ht="14.75" spans="1:4">
-      <c r="A42" s="1">
+      <c r="A42" s="2">
         <v>41395</v>
       </c>
-      <c r="B42" s="12">
+      <c r="B42" s="15">
         <v>0.1792</v>
       </c>
-      <c r="C42" s="12"/>
-      <c r="D42" s="12"/>
+      <c r="C42" s="15"/>
+      <c r="D42" s="15"/>
     </row>
     <row r="43" ht="14.75" spans="1:4">
-      <c r="A43" s="1">
+      <c r="A43" s="2">
         <v>41426</v>
       </c>
-      <c r="B43" s="12">
+      <c r="B43" s="15">
         <v>-0.1098</v>
       </c>
-      <c r="C43" s="12"/>
-      <c r="D43" s="12"/>
+      <c r="C43" s="15"/>
+      <c r="D43" s="15"/>
     </row>
     <row r="44" ht="14.75" spans="1:4">
-      <c r="A44" s="1">
+      <c r="A44" s="2">
         <v>41456</v>
       </c>
-      <c r="B44" s="12">
+      <c r="B44" s="15">
         <v>0.1573</v>
       </c>
-      <c r="C44" s="12"/>
-      <c r="D44" s="12"/>
+      <c r="C44" s="15"/>
+      <c r="D44" s="15"/>
     </row>
     <row r="45" ht="14.75" spans="1:4">
-      <c r="A45" s="1">
+      <c r="A45" s="2">
         <v>41487</v>
       </c>
-      <c r="B45" s="12">
+      <c r="B45" s="15">
         <v>0.1024</v>
       </c>
-      <c r="C45" s="12"/>
-      <c r="D45" s="12"/>
+      <c r="C45" s="15"/>
+      <c r="D45" s="15"/>
     </row>
     <row r="46" ht="14.75" spans="1:4">
-      <c r="A46" s="1">
+      <c r="A46" s="2">
         <v>41518</v>
       </c>
-      <c r="B46" s="12">
+      <c r="B46" s="15">
         <v>0.0868</v>
       </c>
-      <c r="C46" s="12"/>
-      <c r="D46" s="12"/>
+      <c r="C46" s="15"/>
+      <c r="D46" s="15"/>
     </row>
     <row r="47" ht="14.75" spans="1:4">
-      <c r="A47" s="1">
+      <c r="A47" s="2">
         <v>41548</v>
       </c>
-      <c r="B47" s="12">
+      <c r="B47" s="15">
         <v>-0.0176</v>
       </c>
-      <c r="C47" s="12"/>
-      <c r="D47" s="12"/>
+      <c r="C47" s="15"/>
+      <c r="D47" s="15"/>
     </row>
     <row r="48" ht="14.75" spans="1:4">
-      <c r="A48" s="1">
+      <c r="A48" s="2">
         <v>41579</v>
       </c>
-      <c r="B48" s="12">
+      <c r="B48" s="15">
         <v>0.1627</v>
       </c>
-      <c r="C48" s="12"/>
-      <c r="D48" s="12"/>
+      <c r="C48" s="15"/>
+      <c r="D48" s="15"/>
     </row>
     <row r="49" ht="14.75" spans="1:4">
-      <c r="A49" s="1">
+      <c r="A49" s="2">
         <v>41609</v>
       </c>
-      <c r="B49" s="12">
+      <c r="B49" s="15">
         <v>0.0207</v>
       </c>
-      <c r="C49" s="12"/>
-      <c r="D49" s="12"/>
+      <c r="C49" s="15"/>
+      <c r="D49" s="15"/>
     </row>
     <row r="50" ht="14.75" spans="1:4">
-      <c r="A50" s="1">
+      <c r="A50" s="2">
         <v>41640</v>
       </c>
-      <c r="B50" s="12">
+      <c r="B50" s="15">
         <v>-0.0057</v>
       </c>
-      <c r="C50" s="12"/>
-      <c r="D50" s="12"/>
+      <c r="C50" s="15"/>
+      <c r="D50" s="15"/>
     </row>
     <row r="51" ht="14.75" spans="1:4">
-      <c r="A51" s="1">
+      <c r="A51" s="2">
         <v>41671</v>
       </c>
-      <c r="B51" s="12">
+      <c r="B51" s="15">
         <v>0.0822</v>
       </c>
-      <c r="C51" s="12"/>
-      <c r="D51" s="12"/>
+      <c r="C51" s="15"/>
+      <c r="D51" s="15"/>
     </row>
     <row r="52" ht="14.75" spans="1:4">
-      <c r="A52" s="1">
+      <c r="A52" s="2">
         <v>41699</v>
       </c>
-      <c r="B52" s="12">
+      <c r="B52" s="15">
         <v>0.0133</v>
       </c>
-      <c r="C52" s="12"/>
-      <c r="D52" s="12"/>
+      <c r="C52" s="15"/>
+      <c r="D52" s="15"/>
     </row>
     <row r="53" ht="14.75" spans="1:4">
-      <c r="A53" s="1">
+      <c r="A53" s="2">
         <v>41730</v>
       </c>
-      <c r="B53" s="12">
+      <c r="B53" s="15">
         <v>0.0346</v>
       </c>
-      <c r="C53" s="12"/>
-      <c r="D53" s="12"/>
+      <c r="C53" s="15"/>
+      <c r="D53" s="15"/>
     </row>
     <row r="54" ht="14.75" spans="1:4">
-      <c r="A54" s="1">
+      <c r="A54" s="2">
         <v>41760</v>
       </c>
-      <c r="B54" s="12">
+      <c r="B54" s="15">
         <v>0.0267</v>
       </c>
-      <c r="C54" s="12"/>
-      <c r="D54" s="12"/>
+      <c r="C54" s="15"/>
+      <c r="D54" s="15"/>
     </row>
     <row r="55" ht="14.75" spans="1:4">
-      <c r="A55" s="1">
+      <c r="A55" s="2">
         <v>41791</v>
       </c>
-      <c r="B55" s="12">
+      <c r="B55" s="15">
         <v>0.2214</v>
       </c>
-      <c r="C55" s="12"/>
-      <c r="D55" s="12"/>
+      <c r="C55" s="15"/>
+      <c r="D55" s="15"/>
     </row>
     <row r="56" ht="14.75" spans="1:4">
-      <c r="A56" s="1">
+      <c r="A56" s="2">
         <v>41821</v>
       </c>
-      <c r="B56" s="12">
+      <c r="B56" s="15">
         <v>0.1535</v>
       </c>
-      <c r="C56" s="12"/>
-      <c r="D56" s="12"/>
+      <c r="C56" s="15"/>
+      <c r="D56" s="15"/>
     </row>
     <row r="57" ht="14.75" spans="1:4">
-      <c r="A57" s="1">
+      <c r="A57" s="2">
         <v>41852</v>
       </c>
-      <c r="B57" s="12">
+      <c r="B57" s="15">
         <v>0.1294</v>
       </c>
-      <c r="C57" s="12"/>
-      <c r="D57" s="12"/>
+      <c r="C57" s="15"/>
+      <c r="D57" s="15"/>
     </row>
     <row r="58" ht="14.75" spans="1:4">
-      <c r="A58" s="1">
+      <c r="A58" s="2">
         <v>41883</v>
       </c>
-      <c r="B58" s="12">
+      <c r="B58" s="15">
         <v>0.2618</v>
       </c>
-      <c r="C58" s="12"/>
-      <c r="D58" s="12"/>
+      <c r="C58" s="15"/>
+      <c r="D58" s="15"/>
     </row>
     <row r="59" ht="14.75" spans="1:4">
-      <c r="A59" s="1">
+      <c r="A59" s="2">
         <v>41913</v>
       </c>
-      <c r="B59" s="12">
+      <c r="B59" s="15">
         <v>0.044</v>
       </c>
-      <c r="C59" s="12"/>
-      <c r="D59" s="12"/>
+      <c r="C59" s="15"/>
+      <c r="D59" s="15"/>
     </row>
     <row r="60" ht="14.75" spans="1:4">
-      <c r="A60" s="1">
+      <c r="A60" s="2">
         <v>41944</v>
       </c>
-      <c r="B60" s="12">
+      <c r="B60" s="15">
         <v>0.0477</v>
       </c>
-      <c r="C60" s="12"/>
-      <c r="D60" s="12"/>
+      <c r="C60" s="15"/>
+      <c r="D60" s="15"/>
     </row>
     <row r="61" ht="14.75" spans="1:4">
-      <c r="A61" s="1">
+      <c r="A61" s="2">
         <v>41974</v>
       </c>
-      <c r="B61" s="12">
+      <c r="B61" s="15">
         <v>-0.1353</v>
       </c>
-      <c r="C61" s="12"/>
-      <c r="D61" s="12"/>
+      <c r="C61" s="15"/>
+      <c r="D61" s="15"/>
     </row>
     <row r="62" ht="14.75" spans="1:4">
-      <c r="A62" s="1">
+      <c r="A62" s="2">
         <v>42005</v>
       </c>
-      <c r="B62" s="12">
+      <c r="B62" s="15">
         <v>0.0227</v>
       </c>
-      <c r="C62" s="12"/>
-      <c r="D62" s="12"/>
+      <c r="C62" s="15"/>
+      <c r="D62" s="15"/>
     </row>
     <row r="63" ht="14.75" spans="1:4">
-      <c r="A63" s="1">
+      <c r="A63" s="2">
         <v>42036</v>
       </c>
-      <c r="B63" s="12">
+      <c r="B63" s="15">
         <v>0.0675</v>
       </c>
-      <c r="C63" s="12"/>
-      <c r="D63" s="12"/>
+      <c r="C63" s="15"/>
+      <c r="D63" s="15"/>
     </row>
     <row r="64" ht="14.75" spans="1:4">
-      <c r="A64" s="13">
+      <c r="A64" s="16">
         <v>42064</v>
       </c>
-      <c r="B64" s="14">
+      <c r="B64" s="17">
         <v>0.2462</v>
       </c>
-      <c r="C64" s="14"/>
-      <c r="D64" s="14"/>
+      <c r="C64" s="17"/>
+      <c r="D64" s="17"/>
     </row>
     <row r="65" ht="14.75" spans="1:4">
-      <c r="A65" s="1">
+      <c r="A65" s="2">
         <v>42095</v>
       </c>
-      <c r="B65" s="12">
+      <c r="B65" s="15">
         <v>0.079</v>
       </c>
-      <c r="C65" s="12"/>
-      <c r="D65" s="12"/>
+      <c r="C65" s="15"/>
+      <c r="D65" s="15"/>
     </row>
     <row r="66" ht="14.75" spans="1:4">
-      <c r="A66" s="1">
+      <c r="A66" s="2">
         <v>42125</v>
       </c>
-      <c r="B66" s="12">
+      <c r="B66" s="15">
         <v>0.415</v>
       </c>
-      <c r="C66" s="12"/>
-      <c r="D66" s="12"/>
+      <c r="C66" s="15"/>
+      <c r="D66" s="15"/>
     </row>
     <row r="67" ht="14.75" spans="1:4">
-      <c r="A67" s="1">
+      <c r="A67" s="2">
         <v>42156</v>
       </c>
-      <c r="B67" s="12">
+      <c r="B67" s="15">
         <v>0.0212</v>
       </c>
-      <c r="C67" s="12"/>
-      <c r="D67" s="12"/>
+      <c r="C67" s="15"/>
+      <c r="D67" s="15"/>
     </row>
     <row r="68" ht="14.75" spans="1:4">
-      <c r="A68" s="1">
+      <c r="A68" s="2">
         <v>42186</v>
       </c>
-      <c r="B68" s="12">
+      <c r="B68" s="15">
         <v>0.3626</v>
       </c>
-      <c r="C68" s="12"/>
-      <c r="D68" s="12"/>
+      <c r="C68" s="15"/>
+      <c r="D68" s="15"/>
     </row>
     <row r="69" ht="14.75" spans="1:4">
-      <c r="A69" s="1">
+      <c r="A69" s="2">
         <v>42217</v>
       </c>
-      <c r="B69" s="12">
+      <c r="B69" s="15">
         <v>0.283</v>
       </c>
-      <c r="C69" s="12"/>
-      <c r="D69" s="12"/>
+      <c r="C69" s="15"/>
+      <c r="D69" s="15"/>
     </row>
     <row r="70" ht="14.75" spans="1:4">
-      <c r="A70" s="1">
+      <c r="A70" s="2">
         <v>42248</v>
       </c>
-      <c r="B70" s="12">
+      <c r="B70" s="15">
         <v>-0.0678</v>
       </c>
-      <c r="C70" s="12"/>
-      <c r="D70" s="12"/>
+      <c r="C70" s="15"/>
+      <c r="D70" s="15"/>
     </row>
     <row r="71" ht="14.75" spans="1:4">
-      <c r="A71" s="1">
+      <c r="A71" s="2">
         <v>42278</v>
       </c>
-      <c r="B71" s="12">
+      <c r="B71" s="15">
         <v>0.2277</v>
       </c>
-      <c r="C71" s="12"/>
-      <c r="D71" s="12"/>
+      <c r="C71" s="15"/>
+      <c r="D71" s="15"/>
     </row>
     <row r="72" ht="14.75" spans="1:4">
-      <c r="A72" s="1">
+      <c r="A72" s="2">
         <v>42309</v>
       </c>
-      <c r="B72" s="12">
+      <c r="B72" s="15">
         <v>0.3277</v>
       </c>
-      <c r="C72" s="12"/>
-      <c r="D72" s="12"/>
+      <c r="C72" s="15"/>
+      <c r="D72" s="15"/>
     </row>
     <row r="73" ht="14.75" spans="1:4">
-      <c r="A73" s="1">
+      <c r="A73" s="2">
         <v>42339</v>
       </c>
-      <c r="B73" s="12">
+      <c r="B73" s="15">
         <v>0.2392</v>
       </c>
-      <c r="C73" s="12"/>
-      <c r="D73" s="12"/>
+      <c r="C73" s="15"/>
+      <c r="D73" s="15"/>
     </row>
     <row r="74" ht="14.75" spans="1:4">
-      <c r="A74" s="13">
+      <c r="A74" s="16">
         <v>42370</v>
       </c>
-      <c r="B74" s="14">
+      <c r="B74" s="17">
         <v>-0.0084</v>
       </c>
-      <c r="C74" s="14"/>
-      <c r="D74" s="14"/>
+      <c r="C74" s="17"/>
+      <c r="D74" s="17"/>
     </row>
     <row r="75" ht="14.75" spans="1:4">
-      <c r="A75" s="1">
+      <c r="A75" s="2">
         <v>42401</v>
       </c>
-      <c r="B75" s="12">
+      <c r="B75" s="15">
         <v>0.0011</v>
       </c>
-      <c r="C75" s="12"/>
-      <c r="D75" s="12"/>
+      <c r="C75" s="15"/>
+      <c r="D75" s="15"/>
     </row>
     <row r="76" ht="14.75" spans="1:4">
-      <c r="A76" s="1">
+      <c r="A76" s="2">
         <v>42430</v>
       </c>
-      <c r="B76" s="12">
+      <c r="B76" s="15">
         <v>0.4005</v>
       </c>
-      <c r="C76" s="12"/>
-      <c r="D76" s="12"/>
+      <c r="C76" s="15"/>
+      <c r="D76" s="15"/>
     </row>
     <row r="77" ht="14.75" spans="1:4">
-      <c r="A77" s="1">
+      <c r="A77" s="2">
         <v>42461</v>
       </c>
-      <c r="B77" s="12">
+      <c r="B77" s="15">
         <v>0.0084</v>
       </c>
-      <c r="C77" s="12"/>
-      <c r="D77" s="12"/>
+      <c r="C77" s="15"/>
+      <c r="D77" s="15"/>
     </row>
     <row r="78" ht="14.75" spans="1:4">
-      <c r="A78" s="1">
+      <c r="A78" s="2">
         <v>42491</v>
       </c>
-      <c r="B78" s="12">
+      <c r="B78" s="15">
         <v>-0.0213</v>
       </c>
-      <c r="C78" s="12"/>
-      <c r="D78" s="12"/>
+      <c r="C78" s="15"/>
+      <c r="D78" s="15"/>
     </row>
     <row r="79" ht="14.75" spans="1:4">
-      <c r="A79" s="1">
+      <c r="A79" s="2">
         <v>42522</v>
       </c>
-      <c r="B79" s="12">
+      <c r="B79" s="15">
         <v>0.1059</v>
       </c>
-      <c r="C79" s="12"/>
-      <c r="D79" s="12"/>
+      <c r="C79" s="15"/>
+      <c r="D79" s="15"/>
     </row>
     <row r="80" ht="14.75" spans="1:4">
-      <c r="A80" s="1">
+      <c r="A80" s="2">
         <v>42552</v>
       </c>
-      <c r="B80" s="12">
+      <c r="B80" s="15">
         <v>0.0296</v>
       </c>
-      <c r="C80" s="12"/>
-      <c r="D80" s="12"/>
+      <c r="C80" s="15"/>
+      <c r="D80" s="15"/>
     </row>
     <row r="81" ht="14.75" spans="1:4">
-      <c r="A81" s="1">
+      <c r="A81" s="2">
         <v>42583</v>
       </c>
-      <c r="B81" s="12">
+      <c r="B81" s="15">
         <v>0.0412</v>
       </c>
-      <c r="C81" s="12"/>
-      <c r="D81" s="12"/>
+      <c r="C81" s="15"/>
+      <c r="D81" s="15"/>
     </row>
     <row r="82" ht="14.75" spans="1:4">
-      <c r="A82" s="1">
+      <c r="A82" s="2">
         <v>42614</v>
       </c>
-      <c r="B82" s="12">
+      <c r="B82" s="15">
         <v>0.0455</v>
       </c>
-      <c r="C82" s="12"/>
-      <c r="D82" s="12"/>
+      <c r="C82" s="15"/>
+      <c r="D82" s="15"/>
     </row>
     <row r="83" ht="14.75" spans="1:4">
-      <c r="A83" s="1">
+      <c r="A83" s="2">
         <v>42644</v>
       </c>
-      <c r="B83" s="12">
+      <c r="B83" s="15">
         <v>0.0609</v>
       </c>
-      <c r="C83" s="12"/>
-      <c r="D83" s="12"/>
+      <c r="C83" s="15"/>
+      <c r="D83" s="15"/>
     </row>
     <row r="84" ht="14.75" spans="1:4">
-      <c r="A84" s="1">
+      <c r="A84" s="2">
         <v>42675</v>
       </c>
-      <c r="B84" s="12">
+      <c r="B84" s="15">
         <v>0.0377</v>
       </c>
-      <c r="C84" s="12"/>
-      <c r="D84" s="12"/>
+      <c r="C84" s="15"/>
+      <c r="D84" s="15"/>
     </row>
     <row r="85" ht="14.75" spans="1:4">
-      <c r="A85" s="1">
+      <c r="A85" s="2">
         <v>42705</v>
       </c>
-      <c r="B85" s="12">
+      <c r="B85" s="15">
         <v>0.12</v>
       </c>
-      <c r="C85" s="12"/>
-      <c r="D85" s="12"/>
+      <c r="C85" s="15"/>
+      <c r="D85" s="15"/>
     </row>
     <row r="86" ht="14.75" spans="1:4">
-      <c r="A86" s="1">
+      <c r="A86" s="2">
         <v>42736</v>
       </c>
-      <c r="B86" s="12">
+      <c r="B86" s="15">
         <v>0.0177</v>
       </c>
-      <c r="C86" s="12"/>
-      <c r="D86" s="12"/>
+      <c r="C86" s="15"/>
+      <c r="D86" s="15"/>
     </row>
     <row r="87" ht="14.75" spans="1:4">
-      <c r="A87" s="1">
+      <c r="A87" s="2">
         <v>42767</v>
       </c>
-      <c r="B87" s="12">
+      <c r="B87" s="15">
         <v>0.0514</v>
       </c>
-      <c r="C87" s="12"/>
-      <c r="D87" s="12"/>
+      <c r="C87" s="15"/>
+      <c r="D87" s="15"/>
     </row>
     <row r="88" ht="14.75" spans="1:4">
-      <c r="A88" s="1">
+      <c r="A88" s="2">
         <v>42795</v>
       </c>
-      <c r="B88" s="12">
+      <c r="B88" s="15">
         <v>-0.0782</v>
       </c>
-      <c r="C88" s="12"/>
-      <c r="D88" s="12"/>
+      <c r="C88" s="15"/>
+      <c r="D88" s="15"/>
     </row>
     <row r="89" ht="14.75" spans="1:4">
-      <c r="A89" s="1">
+      <c r="A89" s="2">
         <v>42826</v>
       </c>
-      <c r="B89" s="12">
+      <c r="B89" s="15">
         <v>0.0085</v>
       </c>
-      <c r="C89" s="12"/>
-      <c r="D89" s="12"/>
+      <c r="C89" s="15"/>
+      <c r="D89" s="15"/>
     </row>
     <row r="90" ht="14.75" spans="1:4">
-      <c r="A90" s="1">
+      <c r="A90" s="2">
         <v>42856</v>
       </c>
-      <c r="B90" s="12">
+      <c r="B90" s="15">
         <v>-0.0614</v>
       </c>
-      <c r="C90" s="12"/>
-      <c r="D90" s="12"/>
+      <c r="C90" s="15"/>
+      <c r="D90" s="15"/>
     </row>
     <row r="91" ht="14.75" spans="1:4">
-      <c r="A91" s="1">
+      <c r="A91" s="2">
         <v>42887</v>
       </c>
-      <c r="B91" s="12">
+      <c r="B91" s="15">
         <v>0.0901</v>
       </c>
-      <c r="C91" s="12"/>
-      <c r="D91" s="12"/>
+      <c r="C91" s="15"/>
+      <c r="D91" s="15"/>
     </row>
     <row r="92" ht="14.75" spans="1:4">
-      <c r="A92" s="1">
+      <c r="A92" s="2">
         <v>42917</v>
       </c>
-      <c r="B92" s="12">
+      <c r="B92" s="15">
         <v>-0.0132</v>
       </c>
-      <c r="C92" s="12"/>
-      <c r="D92" s="12"/>
+      <c r="C92" s="15"/>
+      <c r="D92" s="15"/>
     </row>
     <row r="93" ht="14.75" spans="1:4">
-      <c r="A93" s="1">
+      <c r="A93" s="2">
         <v>42948</v>
       </c>
-      <c r="B93" s="12">
+      <c r="B93" s="15">
         <v>0.1779</v>
       </c>
-      <c r="C93" s="12"/>
-      <c r="D93" s="12"/>
+      <c r="C93" s="15"/>
+      <c r="D93" s="15"/>
     </row>
     <row r="94" ht="14.75" spans="1:4">
-      <c r="A94" s="1">
+      <c r="A94" s="2">
         <v>42979</v>
       </c>
-      <c r="B94" s="12">
+      <c r="B94" s="15">
         <v>0.0209</v>
       </c>
-      <c r="C94" s="12"/>
-      <c r="D94" s="12"/>
+      <c r="C94" s="15"/>
+      <c r="D94" s="15"/>
     </row>
     <row r="95" ht="14.75" spans="1:4">
-      <c r="A95" s="1">
+      <c r="A95" s="2">
         <v>43009</v>
       </c>
-      <c r="B95" s="12">
+      <c r="B95" s="15">
         <v>-0.0084</v>
       </c>
-      <c r="C95" s="12"/>
-      <c r="D95" s="12"/>
+      <c r="C95" s="15"/>
+      <c r="D95" s="15"/>
     </row>
     <row r="96" ht="14.75" spans="1:4">
-      <c r="A96" s="1">
+      <c r="A96" s="2">
         <v>43040</v>
       </c>
-      <c r="B96" s="12">
+      <c r="B96" s="15">
         <v>-0.0635</v>
       </c>
-      <c r="C96" s="12"/>
-      <c r="D96" s="12"/>
+      <c r="C96" s="15"/>
+      <c r="D96" s="15"/>
     </row>
     <row r="97" ht="14.75" spans="1:4">
-      <c r="A97" s="1">
+      <c r="A97" s="2">
         <v>43070</v>
       </c>
-      <c r="B97" s="12">
+      <c r="B97" s="15">
         <v>-0.0392</v>
       </c>
-      <c r="C97" s="12"/>
-      <c r="D97" s="12"/>
+      <c r="C97" s="15"/>
+      <c r="D97" s="15"/>
     </row>
     <row r="98" ht="14.75" spans="1:4">
-      <c r="A98" s="1">
+      <c r="A98" s="2">
         <v>43101</v>
       </c>
-      <c r="B98" s="12">
+      <c r="B98" s="15">
         <v>0.0243</v>
       </c>
-      <c r="C98" s="12"/>
-      <c r="D98" s="12"/>
+      <c r="C98" s="15"/>
+      <c r="D98" s="15"/>
     </row>
     <row r="99" ht="14.75" spans="1:4">
-      <c r="A99" s="1">
+      <c r="A99" s="2">
         <v>43132</v>
       </c>
-      <c r="B99" s="12">
+      <c r="B99" s="15">
         <v>0.0119</v>
       </c>
-      <c r="C99" s="12"/>
-      <c r="D99" s="12"/>
+      <c r="C99" s="15"/>
+      <c r="D99" s="15"/>
     </row>
     <row r="100" ht="14.75" spans="1:4">
-      <c r="A100" s="1">
+      <c r="A100" s="2">
         <v>43160</v>
       </c>
-      <c r="B100" s="12">
+      <c r="B100" s="15">
         <v>0.1099</v>
       </c>
-      <c r="C100" s="12"/>
-      <c r="D100" s="12"/>
+      <c r="C100" s="15"/>
+      <c r="D100" s="15"/>
     </row>
     <row r="101" ht="14.75" spans="1:4">
-      <c r="A101" s="1">
+      <c r="A101" s="2">
         <v>43191</v>
       </c>
-      <c r="B101" s="12">
+      <c r="B101" s="15">
         <v>0.0021</v>
       </c>
-      <c r="C101" s="12"/>
-      <c r="D101" s="12"/>
+      <c r="C101" s="15"/>
+      <c r="D101" s="15"/>
     </row>
     <row r="102" ht="14.75" spans="1:4">
-      <c r="A102" s="1">
+      <c r="A102" s="2">
         <v>43221</v>
       </c>
-      <c r="B102" s="12">
+      <c r="B102" s="15">
         <v>0.0257</v>
       </c>
-      <c r="C102" s="12"/>
-      <c r="D102" s="12"/>
+      <c r="C102" s="15"/>
+      <c r="D102" s="15"/>
     </row>
     <row r="103" ht="14.75" spans="1:4">
-      <c r="A103" s="1">
+      <c r="A103" s="2">
         <v>43252</v>
       </c>
-      <c r="B103" s="12">
+      <c r="B103" s="15">
         <v>-0.0844</v>
       </c>
-      <c r="C103" s="12"/>
-      <c r="D103" s="12"/>
+      <c r="C103" s="15"/>
+      <c r="D103" s="15"/>
     </row>
     <row r="104" ht="14.75" spans="1:4">
-      <c r="A104" s="1">
+      <c r="A104" s="2">
         <v>43282</v>
       </c>
-      <c r="B104" s="12">
+      <c r="B104" s="15">
         <v>0.1728</v>
       </c>
-      <c r="C104" s="12"/>
-      <c r="D104" s="12"/>
+      <c r="C104" s="15"/>
+      <c r="D104" s="15"/>
     </row>
     <row r="105" ht="14.75" spans="1:4">
-      <c r="A105" s="1">
+      <c r="A105" s="2">
         <v>43313</v>
       </c>
-      <c r="B105" s="12">
+      <c r="B105" s="15">
         <v>-0.071</v>
       </c>
-      <c r="C105" s="12"/>
-      <c r="D105" s="12"/>
+      <c r="C105" s="15"/>
+      <c r="D105" s="15"/>
     </row>
     <row r="106" ht="14.75" spans="1:4">
-      <c r="A106" s="1">
+      <c r="A106" s="2">
         <v>43344</v>
       </c>
-      <c r="B106" s="12">
+      <c r="B106" s="15">
         <v>0.0614</v>
       </c>
-      <c r="C106" s="12"/>
-      <c r="D106" s="12"/>
+      <c r="C106" s="15"/>
+      <c r="D106" s="15"/>
     </row>
     <row r="107" ht="14.75" spans="1:4">
-      <c r="A107" s="1">
+      <c r="A107" s="2">
         <v>43374</v>
       </c>
-      <c r="B107" s="12">
+      <c r="B107" s="15">
         <v>0.0711</v>
       </c>
-      <c r="C107" s="12"/>
-      <c r="D107" s="12"/>
+      <c r="C107" s="15"/>
+      <c r="D107" s="15"/>
     </row>
     <row r="108" ht="14.75" spans="1:4">
-      <c r="A108" s="1">
+      <c r="A108" s="2">
         <v>43405</v>
       </c>
-      <c r="B108" s="12">
+      <c r="B108" s="15">
         <v>0.1498</v>
       </c>
-      <c r="C108" s="12"/>
-      <c r="D108" s="12"/>
+      <c r="C108" s="15"/>
+      <c r="D108" s="15"/>
     </row>
     <row r="109" ht="14.75" spans="1:4">
-      <c r="A109" s="1">
+      <c r="A109" s="2">
         <v>43435</v>
       </c>
-      <c r="B109" s="12">
+      <c r="B109" s="15">
         <v>-0.0448</v>
       </c>
-      <c r="C109" s="12"/>
-      <c r="D109" s="12"/>
+      <c r="C109" s="15"/>
+      <c r="D109" s="15"/>
     </row>
     <row r="110" ht="14.75" spans="1:4">
-      <c r="A110" s="1">
+      <c r="A110" s="2">
         <v>43466</v>
       </c>
-      <c r="B110" s="12">
+      <c r="B110" s="15">
         <v>0.0143</v>
       </c>
-      <c r="C110" s="12"/>
-      <c r="D110" s="12"/>
+      <c r="C110" s="15"/>
+      <c r="D110" s="15"/>
     </row>
     <row r="111" ht="14.75" spans="1:4">
-      <c r="A111" s="1">
+      <c r="A111" s="2">
         <v>43497</v>
       </c>
-      <c r="B111" s="12">
+      <c r="B111" s="15">
         <v>0.1369</v>
       </c>
-      <c r="C111" s="12"/>
-      <c r="D111" s="12"/>
+      <c r="C111" s="15"/>
+      <c r="D111" s="15"/>
     </row>
     <row r="112" ht="14.75" spans="1:4">
-      <c r="A112" s="1">
+      <c r="A112" s="2">
         <v>43525</v>
       </c>
-      <c r="B112" s="12">
+      <c r="B112" s="15">
         <v>0.1862</v>
       </c>
-      <c r="C112" s="12"/>
-      <c r="D112" s="12"/>
+      <c r="C112" s="15"/>
+      <c r="D112" s="15"/>
     </row>
     <row r="113" ht="14.75" spans="1:4">
-      <c r="A113" s="1">
+      <c r="A113" s="2">
         <v>43556</v>
       </c>
-      <c r="B113" s="12">
+      <c r="B113" s="15">
         <v>0.0276</v>
       </c>
-      <c r="C113" s="12"/>
-      <c r="D113" s="12"/>
+      <c r="C113" s="15"/>
+      <c r="D113" s="15"/>
     </row>
     <row r="114" ht="14.75" spans="1:4">
-      <c r="A114" s="1">
+      <c r="A114" s="2">
         <v>43586</v>
       </c>
-      <c r="B114" s="12">
+      <c r="B114" s="15">
         <v>0.0582</v>
       </c>
-      <c r="C114" s="12"/>
-      <c r="D114" s="12"/>
+      <c r="C114" s="15"/>
+      <c r="D114" s="15"/>
     </row>
     <row r="115" ht="14.75" spans="1:4">
-      <c r="A115" s="1">
+      <c r="A115" s="2">
         <v>43617</v>
       </c>
-      <c r="B115" s="12">
+      <c r="B115" s="15">
         <v>0.0329</v>
       </c>
-      <c r="C115" s="12"/>
-      <c r="D115" s="12"/>
+      <c r="C115" s="15"/>
+      <c r="D115" s="15"/>
     </row>
     <row r="116" ht="14.75" spans="1:4">
-      <c r="A116" s="1">
+      <c r="A116" s="2">
         <v>43647</v>
       </c>
-      <c r="B116" s="12">
+      <c r="B116" s="15">
         <v>-0.0096</v>
       </c>
-      <c r="C116" s="12"/>
-      <c r="D116" s="12"/>
+      <c r="C116" s="15"/>
+      <c r="D116" s="15"/>
     </row>
     <row r="117" ht="14.75" spans="1:4">
-      <c r="A117" s="1">
+      <c r="A117" s="2">
         <v>43678</v>
       </c>
-      <c r="B117" s="12">
+      <c r="B117" s="15">
         <v>-0.0119</v>
       </c>
-      <c r="C117" s="12"/>
-      <c r="D117" s="12"/>
+      <c r="C117" s="15"/>
+      <c r="D117" s="15"/>
     </row>
     <row r="118" ht="14.75" spans="1:4">
-      <c r="A118" s="1">
+      <c r="A118" s="2">
         <v>43709</v>
       </c>
-      <c r="B118" s="12">
+      <c r="B118" s="15">
         <v>0.0449</v>
       </c>
-      <c r="C118" s="12"/>
-      <c r="D118" s="12"/>
+      <c r="C118" s="15"/>
+      <c r="D118" s="15"/>
     </row>
     <row r="119" ht="14.75" spans="1:4">
-      <c r="A119" s="1">
+      <c r="A119" s="2">
         <v>43739</v>
       </c>
-      <c r="B119" s="12">
+      <c r="B119" s="15">
         <v>-0.0117</v>
       </c>
-      <c r="C119" s="12"/>
-      <c r="D119" s="12"/>
+      <c r="C119" s="15"/>
+      <c r="D119" s="15"/>
     </row>
     <row r="120" ht="14.75" spans="1:4">
-      <c r="A120" s="1">
+      <c r="A120" s="2">
         <v>43770</v>
       </c>
-      <c r="B120" s="12">
+      <c r="B120" s="15">
         <v>-0.0051</v>
       </c>
-      <c r="C120" s="12"/>
-      <c r="D120" s="12"/>
+      <c r="C120" s="15"/>
+      <c r="D120" s="15"/>
     </row>
     <row r="121" ht="14.75" spans="1:4">
-      <c r="A121" s="1">
+      <c r="A121" s="2">
         <v>43800</v>
       </c>
-      <c r="B121" s="12">
+      <c r="B121" s="15">
         <v>0.1302</v>
       </c>
-      <c r="C121" s="12"/>
-      <c r="D121" s="12"/>
+      <c r="C121" s="15"/>
+      <c r="D121" s="15"/>
     </row>
     <row r="122" ht="14.75" spans="1:4">
-      <c r="A122" s="1">
+      <c r="A122" s="2">
         <v>43831</v>
       </c>
-      <c r="B122" s="12">
+      <c r="B122" s="15">
         <v>0.0099</v>
       </c>
-      <c r="C122" s="12"/>
-      <c r="D122" s="12"/>
+      <c r="C122" s="15"/>
+      <c r="D122" s="15"/>
     </row>
     <row r="123" ht="14.75" spans="1:4">
-      <c r="A123" s="1">
+      <c r="A123" s="2">
         <v>43862</v>
       </c>
-      <c r="B123" s="12">
+      <c r="B123" s="15">
         <v>0.0369</v>
       </c>
-      <c r="C123" s="12"/>
-      <c r="D123" s="12"/>
+      <c r="C123" s="15"/>
+      <c r="D123" s="15"/>
     </row>
     <row r="124" ht="14.75" spans="1:4">
-      <c r="A124" s="1">
+      <c r="A124" s="2">
         <v>43891</v>
       </c>
-      <c r="B124" s="12">
+      <c r="B124" s="15">
         <v>0.0595</v>
       </c>
-      <c r="C124" s="12"/>
-      <c r="D124" s="12"/>
+      <c r="C124" s="15"/>
+      <c r="D124" s="15"/>
     </row>
     <row r="125" ht="14.75" spans="1:4">
-      <c r="A125" s="1">
+      <c r="A125" s="2">
         <v>43922</v>
       </c>
-      <c r="B125" s="12">
+      <c r="B125" s="15">
         <v>0.0314</v>
       </c>
-      <c r="C125" s="12"/>
-      <c r="D125" s="12"/>
+      <c r="C125" s="15"/>
+      <c r="D125" s="15"/>
     </row>
     <row r="126" ht="14.75" spans="1:4">
-      <c r="A126" s="1">
+      <c r="A126" s="2">
         <v>43952</v>
       </c>
-      <c r="B126" s="12">
+      <c r="B126" s="15">
         <v>0.0684</v>
       </c>
-      <c r="C126" s="12"/>
-      <c r="D126" s="12"/>
+      <c r="C126" s="15"/>
+      <c r="D126" s="15"/>
     </row>
     <row r="127" ht="14.75" spans="1:4">
-      <c r="A127" s="1">
+      <c r="A127" s="2">
         <v>43983</v>
       </c>
-      <c r="B127" s="12">
+      <c r="B127" s="15">
         <v>0.0866</v>
       </c>
-      <c r="C127" s="12"/>
-      <c r="D127" s="12"/>
+      <c r="C127" s="15"/>
+      <c r="D127" s="15"/>
     </row>
     <row r="128" ht="14.75" spans="1:4">
-      <c r="A128" s="1">
+      <c r="A128" s="2">
         <v>44013</v>
       </c>
-      <c r="B128" s="12">
+      <c r="B128" s="15">
         <v>0.0961</v>
       </c>
-      <c r="C128" s="12"/>
-      <c r="D128" s="12"/>
+      <c r="C128" s="15"/>
+      <c r="D128" s="15"/>
     </row>
     <row r="129" ht="14.75" spans="1:4">
-      <c r="A129" s="1">
+      <c r="A129" s="2">
         <v>44044</v>
       </c>
-      <c r="B129" s="12">
+      <c r="B129" s="15">
         <v>0.1462</v>
       </c>
-      <c r="C129" s="12"/>
-      <c r="D129" s="12"/>
+      <c r="C129" s="15"/>
+      <c r="D129" s="15"/>
     </row>
     <row r="130" ht="14.75" spans="1:4">
-      <c r="A130" s="1">
+      <c r="A130" s="2">
         <v>44075</v>
       </c>
-      <c r="B130" s="12">
+      <c r="B130" s="15">
         <v>-0.0312</v>
       </c>
-      <c r="C130" s="12"/>
-      <c r="D130" s="12"/>
+      <c r="C130" s="15"/>
+      <c r="D130" s="15"/>
     </row>
     <row r="131" ht="14.75" spans="1:4">
-      <c r="A131" s="1">
+      <c r="A131" s="2">
         <v>44105</v>
       </c>
-      <c r="B131" s="12">
+      <c r="B131" s="15">
         <v>0.0274</v>
       </c>
-      <c r="C131" s="12"/>
-      <c r="D131" s="12"/>
+      <c r="C131" s="15"/>
+      <c r="D131" s="15"/>
     </row>
     <row r="132" ht="14.75" spans="1:4">
-      <c r="A132" s="1">
+      <c r="A132" s="2">
         <v>44136</v>
       </c>
-      <c r="B132" s="12">
+      <c r="B132" s="15">
         <v>0.0181</v>
       </c>
-      <c r="C132" s="12"/>
-      <c r="D132" s="12"/>
+      <c r="C132" s="15"/>
+      <c r="D132" s="15"/>
     </row>
     <row r="133" ht="14.75" spans="1:4">
-      <c r="A133" s="1">
+      <c r="A133" s="2">
         <v>44166</v>
       </c>
-      <c r="B133" s="12">
+      <c r="B133" s="15">
         <v>-0.112</v>
       </c>
-      <c r="C133" s="12"/>
-      <c r="D133" s="12"/>
+      <c r="C133" s="15"/>
+      <c r="D133" s="15"/>
     </row>
     <row r="134" ht="14.75" spans="1:4">
-      <c r="A134" s="1">
+      <c r="A134" s="2">
         <v>44197</v>
       </c>
-      <c r="B134" s="12">
+      <c r="B134" s="15">
         <v>0.0077</v>
       </c>
-      <c r="C134" s="12"/>
-      <c r="D134" s="12"/>
+      <c r="C134" s="15"/>
+      <c r="D134" s="15"/>
     </row>
     <row r="135" ht="14.75" spans="1:4">
-      <c r="A135" s="1">
+      <c r="A135" s="2">
         <v>44228</v>
       </c>
-      <c r="B135" s="12">
+      <c r="B135" s="15">
         <v>0.1271</v>
       </c>
-      <c r="C135" s="12"/>
-      <c r="D135" s="12"/>
+      <c r="C135" s="15"/>
+      <c r="D135" s="15"/>
     </row>
     <row r="136" ht="14.75" spans="1:4">
-      <c r="A136" s="1">
+      <c r="A136" s="2">
         <v>44256</v>
       </c>
-      <c r="B136" s="12">
+      <c r="B136" s="15">
         <v>0.1564</v>
       </c>
-      <c r="C136" s="12"/>
-      <c r="D136" s="12"/>
+      <c r="C136" s="15"/>
+      <c r="D136" s="15"/>
     </row>
     <row r="137" ht="14.75" spans="1:4">
-      <c r="A137" s="1">
+      <c r="A137" s="2">
         <v>44287</v>
       </c>
-      <c r="B137" s="12">
+      <c r="B137" s="15">
         <v>-0.0061</v>
       </c>
-      <c r="C137" s="12"/>
-      <c r="D137" s="12"/>
+      <c r="C137" s="15"/>
+      <c r="D137" s="15"/>
     </row>
     <row r="138" ht="14.75" spans="1:4">
-      <c r="A138" s="1">
+      <c r="A138" s="2">
         <v>44317</v>
       </c>
-      <c r="B138" s="12">
+      <c r="B138" s="15">
         <v>0.0562</v>
       </c>
-      <c r="C138" s="12"/>
-      <c r="D138" s="12"/>
+      <c r="C138" s="15"/>
+      <c r="D138" s="15"/>
     </row>
     <row r="139" ht="14.75" spans="1:4">
-      <c r="A139" s="1">
+      <c r="A139" s="2">
         <v>44348</v>
       </c>
-      <c r="B139" s="12">
+      <c r="B139" s="15">
         <v>0.0235</v>
       </c>
-      <c r="C139" s="12"/>
-      <c r="D139" s="12"/>
+      <c r="C139" s="15"/>
+      <c r="D139" s="15"/>
     </row>
     <row r="140" ht="14.75" spans="1:4">
-      <c r="A140" s="1">
+      <c r="A140" s="2">
         <v>44378</v>
       </c>
-      <c r="B140" s="12">
+      <c r="B140" s="15">
         <v>-0.0538</v>
       </c>
-      <c r="C140" s="12"/>
-      <c r="D140" s="12"/>
+      <c r="C140" s="15"/>
+      <c r="D140" s="15"/>
     </row>
     <row r="141" ht="14.75" spans="1:4">
-      <c r="A141" s="1">
+      <c r="A141" s="2">
         <v>44409</v>
       </c>
-      <c r="B141" s="12">
+      <c r="B141" s="15">
         <v>0.0861</v>
       </c>
-      <c r="C141" s="12"/>
-      <c r="D141" s="12"/>
+      <c r="C141" s="15"/>
+      <c r="D141" s="15"/>
     </row>
     <row r="142" ht="14.75" spans="1:4">
-      <c r="A142" s="1">
+      <c r="A142" s="2">
         <v>44440</v>
       </c>
-      <c r="B142" s="12">
+      <c r="B142" s="15">
         <v>-0.0215</v>
       </c>
-      <c r="C142" s="12"/>
-      <c r="D142" s="12"/>
+      <c r="C142" s="15"/>
+      <c r="D142" s="15"/>
     </row>
     <row r="143" ht="14.75" spans="1:4">
-      <c r="A143" s="1">
+      <c r="A143" s="2">
         <v>44470</v>
       </c>
-      <c r="B143" s="12">
+      <c r="B143" s="15">
         <v>-0.0512</v>
       </c>
-      <c r="C143" s="12"/>
-      <c r="D143" s="12"/>
+      <c r="C143" s="15"/>
+      <c r="D143" s="15"/>
     </row>
     <row r="144" ht="14.75" spans="1:4">
-      <c r="A144" s="1">
+      <c r="A144" s="2">
         <v>44501</v>
       </c>
-      <c r="B144" s="12">
+      <c r="B144" s="15">
         <v>0.1091</v>
       </c>
-      <c r="C144" s="12"/>
-      <c r="D144" s="12"/>
+      <c r="C144" s="15"/>
+      <c r="D144" s="15"/>
     </row>
     <row r="145" ht="14.75" spans="1:4">
-      <c r="A145" s="1">
+      <c r="A145" s="2">
         <v>44531</v>
       </c>
-      <c r="B145" s="12">
+      <c r="B145" s="15">
         <v>0.1123</v>
       </c>
-      <c r="C145" s="12"/>
-      <c r="D145" s="12"/>
+      <c r="C145" s="15"/>
+      <c r="D145" s="15"/>
     </row>
     <row r="146" ht="14.75" spans="1:4">
-      <c r="A146" s="1">
+      <c r="A146" s="2">
         <v>44562</v>
       </c>
-      <c r="B146" s="12">
+      <c r="B146" s="15">
         <v>-0.0016</v>
       </c>
-      <c r="C146" s="12"/>
-      <c r="D146" s="12"/>
+      <c r="C146" s="15"/>
+      <c r="D146" s="15"/>
     </row>
     <row r="147" ht="14.75" spans="1:4">
-      <c r="A147" s="1">
+      <c r="A147" s="2">
         <v>44593</v>
       </c>
-      <c r="B147" s="12">
+      <c r="B147" s="15">
         <v>0.0797</v>
       </c>
-      <c r="C147" s="12"/>
-      <c r="D147" s="12"/>
+      <c r="C147" s="15"/>
+      <c r="D147" s="15"/>
     </row>
     <row r="148" ht="14.75" spans="1:4">
-      <c r="A148" s="1">
+      <c r="A148" s="2">
         <v>44621</v>
       </c>
-      <c r="B148" s="12">
+      <c r="B148" s="15">
         <v>0.0547</v>
       </c>
-      <c r="C148" s="12"/>
-      <c r="D148" s="12"/>
+      <c r="C148" s="15"/>
+      <c r="D148" s="15"/>
     </row>
     <row r="149" ht="14.75" spans="1:4">
-      <c r="A149" s="1">
+      <c r="A149" s="2">
         <v>44652</v>
       </c>
-      <c r="B149" s="12">
+      <c r="B149" s="15">
         <v>-0.0187</v>
       </c>
-      <c r="C149" s="12"/>
-      <c r="D149" s="12"/>
+      <c r="C149" s="15"/>
+      <c r="D149" s="15"/>
     </row>
     <row r="150" ht="14.75" spans="1:4">
-      <c r="A150" s="1">
+      <c r="A150" s="2">
         <v>44682</v>
       </c>
-      <c r="B150" s="12">
+      <c r="B150" s="15">
         <v>0.2725</v>
       </c>
-      <c r="C150" s="12"/>
-      <c r="D150" s="12"/>
+      <c r="C150" s="15"/>
+      <c r="D150" s="15"/>
     </row>
     <row r="151" ht="14.75" spans="1:4">
-      <c r="A151" s="1">
+      <c r="A151" s="2">
         <v>44713</v>
       </c>
-      <c r="B151" s="12">
+      <c r="B151" s="15">
         <v>0.1417</v>
       </c>
-      <c r="C151" s="12"/>
-      <c r="D151" s="12"/>
+      <c r="C151" s="15"/>
+      <c r="D151" s="15"/>
     </row>
     <row r="152" ht="14.75" spans="1:4">
-      <c r="A152" s="1">
+      <c r="A152" s="2">
         <v>44743</v>
       </c>
-      <c r="B152" s="12">
+      <c r="B152" s="15">
         <v>0.2166</v>
       </c>
-      <c r="C152" s="12"/>
-      <c r="D152" s="12"/>
+      <c r="C152" s="15"/>
+      <c r="D152" s="15"/>
     </row>
     <row r="153" ht="14.75" spans="1:4">
-      <c r="A153" s="1">
+      <c r="A153" s="2">
         <v>44774</v>
       </c>
-      <c r="B153" s="12">
+      <c r="B153" s="15">
         <v>0.1873</v>
       </c>
-      <c r="C153" s="12"/>
-      <c r="D153" s="12"/>
+      <c r="C153" s="15"/>
+      <c r="D153" s="15"/>
     </row>
     <row r="154" ht="14.75" spans="1:4">
-      <c r="A154" s="1">
+      <c r="A154" s="2">
         <v>44805</v>
       </c>
-      <c r="B154" s="12">
+      <c r="B154" s="15">
         <v>0.0367</v>
       </c>
-      <c r="C154" s="12"/>
-      <c r="D154" s="12"/>
+      <c r="C154" s="15"/>
+      <c r="D154" s="15"/>
     </row>
     <row r="155" ht="14.75" spans="1:4">
-      <c r="A155" s="1">
+      <c r="A155" s="2">
         <v>44835</v>
       </c>
-      <c r="B155" s="12">
+      <c r="B155" s="15">
         <v>0.0711</v>
       </c>
-      <c r="C155" s="12"/>
-      <c r="D155" s="12"/>
+      <c r="C155" s="15"/>
+      <c r="D155" s="15"/>
     </row>
     <row r="156" ht="14.75" spans="1:4">
-      <c r="A156" s="1">
+      <c r="A156" s="2">
         <v>44866</v>
       </c>
-      <c r="B156" s="12">
+      <c r="B156" s="15">
         <v>0.1051</v>
       </c>
-      <c r="C156" s="12"/>
-      <c r="D156" s="12"/>
+      <c r="C156" s="15"/>
+      <c r="D156" s="15"/>
     </row>
     <row r="157" ht="14.75" spans="1:4">
-      <c r="A157" s="1">
+      <c r="A157" s="2">
         <v>44896</v>
       </c>
-      <c r="B157" s="12">
+      <c r="B157" s="15">
         <v>0.0431</v>
       </c>
-      <c r="C157" s="12"/>
-      <c r="D157" s="12"/>
+      <c r="C157" s="15"/>
+      <c r="D157" s="15"/>
     </row>
     <row r="158" ht="14.75" spans="1:4">
-      <c r="A158" s="1">
+      <c r="A158" s="2">
         <v>44927</v>
       </c>
-      <c r="B158" s="12">
+      <c r="B158" s="15">
         <v>0.0148</v>
       </c>
-      <c r="C158" s="12"/>
-      <c r="D158" s="12"/>
+      <c r="C158" s="15"/>
+      <c r="D158" s="15"/>
     </row>
     <row r="159" ht="14.75" spans="1:4">
-      <c r="A159" s="1">
+      <c r="A159" s="2">
         <v>44958</v>
       </c>
-      <c r="B159" s="12">
+      <c r="B159" s="15">
         <v>0.0113</v>
       </c>
-      <c r="C159" s="12"/>
-      <c r="D159" s="12"/>
+      <c r="C159" s="15"/>
+      <c r="D159" s="15"/>
     </row>
     <row r="160" ht="14.75" spans="1:4">
-      <c r="A160" s="1">
+      <c r="A160" s="2">
         <v>44986</v>
       </c>
-      <c r="B160" s="12">
+      <c r="B160" s="15">
         <v>-0.0182</v>
       </c>
-      <c r="C160" s="12"/>
-      <c r="D160" s="12"/>
+      <c r="C160" s="15"/>
+      <c r="D160" s="15"/>
     </row>
     <row r="161" ht="14.75" spans="1:4">
-      <c r="A161" s="1">
+      <c r="A161" s="2">
         <v>45017</v>
       </c>
-      <c r="B161" s="12">
+      <c r="B161" s="15">
         <v>0.0234</v>
       </c>
-      <c r="C161" s="12"/>
-      <c r="D161" s="12"/>
+      <c r="C161" s="15"/>
+      <c r="D161" s="15"/>
     </row>
     <row r="162" ht="14.75" spans="1:4">
-      <c r="A162" s="1">
+      <c r="A162" s="2">
         <v>45047</v>
       </c>
-      <c r="B162" s="12">
+      <c r="B162" s="15">
         <v>0.0327</v>
       </c>
-      <c r="C162" s="12"/>
-      <c r="D162" s="12"/>
+      <c r="C162" s="15"/>
+      <c r="D162" s="15"/>
     </row>
     <row r="163" ht="14.75" spans="1:4">
-      <c r="A163" s="1">
+      <c r="A163" s="2">
         <v>45078</v>
       </c>
-      <c r="B163" s="12">
+      <c r="B163" s="15">
         <v>0.047</v>
       </c>
-      <c r="C163" s="12"/>
-      <c r="D163" s="12"/>
+      <c r="C163" s="15"/>
+      <c r="D163" s="15"/>
     </row>
     <row r="164" ht="14.75" spans="1:4">
-      <c r="A164" s="1">
+      <c r="A164" s="2">
         <v>45108</v>
       </c>
-      <c r="B164" s="12">
+      <c r="B164" s="15">
         <v>0.1586</v>
       </c>
-      <c r="C164" s="12"/>
-      <c r="D164" s="12"/>
+      <c r="C164" s="15"/>
+      <c r="D164" s="15"/>
     </row>
     <row r="165" ht="14.75" spans="1:4">
-      <c r="A165" s="1">
+      <c r="A165" s="2">
         <v>45139</v>
       </c>
-      <c r="B165" s="12">
+      <c r="B165" s="15">
         <v>-0.021</v>
       </c>
-      <c r="C165" s="12"/>
-      <c r="D165" s="12"/>
+      <c r="C165" s="15"/>
+      <c r="D165" s="15"/>
     </row>
     <row r="166" ht="14.75" spans="1:4">
-      <c r="A166" s="1">
+      <c r="A166" s="2">
         <v>45170</v>
       </c>
-      <c r="B166" s="12">
+      <c r="B166" s="15">
         <v>0.024</v>
       </c>
-      <c r="C166" s="12"/>
-      <c r="D166" s="12"/>
+      <c r="C166" s="15"/>
+      <c r="D166" s="15"/>
     </row>
     <row r="167" ht="14.75" spans="1:4">
-      <c r="A167" s="1">
+      <c r="A167" s="2">
         <v>45200</v>
       </c>
-      <c r="B167" s="12">
+      <c r="B167" s="15">
         <v>0.0474</v>
       </c>
-      <c r="C167" s="12"/>
-      <c r="D167" s="12"/>
+      <c r="C167" s="15"/>
+      <c r="D167" s="15"/>
     </row>
     <row r="168" ht="14.75" spans="1:4">
-      <c r="A168" s="1">
+      <c r="A168" s="2">
         <v>45231</v>
       </c>
-      <c r="B168" s="12">
+      <c r="B168" s="15">
         <v>0.1049</v>
       </c>
-      <c r="C168" s="12"/>
-      <c r="D168" s="12"/>
+      <c r="C168" s="15"/>
+      <c r="D168" s="15"/>
     </row>
     <row r="169" ht="14.75" spans="1:4">
-      <c r="A169" s="1">
+      <c r="A169" s="2">
         <v>45261</v>
       </c>
-      <c r="B169" s="12">
+      <c r="B169" s="15">
         <v>-0.0024</v>
       </c>
-      <c r="C169" s="12"/>
-      <c r="D169" s="12"/>
+      <c r="C169" s="15"/>
+      <c r="D169" s="15"/>
     </row>
     <row r="170" ht="14.75" spans="1:4">
-      <c r="A170" s="1">
+      <c r="A170" s="2">
         <v>45292</v>
       </c>
-      <c r="B170" s="12">
+      <c r="B170" s="15">
         <v>0.0587</v>
       </c>
-      <c r="C170" s="12"/>
-      <c r="D170" s="12"/>
+      <c r="C170" s="15"/>
+      <c r="D170" s="15"/>
     </row>
     <row r="171" ht="14.75" spans="1:4">
-      <c r="A171" s="1">
+      <c r="A171" s="2">
         <v>45323</v>
       </c>
-      <c r="B171" s="12">
+      <c r="B171" s="15">
         <v>0.1895</v>
       </c>
-      <c r="C171" s="12"/>
-      <c r="D171" s="12"/>
+      <c r="C171" s="15"/>
+      <c r="D171" s="15"/>
     </row>
     <row r="172" ht="14.75" spans="1:4">
-      <c r="A172" s="1">
+      <c r="A172" s="2">
         <v>45352</v>
       </c>
-      <c r="B172" s="12">
+      <c r="B172" s="15">
         <v>0.2207</v>
       </c>
-      <c r="C172" s="12"/>
-      <c r="D172" s="12"/>
+      <c r="C172" s="15"/>
+      <c r="D172" s="15"/>
     </row>
     <row r="173" ht="14.75" spans="1:4">
-      <c r="A173" s="1">
+      <c r="A173" s="2">
         <v>45383</v>
       </c>
-      <c r="B173" s="12">
+      <c r="B173" s="15">
         <v>0.0343</v>
       </c>
-      <c r="C173" s="12"/>
-      <c r="D173" s="12"/>
+      <c r="C173" s="15"/>
+      <c r="D173" s="15"/>
     </row>
     <row r="174" ht="14.75" spans="1:4">
-      <c r="A174" s="1">
+      <c r="A174" s="2">
         <v>45413</v>
       </c>
-      <c r="B174" s="12">
+      <c r="B174" s="15">
         <v>-0.0156</v>
       </c>
-      <c r="C174" s="12"/>
-      <c r="D174" s="12"/>
+      <c r="C174" s="15"/>
+      <c r="D174" s="15"/>
     </row>
     <row r="175" ht="14.75" spans="1:4">
-      <c r="A175" s="1">
+      <c r="A175" s="2">
         <v>45444</v>
       </c>
-      <c r="B175" s="12">
+      <c r="B175" s="15">
         <v>-0.1354</v>
       </c>
-      <c r="C175" s="12"/>
-      <c r="D175" s="12"/>
+      <c r="C175" s="15"/>
+      <c r="D175" s="15"/>
     </row>
     <row r="176" ht="14.75" spans="1:4">
-      <c r="A176" s="1">
+      <c r="A176" s="2">
         <v>45474</v>
       </c>
-      <c r="B176" s="12">
+      <c r="B176" s="15">
         <v>0.1169</v>
       </c>
-      <c r="C176" s="12"/>
-      <c r="D176" s="12"/>
+      <c r="C176" s="15"/>
+      <c r="D176" s="15"/>
     </row>
     <row r="177" ht="14.75" spans="1:4">
-      <c r="A177" s="1">
+      <c r="A177" s="2">
         <v>45505</v>
       </c>
-      <c r="B177" s="12">
+      <c r="B177" s="15">
         <v>0.1481</v>
       </c>
-      <c r="C177" s="12"/>
-      <c r="D177" s="12"/>
+      <c r="C177" s="15"/>
+      <c r="D177" s="15"/>
     </row>
     <row r="178" ht="14.75" spans="1:4">
-      <c r="A178" s="1">
+      <c r="A178" s="2">
         <v>45536</v>
       </c>
-      <c r="B178" s="12">
+      <c r="B178" s="15">
         <v>0.2549</v>
       </c>
-      <c r="C178" s="12"/>
-      <c r="D178" s="12"/>
+      <c r="C178" s="15"/>
+      <c r="D178" s="15"/>
     </row>
     <row r="179" ht="14.75" spans="1:4">
-      <c r="A179" s="1">
+      <c r="A179" s="2">
         <v>45566</v>
       </c>
-      <c r="B179" s="12">
+      <c r="B179" s="15">
         <v>0.2231</v>
       </c>
-      <c r="C179" s="12"/>
-      <c r="D179" s="12"/>
+      <c r="C179" s="15"/>
+      <c r="D179" s="15"/>
     </row>
     <row r="180" ht="14.75" spans="1:4">
-      <c r="A180" s="1">
+      <c r="A180" s="2">
         <v>45597</v>
       </c>
-      <c r="B180" s="12">
+      <c r="B180" s="15">
         <v>0.1335</v>
       </c>
-      <c r="C180" s="12"/>
-      <c r="D180" s="12"/>
+      <c r="C180" s="15"/>
+      <c r="D180" s="15"/>
     </row>
     <row r="181" ht="14.75" spans="1:4">
-      <c r="A181" s="1">
+      <c r="A181" s="2">
         <v>45627</v>
       </c>
-      <c r="B181" s="12">
+      <c r="B181" s="15">
         <v>0.0415</v>
       </c>
-      <c r="C181" s="12"/>
-      <c r="D181" s="12"/>
+      <c r="C181" s="15"/>
+      <c r="D181" s="15"/>
     </row>
     <row r="182" ht="14.75" spans="1:4">
-      <c r="A182" s="1">
+      <c r="A182" s="2">
         <v>45658</v>
       </c>
-      <c r="B182" s="12">
+      <c r="B182" s="15">
         <v>-0.0074</v>
       </c>
-      <c r="C182" s="12"/>
-      <c r="D182" s="12"/>
+      <c r="C182" s="15"/>
+      <c r="D182" s="15"/>
     </row>
     <row r="183" ht="14.75" spans="1:4">
-      <c r="A183" s="1">
+      <c r="A183" s="2">
         <v>45689</v>
       </c>
-      <c r="B183" s="12">
+      <c r="B183" s="15">
         <v>0.2489</v>
       </c>
-      <c r="C183" s="12"/>
-      <c r="D183" s="12"/>
+      <c r="C183" s="15"/>
+      <c r="D183" s="15"/>
     </row>
     <row r="184" ht="14.75" spans="1:4">
-      <c r="A184" s="1">
+      <c r="A184" s="2">
         <v>45717</v>
       </c>
-      <c r="B184" s="12">
+      <c r="B184" s="15">
         <v>-0.0711</v>
       </c>
-      <c r="C184" s="12"/>
-      <c r="D184" s="12"/>
+      <c r="C184" s="15"/>
+      <c r="D184" s="15"/>
     </row>
     <row r="185" ht="14.75" spans="1:4">
-      <c r="A185" s="1">
+      <c r="A185" s="2">
         <v>45748</v>
       </c>
-      <c r="B185" s="12">
+      <c r="B185" s="15">
         <v>0.0526</v>
       </c>
-      <c r="C185" s="12"/>
-      <c r="D185" s="12"/>
+      <c r="C185" s="15"/>
+      <c r="D185" s="15"/>
     </row>
     <row r="186" ht="14.75" spans="1:4">
-      <c r="A186" s="1">
+      <c r="A186" s="2">
         <v>45778</v>
       </c>
-      <c r="B186" s="12">
+      <c r="B186" s="15">
         <v>0.0431</v>
       </c>
-      <c r="C186" s="12"/>
-      <c r="D186" s="12"/>
+      <c r="C186" s="15"/>
+      <c r="D186" s="15"/>
     </row>
     <row r="187" ht="14.75" spans="1:4">
-      <c r="A187" s="1">
+      <c r="A187" s="2">
         <v>45809</v>
       </c>
-      <c r="B187" s="12">
+      <c r="B187" s="15">
         <v>0.1423</v>
       </c>
-      <c r="C187" s="12"/>
-      <c r="D187" s="12"/>
+      <c r="C187" s="15"/>
+      <c r="D187" s="15"/>
     </row>
     <row r="188" ht="14.75" spans="1:4">
-      <c r="A188" s="1">
+      <c r="A188" s="2">
         <v>45839</v>
       </c>
-      <c r="B188" s="12">
+      <c r="B188" s="15">
         <v>0.0876</v>
       </c>
-      <c r="C188" s="12"/>
-      <c r="D188" s="12"/>
+      <c r="C188" s="15"/>
+      <c r="D188" s="15"/>
     </row>
     <row r="189" ht="14.75" spans="1:4">
-      <c r="A189" s="1">
+      <c r="A189" s="2">
         <v>45870</v>
       </c>
-      <c r="B189" s="12">
+      <c r="B189" s="15">
         <v>-0.0326</v>
       </c>
-      <c r="C189" s="12"/>
-      <c r="D189" s="12"/>
+      <c r="C189" s="15"/>
+      <c r="D189" s="15"/>
     </row>
     <row r="190" ht="14.75" spans="1:4">
-      <c r="A190" s="1">
+      <c r="A190" s="2">
         <v>45901</v>
       </c>
-      <c r="B190" s="12">
+      <c r="B190" s="15">
         <v>0.1218</v>
       </c>
-      <c r="C190" s="12"/>
-      <c r="D190" s="12"/>
+      <c r="C190" s="15"/>
+      <c r="D190" s="15"/>
     </row>
     <row r="191" ht="14.75" spans="1:4">
-      <c r="A191" s="1">
+      <c r="A191" s="2">
         <v>45931</v>
       </c>
-      <c r="B191" s="12">
+      <c r="B191" s="15">
         <v>0.0044</v>
       </c>
-      <c r="C191" s="12"/>
-      <c r="D191" s="12"/>
+      <c r="C191" s="15"/>
+      <c r="D191" s="15"/>
     </row>
     <row r="192" ht="14.75" spans="1:4">
-      <c r="A192" s="1">
+      <c r="A192" s="2">
         <v>45962</v>
       </c>
-      <c r="B192" s="12">
+      <c r="B192" s="15">
         <v>0.0793</v>
       </c>
-      <c r="C192" s="12"/>
-      <c r="D192" s="12"/>
+      <c r="C192" s="15"/>
+      <c r="D192" s="15"/>
     </row>
     <row r="193" ht="14.75" spans="1:4">
-      <c r="A193" s="13">
+      <c r="A193" s="16">
         <v>45992</v>
       </c>
-      <c r="B193" s="14">
+      <c r="B193" s="17">
         <v>-0.0685</v>
       </c>
-      <c r="C193" s="14"/>
-      <c r="D193" s="14"/>
+      <c r="C193" s="17"/>
+      <c r="D193" s="17"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5926,7 +5985,7 @@
       </c>
     </row>
     <row r="2" ht="14.75" spans="1:21">
-      <c r="A2" s="1">
+      <c r="A2" s="2">
         <v>40179</v>
       </c>
       <c r="B2">
@@ -5977,7 +6036,7 @@
       <c r="Q2">
         <v>-0.0074</v>
       </c>
-      <c r="R2" s="10" cm="1">
+      <c r="R2" s="13" cm="1">
         <f t="array" ref="R2">PRODUCT(B2:Q2+1)-1</f>
         <v>0.194840242744342</v>
       </c>
@@ -5985,7 +6044,7 @@
         <f>SUM(B2:Q2)</f>
         <v>0.1812</v>
       </c>
-      <c r="T2" s="1">
+      <c r="T2" s="2">
         <v>40179</v>
       </c>
       <c r="U2">
@@ -5994,7 +6053,7 @@
       </c>
     </row>
     <row r="3" ht="14.75" spans="1:21">
-      <c r="A3" s="1">
+      <c r="A3" s="2">
         <v>40210</v>
       </c>
       <c r="B3">
@@ -6053,7 +6112,7 @@
         <f t="shared" ref="S3:S13" si="0">SUM(B3:Q3)</f>
         <v>1.4082</v>
       </c>
-      <c r="T3" s="1">
+      <c r="T3" s="2">
         <v>40210</v>
       </c>
       <c r="U3">
@@ -6062,7 +6121,7 @@
       </c>
     </row>
     <row r="4" ht="14.75" spans="1:21">
-      <c r="A4" s="1">
+      <c r="A4" s="2">
         <v>40238</v>
       </c>
       <c r="B4">
@@ -6121,7 +6180,7 @@
         <f t="shared" si="0"/>
         <v>1.3299</v>
       </c>
-      <c r="T4" s="1">
+      <c r="T4" s="2">
         <v>40238</v>
       </c>
       <c r="U4">
@@ -6130,7 +6189,7 @@
       </c>
     </row>
     <row r="5" ht="14.75" spans="1:21">
-      <c r="A5" s="1">
+      <c r="A5" s="2">
         <v>40269</v>
       </c>
       <c r="B5">
@@ -6181,7 +6240,7 @@
       <c r="Q5">
         <v>0.0526</v>
       </c>
-      <c r="R5" s="11" cm="1">
+      <c r="R5" s="14" cm="1">
         <f t="array" ref="R5">PRODUCT(B5:Q5+1)-1</f>
         <v>0.323510793037694</v>
       </c>
@@ -6189,7 +6248,7 @@
         <f t="shared" si="0"/>
         <v>0.2872</v>
       </c>
-      <c r="T5" s="1">
+      <c r="T5" s="2">
         <v>40269</v>
       </c>
       <c r="U5">
@@ -6198,7 +6257,7 @@
       </c>
     </row>
     <row r="6" ht="14.75" spans="1:21">
-      <c r="A6" s="1">
+      <c r="A6" s="2">
         <v>40299</v>
       </c>
       <c r="B6">
@@ -6249,7 +6308,7 @@
       <c r="Q6">
         <v>0.0431</v>
       </c>
-      <c r="R6" s="11" cm="1">
+      <c r="R6" s="14" cm="1">
         <f t="array" ref="R6">PRODUCT(B6:Q6+1)-1</f>
         <v>1.28723547337183</v>
       </c>
@@ -6257,7 +6316,7 @@
         <f t="shared" si="0"/>
         <v>0.955</v>
       </c>
-      <c r="T6" s="1">
+      <c r="T6" s="2">
         <v>40299</v>
       </c>
       <c r="U6">
@@ -6266,7 +6325,7 @@
       </c>
     </row>
     <row r="7" ht="14.75" spans="1:21">
-      <c r="A7" s="1">
+      <c r="A7" s="2">
         <v>40330</v>
       </c>
       <c r="B7">
@@ -6317,7 +6376,7 @@
       <c r="Q7">
         <v>0.1423</v>
       </c>
-      <c r="R7" s="11" cm="1">
+      <c r="R7" s="14" cm="1">
         <f t="array" ref="R7">PRODUCT(B7:Q7+1)-1</f>
         <v>0.595591661283158</v>
       </c>
@@ -6325,7 +6384,7 @@
         <f t="shared" si="0"/>
         <v>0.5492</v>
       </c>
-      <c r="T7" s="1">
+      <c r="T7" s="2">
         <v>40330</v>
       </c>
       <c r="U7">
@@ -6334,7 +6393,7 @@
       </c>
     </row>
     <row r="8" ht="14.75" spans="1:21">
-      <c r="A8" s="1">
+      <c r="A8" s="2">
         <v>40360</v>
       </c>
       <c r="B8">
@@ -6393,7 +6452,7 @@
         <f t="shared" si="0"/>
         <v>1.4965</v>
       </c>
-      <c r="T8" s="1">
+      <c r="T8" s="2">
         <v>40360</v>
       </c>
       <c r="U8">
@@ -6402,7 +6461,7 @@
       </c>
     </row>
     <row r="9" ht="14.75" spans="1:21">
-      <c r="A9" s="1">
+      <c r="A9" s="2">
         <v>40391</v>
       </c>
       <c r="B9">
@@ -6461,7 +6520,7 @@
         <f t="shared" si="0"/>
         <v>1.3491</v>
       </c>
-      <c r="T9" s="1">
+      <c r="T9" s="2">
         <v>40391</v>
       </c>
       <c r="U9">
@@ -6470,7 +6529,7 @@
       </c>
     </row>
     <row r="10" ht="14.75" spans="1:21">
-      <c r="A10" s="1">
+      <c r="A10" s="2">
         <v>40422</v>
       </c>
       <c r="B10">
@@ -6529,7 +6588,7 @@
         <f t="shared" si="0"/>
         <v>0.8786</v>
       </c>
-      <c r="T10" s="1">
+      <c r="T10" s="2">
         <v>40422</v>
       </c>
       <c r="U10">
@@ -6538,7 +6597,7 @@
       </c>
     </row>
     <row r="11" ht="14.75" spans="1:21">
-      <c r="A11" s="1">
+      <c r="A11" s="2">
         <v>40452</v>
       </c>
       <c r="B11">
@@ -6597,7 +6656,7 @@
         <f t="shared" si="0"/>
         <v>0.8179</v>
       </c>
-      <c r="T11" s="1">
+      <c r="T11" s="2">
         <v>40452</v>
       </c>
       <c r="U11">
@@ -6606,7 +6665,7 @@
       </c>
     </row>
     <row r="12" ht="14.75" spans="1:21">
-      <c r="A12" s="1">
+      <c r="A12" s="2">
         <v>40483</v>
       </c>
       <c r="B12">
@@ -6665,7 +6724,7 @@
         <f t="shared" si="0"/>
         <v>1.0945</v>
       </c>
-      <c r="T12" s="1">
+      <c r="T12" s="2">
         <v>40483</v>
       </c>
       <c r="U12">
@@ -6674,7 +6733,7 @@
       </c>
     </row>
     <row r="13" spans="1:21">
-      <c r="A13" s="1">
+      <c r="A13" s="2">
         <v>40513</v>
       </c>
       <c r="B13">
@@ -6733,7 +6792,7 @@
         <f t="shared" si="0"/>
         <v>0.368</v>
       </c>
-      <c r="T13" s="1">
+      <c r="T13" s="2">
         <v>40513</v>
       </c>
       <c r="U13">
@@ -6742,71 +6801,71 @@
       </c>
     </row>
     <row r="14" spans="2:18">
-      <c r="B14" s="7">
+      <c r="B14" s="10">
         <f>(1+B2)*(1+B3)*(1+B4)*(1+B5)*(1+B6)*(1+B7)*(1+B8)*(1+B9)*(1+B10)*(1+B11)*(1+B12)*(1+B13)-1</f>
         <v>0.653614174322446</v>
       </c>
-      <c r="C14" s="7">
+      <c r="C14" s="10">
         <f t="shared" ref="C14:Q14" si="2">(1+C2)*(1+C3)*(1+C4)*(1+C5)*(1+C6)*(1+C7)*(1+C8)*(1+C9)*(1+C10)*(1+C11)*(1+C12)*(1+C13)-1</f>
         <v>-0.0855664203647523</v>
       </c>
-      <c r="D14" s="7">
+      <c r="D14" s="10">
         <f t="shared" si="2"/>
         <v>0.0384573958480514</v>
       </c>
-      <c r="E14" s="7">
+      <c r="E14" s="10">
         <f t="shared" si="2"/>
         <v>0.765405002524292</v>
       </c>
-      <c r="F14" s="7">
+      <c r="F14" s="10">
         <f t="shared" si="2"/>
         <v>1.19935720490706</v>
       </c>
-      <c r="G14" s="7">
+      <c r="G14" s="10">
         <f t="shared" si="2"/>
         <v>5.98281172803228</v>
       </c>
-      <c r="H14" s="7">
+      <c r="H14" s="10">
         <f t="shared" si="2"/>
         <v>1.09694188883488</v>
       </c>
-      <c r="I14" s="7">
+      <c r="I14" s="10">
         <f t="shared" si="2"/>
         <v>0.0775695328691113</v>
       </c>
-      <c r="J14" s="7">
+      <c r="J14" s="10">
         <f t="shared" si="2"/>
         <v>0.472825224873327</v>
       </c>
-      <c r="K14" s="7">
+      <c r="K14" s="10">
         <f t="shared" si="2"/>
         <v>0.745848408003567</v>
       </c>
-      <c r="L14" s="7">
+      <c r="L14" s="10">
         <f t="shared" si="2"/>
         <v>0.501877778017195</v>
       </c>
-      <c r="M14" s="7">
+      <c r="M14" s="10">
         <f t="shared" si="2"/>
         <v>0.660960857965097</v>
       </c>
-      <c r="N14" s="7">
+      <c r="N14" s="10">
         <f t="shared" si="2"/>
         <v>1.99686467587207</v>
       </c>
-      <c r="O14" s="7">
+      <c r="O14" s="10">
         <f t="shared" si="2"/>
         <v>0.495057586521658</v>
       </c>
-      <c r="P14" s="7">
+      <c r="P14" s="10">
         <f t="shared" si="2"/>
         <v>2.14431144891796</v>
       </c>
-      <c r="Q14" s="7">
+      <c r="Q14" s="10">
         <f t="shared" si="2"/>
         <v>0.721324876500654</v>
       </c>
-      <c r="R14" s="7"/>
+      <c r="R14" s="10"/>
     </row>
     <row r="15" spans="2:17">
       <c r="B15">
@@ -6905,51 +6964,52 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Q28"/>
+  <dimension ref="A1:Q29"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="12.5363636363636" customWidth="1"/>
     <col min="2" max="13" width="8.54545454545454" customWidth="1"/>
     <col min="14" max="14" width="13.9636363636364" customWidth="1"/>
     <col min="15" max="15" width="12.2727272727273" customWidth="1"/>
+    <col min="16" max="16" width="7.08181818181818" customWidth="1"/>
     <col min="17" max="17" width="9.54545454545454"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:15">
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" s="2" t="s">
         <v>11</v>
       </c>
       <c r="N1" t="s">
@@ -6960,7 +7020,7 @@
       </c>
     </row>
     <row r="2" spans="1:16">
-      <c r="A2">
+      <c r="A2" s="3">
         <v>2010</v>
       </c>
       <c r="B2">
@@ -6999,20 +7059,20 @@
       <c r="M2">
         <v>-0.0207</v>
       </c>
-      <c r="N2" s="7">
+      <c r="N2" s="10">
         <f>(1+B2)*(1+C2)*(1+D2)*(1+E2)*(1+F2)*(1+G2)*(1+H2)*(1+I2)*(1+J2)*(1+K2)*(1+L2)*(1+M2)-1</f>
         <v>0.653614174322446</v>
       </c>
-      <c r="O2" s="6">
+      <c r="O2" s="9">
         <f>N2</f>
         <v>0.653614174322446</v>
       </c>
-      <c r="P2">
+      <c r="P2" s="3">
         <v>2010</v>
       </c>
     </row>
     <row r="3" spans="1:16">
-      <c r="A3">
+      <c r="A3" s="3">
         <v>2011</v>
       </c>
       <c r="B3">
@@ -7051,20 +7111,20 @@
       <c r="M3">
         <v>-0.1536</v>
       </c>
-      <c r="N3" s="7">
+      <c r="N3" s="10">
         <f>(1+B3)*(1+C3)*(1+D3)*(1+E3)*(1+F3)*(1+G3)*(1+H3)*(1+I3)*(1+J3)*(1+K3)*(1+L3)*(1+M3)-1</f>
         <v>-0.0855664203647523</v>
       </c>
-      <c r="O3" s="6">
-        <f t="shared" ref="O3:O17" si="0">N3</f>
+      <c r="O3" s="9">
+        <f t="shared" ref="O3:O18" si="0">N3</f>
         <v>-0.0855664203647523</v>
       </c>
-      <c r="P3">
+      <c r="P3" s="3">
         <v>2011</v>
       </c>
     </row>
     <row r="4" spans="1:16">
-      <c r="A4">
+      <c r="A4" s="3">
         <v>2012</v>
       </c>
       <c r="B4">
@@ -7103,20 +7163,20 @@
       <c r="M4">
         <v>0.2375</v>
       </c>
-      <c r="N4" s="7">
+      <c r="N4" s="10">
         <f t="shared" ref="N2:N17" si="1">(1+B4)*(1+C4)*(1+D4)*(1+E4)*(1+F4)*(1+G4)*(1+H4)*(1+I4)*(1+J4)*(1+K4)*(1+L4)*(1+M4)-1</f>
         <v>0.0384573958480514</v>
       </c>
-      <c r="O4" s="6">
+      <c r="O4" s="9">
         <f t="shared" si="0"/>
         <v>0.0384573958480514</v>
       </c>
-      <c r="P4">
+      <c r="P4" s="3">
         <v>2012</v>
       </c>
     </row>
     <row r="5" spans="1:16">
-      <c r="A5">
+      <c r="A5" s="3">
         <v>2013</v>
       </c>
       <c r="B5">
@@ -7155,20 +7215,20 @@
       <c r="M5">
         <v>0.0207</v>
       </c>
-      <c r="N5" s="7">
+      <c r="N5" s="10">
         <f t="shared" si="1"/>
         <v>0.765405002524292</v>
       </c>
-      <c r="O5" s="6">
+      <c r="O5" s="9">
         <f t="shared" si="0"/>
         <v>0.765405002524292</v>
       </c>
-      <c r="P5">
+      <c r="P5" s="3">
         <v>2013</v>
       </c>
     </row>
     <row r="6" spans="1:16">
-      <c r="A6">
+      <c r="A6" s="3">
         <v>2014</v>
       </c>
       <c r="B6">
@@ -7207,20 +7267,20 @@
       <c r="M6">
         <v>-0.1353</v>
       </c>
-      <c r="N6" s="7">
+      <c r="N6" s="10">
         <f t="shared" si="1"/>
         <v>1.19935720490706</v>
       </c>
-      <c r="O6" s="6">
+      <c r="O6" s="9">
         <f t="shared" si="0"/>
         <v>1.19935720490706</v>
       </c>
-      <c r="P6">
+      <c r="P6" s="3">
         <v>2014</v>
       </c>
     </row>
     <row r="7" spans="1:16">
-      <c r="A7">
+      <c r="A7" s="3">
         <v>2015</v>
       </c>
       <c r="B7">
@@ -7259,20 +7319,20 @@
       <c r="M7">
         <v>0.2392</v>
       </c>
-      <c r="N7" s="7">
+      <c r="N7" s="10">
         <f t="shared" si="1"/>
         <v>5.98281172803228</v>
       </c>
-      <c r="O7" s="6">
+      <c r="O7" s="9">
         <f t="shared" si="0"/>
         <v>5.98281172803228</v>
       </c>
-      <c r="P7">
+      <c r="P7" s="3">
         <v>2015</v>
       </c>
     </row>
     <row r="8" spans="1:16">
-      <c r="A8">
+      <c r="A8" s="3">
         <v>2016</v>
       </c>
       <c r="B8">
@@ -7311,20 +7371,20 @@
       <c r="M8">
         <v>0.12</v>
       </c>
-      <c r="N8" s="7">
+      <c r="N8" s="10">
         <f t="shared" si="1"/>
         <v>1.09694188883488</v>
       </c>
-      <c r="O8" s="6">
+      <c r="O8" s="9">
         <f t="shared" si="0"/>
         <v>1.09694188883488</v>
       </c>
-      <c r="P8">
+      <c r="P8" s="3">
         <v>2016</v>
       </c>
     </row>
     <row r="9" spans="1:16">
-      <c r="A9">
+      <c r="A9" s="3">
         <v>2017</v>
       </c>
       <c r="B9">
@@ -7363,20 +7423,20 @@
       <c r="M9">
         <v>-0.0392</v>
       </c>
-      <c r="N9" s="7">
+      <c r="N9" s="10">
         <f t="shared" si="1"/>
         <v>0.0775695328691113</v>
       </c>
-      <c r="O9" s="6">
+      <c r="O9" s="9">
         <f t="shared" si="0"/>
         <v>0.0775695328691113</v>
       </c>
-      <c r="P9">
+      <c r="P9" s="3">
         <v>2017</v>
       </c>
     </row>
     <row r="10" spans="1:16">
-      <c r="A10">
+      <c r="A10" s="3">
         <v>2018</v>
       </c>
       <c r="B10">
@@ -7415,20 +7475,20 @@
       <c r="M10">
         <v>-0.0448</v>
       </c>
-      <c r="N10" s="7">
+      <c r="N10" s="10">
         <f t="shared" si="1"/>
         <v>0.472825224873327</v>
       </c>
-      <c r="O10" s="6">
+      <c r="O10" s="9">
         <f t="shared" si="0"/>
         <v>0.472825224873327</v>
       </c>
-      <c r="P10">
+      <c r="P10" s="3">
         <v>2018</v>
       </c>
     </row>
     <row r="11" spans="1:16">
-      <c r="A11">
+      <c r="A11" s="3">
         <v>2019</v>
       </c>
       <c r="B11">
@@ -7467,20 +7527,20 @@
       <c r="M11">
         <v>0.1302</v>
       </c>
-      <c r="N11" s="7">
+      <c r="N11" s="10">
         <f t="shared" si="1"/>
         <v>0.745848408003567</v>
       </c>
-      <c r="O11" s="6">
+      <c r="O11" s="9">
         <f t="shared" si="0"/>
         <v>0.745848408003567</v>
       </c>
-      <c r="P11">
+      <c r="P11" s="3">
         <v>2019</v>
       </c>
     </row>
     <row r="12" spans="1:16">
-      <c r="A12">
+      <c r="A12" s="3">
         <v>2020</v>
       </c>
       <c r="B12">
@@ -7519,20 +7579,20 @@
       <c r="M12">
         <v>-0.112</v>
       </c>
-      <c r="N12" s="7">
+      <c r="N12" s="10">
         <f t="shared" si="1"/>
         <v>0.501877778017195</v>
       </c>
-      <c r="O12" s="6">
+      <c r="O12" s="9">
         <f t="shared" si="0"/>
         <v>0.501877778017195</v>
       </c>
-      <c r="P12">
+      <c r="P12" s="3">
         <v>2020</v>
       </c>
     </row>
     <row r="13" spans="1:16">
-      <c r="A13">
+      <c r="A13" s="3">
         <v>2021</v>
       </c>
       <c r="B13">
@@ -7571,20 +7631,20 @@
       <c r="M13">
         <v>0.1123</v>
       </c>
-      <c r="N13" s="7">
+      <c r="N13" s="10">
         <f t="shared" si="1"/>
         <v>0.660960857965097</v>
       </c>
-      <c r="O13" s="6">
+      <c r="O13" s="9">
         <f t="shared" si="0"/>
         <v>0.660960857965097</v>
       </c>
-      <c r="P13">
+      <c r="P13" s="3">
         <v>2021</v>
       </c>
     </row>
     <row r="14" spans="1:16">
-      <c r="A14">
+      <c r="A14" s="3">
         <v>2022</v>
       </c>
       <c r="B14">
@@ -7623,20 +7683,20 @@
       <c r="M14">
         <v>0.0431</v>
       </c>
-      <c r="N14" s="7">
+      <c r="N14" s="10">
         <f t="shared" si="1"/>
         <v>1.99686467587207</v>
       </c>
-      <c r="O14" s="6">
+      <c r="O14" s="9">
         <f t="shared" si="0"/>
         <v>1.99686467587207</v>
       </c>
-      <c r="P14">
+      <c r="P14" s="3">
         <v>2022</v>
       </c>
     </row>
     <row r="15" spans="1:16">
-      <c r="A15">
+      <c r="A15" s="3">
         <v>2023</v>
       </c>
       <c r="B15">
@@ -7675,20 +7735,20 @@
       <c r="M15">
         <v>-0.0024</v>
       </c>
-      <c r="N15" s="7">
+      <c r="N15" s="10">
         <f t="shared" si="1"/>
         <v>0.495057586521658</v>
       </c>
-      <c r="O15" s="6">
+      <c r="O15" s="9">
         <f t="shared" si="0"/>
         <v>0.495057586521658</v>
       </c>
-      <c r="P15">
+      <c r="P15" s="3">
         <v>2023</v>
       </c>
     </row>
     <row r="16" spans="1:16">
-      <c r="A16">
+      <c r="A16" s="3">
         <v>2024</v>
       </c>
       <c r="B16">
@@ -7727,20 +7787,20 @@
       <c r="M16">
         <v>0.0415</v>
       </c>
-      <c r="N16" s="7">
+      <c r="N16" s="10">
         <f t="shared" si="1"/>
         <v>2.14431144891796</v>
       </c>
-      <c r="O16" s="6">
+      <c r="O16" s="9">
         <f t="shared" si="0"/>
         <v>2.14431144891796</v>
       </c>
-      <c r="P16">
+      <c r="P16" s="3">
         <v>2024</v>
       </c>
     </row>
     <row r="17" spans="1:16">
-      <c r="A17">
+      <c r="A17" s="3">
         <v>2025</v>
       </c>
       <c r="B17">
@@ -7779,433 +7839,480 @@
       <c r="M17">
         <v>-0.0685</v>
       </c>
-      <c r="N17" s="7">
-        <f t="shared" si="1"/>
+      <c r="N17" s="10">
+        <f>(1+B17)*(1+C17)*(1+D17)*(1+E17)*(1+F17)*(1+G17)*(1+H17)*(1+I17)*(1+J17)*(1+K17)*(1+L17)*(1+M17)-1</f>
         <v>0.721324876500654</v>
       </c>
-      <c r="O17" s="6">
+      <c r="O17" s="9">
         <f>N17</f>
         <v>0.721324876500654</v>
       </c>
-      <c r="P17">
+      <c r="P17" s="3">
         <v>2025</v>
       </c>
     </row>
-    <row r="18" ht="14.75" spans="1:15">
-      <c r="A18" t="s">
+    <row r="18" ht="14.75" spans="1:16">
+      <c r="A18" s="3"/>
+      <c r="N18" s="10"/>
+      <c r="O18" s="9"/>
+      <c r="P18" s="3"/>
+    </row>
+    <row r="19" ht="24" customHeight="1" spans="1:15">
+      <c r="A19" t="s">
         <v>14</v>
       </c>
-      <c r="B18" s="2" cm="1">
-        <f t="array" ref="B18">PRODUCT(B2:B17+1)-1</f>
+      <c r="B19" s="4" cm="1">
+        <f t="array" ref="B19">PRODUCT(B2:B17+1)-1</f>
         <v>0.194840242744342</v>
       </c>
-      <c r="C18" s="3" cm="1">
-        <f t="array" ref="C18">PRODUCT(C2:C17+1)-1</f>
+      <c r="C19" s="5" cm="1">
+        <f t="array" ref="C19">PRODUCT(C2:C17+1)-1</f>
         <v>2.74859148623959</v>
       </c>
-      <c r="D18" s="3" cm="1">
-        <f t="array" ref="D18">PRODUCT(D2:D17+1)-1</f>
+      <c r="D19" s="5" cm="1">
+        <f t="array" ref="D19">PRODUCT(D2:D17+1)-1</f>
         <v>2.22374556844742</v>
       </c>
-      <c r="E18" s="4" cm="1">
-        <f t="array" ref="E18">PRODUCT(E2:E17+1)-1</f>
+      <c r="E19" s="6" cm="1">
+        <f t="array" ref="E19">PRODUCT(E2:E17+1)-1</f>
         <v>0.323510793037694</v>
       </c>
-      <c r="F18" s="4" cm="1">
-        <f t="array" ref="F18">PRODUCT(F2:F17+1)-1</f>
+      <c r="F19" s="6" cm="1">
+        <f t="array" ref="F19">PRODUCT(F2:F17+1)-1</f>
         <v>1.28723547337183</v>
       </c>
-      <c r="G18" s="4" cm="1">
-        <f t="array" ref="G18">PRODUCT(G2:G17+1)-1</f>
+      <c r="G19" s="6" cm="1">
+        <f t="array" ref="G19">PRODUCT(G2:G17+1)-1</f>
         <v>0.595591661283158</v>
       </c>
-      <c r="H18" s="3" cm="1">
-        <f t="array" ref="H18">PRODUCT(H2:H17+1)-1</f>
+      <c r="H19" s="5" cm="1">
+        <f t="array" ref="H19">PRODUCT(H2:H17+1)-1</f>
         <v>2.77618998463726</v>
       </c>
-      <c r="I18" s="3" cm="1">
-        <f t="array" ref="I18">PRODUCT(I2:I17+1)-1</f>
+      <c r="I19" s="5" cm="1">
+        <f t="array" ref="I19">PRODUCT(I2:I17+1)-1</f>
         <v>2.44214606607075</v>
       </c>
-      <c r="J18" s="3" cm="1">
-        <f t="array" ref="J18">PRODUCT(J2:J17+1)-1</f>
+      <c r="J19" s="5" cm="1">
+        <f t="array" ref="J19">PRODUCT(J2:J17+1)-1</f>
         <v>1.20998365758364</v>
       </c>
-      <c r="K18" s="3" cm="1">
-        <f t="array" ref="K18">PRODUCT(K2:K17+1)-1</f>
+      <c r="K19" s="5" cm="1">
+        <f t="array" ref="K19">PRODUCT(K2:K17+1)-1</f>
         <v>1.1322825420196</v>
       </c>
-      <c r="L18" s="3" cm="1">
-        <f t="array" ref="L18">PRODUCT(L2:L17+1)-1</f>
+      <c r="L19" s="5" cm="1">
+        <f t="array" ref="L19">PRODUCT(L2:L17+1)-1</f>
         <v>1.69541069581852</v>
       </c>
-      <c r="M18" s="3" cm="1">
-        <f t="array" ref="M18">PRODUCT(M2:M17+1)-1</f>
+      <c r="M19" s="5" cm="1">
+        <f t="array" ref="M19">PRODUCT(M2:M17+1)-1</f>
         <v>0.299575907581825</v>
       </c>
-      <c r="N18" s="8" cm="1">
-        <f t="array" ref="N18">PRODUCT(N2:N17+1)-1</f>
-        <v>14962.8167474189</v>
-      </c>
-      <c r="O18" s="9">
-        <f>N18</f>
-        <v>14962.8167474189</v>
-      </c>
-    </row>
-    <row r="19" spans="2:13">
-      <c r="B19" s="1" t="s">
+      <c r="N19" s="11" cm="1">
+        <f t="array" ref="N19">PRODUCT(N2:N17+1)-1</f>
+        <v>14962.816747419</v>
+      </c>
+      <c r="O19" s="12">
+        <f>N19</f>
+        <v>14962.816747419</v>
+      </c>
+    </row>
+    <row r="20" ht="14.75" spans="2:13">
+      <c r="B20" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="C19" s="1" t="s">
+      <c r="C20" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="D19" s="1" t="s">
+      <c r="D20" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="E19" s="1" t="s">
+      <c r="E20" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="F19" s="1" t="s">
+      <c r="F20" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="G19" s="1" t="s">
+      <c r="G20" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="H19" s="1" t="s">
+      <c r="H20" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="I19" s="1" t="s">
+      <c r="I20" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="J19" s="1" t="s">
+      <c r="J20" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="K19" s="1" t="s">
+      <c r="K20" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="L19" s="1" t="s">
+      <c r="L20" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="M19" s="1" t="s">
+      <c r="M20" s="7" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="20" spans="1:13">
-      <c r="A20" t="s">
+    <row r="21" spans="1:13">
+      <c r="A21" t="s">
         <v>15</v>
       </c>
-      <c r="B20">
+      <c r="B21">
         <f>COUNTIF(B2:B17,"&lt;0")</f>
         <v>5</v>
       </c>
-      <c r="C20">
-        <f t="shared" ref="B20:M20" si="2">COUNTIF(C2:C17,"&lt;0")</f>
+      <c r="C21">
+        <f>COUNTIF(C2:C17,"&lt;0")</f>
         <v>0</v>
       </c>
-      <c r="D20">
+      <c r="D21">
+        <f t="shared" ref="B21:M21" si="2">COUNTIF(D2:D17,"&lt;0")</f>
+        <v>5</v>
+      </c>
+      <c r="E21">
+        <f t="shared" si="2"/>
+        <v>4</v>
+      </c>
+      <c r="F21">
         <f t="shared" si="2"/>
         <v>5</v>
       </c>
-      <c r="E20">
+      <c r="G21">
+        <f t="shared" si="2"/>
+        <v>5</v>
+      </c>
+      <c r="H21">
+        <f t="shared" si="2"/>
+        <v>5</v>
+      </c>
+      <c r="I21">
+        <f t="shared" si="2"/>
+        <v>5</v>
+      </c>
+      <c r="J21">
         <f t="shared" si="2"/>
         <v>4</v>
       </c>
-      <c r="F20">
-        <f t="shared" si="2"/>
-        <v>5</v>
-      </c>
-      <c r="G20">
-        <f t="shared" si="2"/>
-        <v>5</v>
-      </c>
-      <c r="H20">
-        <f t="shared" si="2"/>
-        <v>5</v>
-      </c>
-      <c r="I20">
-        <f t="shared" si="2"/>
-        <v>5</v>
-      </c>
-      <c r="J20">
+      <c r="K21">
         <f t="shared" si="2"/>
         <v>4</v>
       </c>
-      <c r="K20">
+      <c r="L21">
         <f t="shared" si="2"/>
         <v>4</v>
       </c>
-      <c r="L20">
-        <f t="shared" si="2"/>
-        <v>4</v>
-      </c>
-      <c r="M20">
+      <c r="M21">
         <f t="shared" si="2"/>
         <v>8</v>
       </c>
     </row>
-    <row r="21" spans="1:13">
-      <c r="A21" t="s">
+    <row r="22" spans="1:13">
+      <c r="A22" t="s">
         <v>16</v>
       </c>
-      <c r="B21">
+      <c r="B22">
         <f>COUNTIF(B2:B17,"&gt;0.1")</f>
         <v>0</v>
       </c>
-      <c r="C21">
-        <f t="shared" ref="C21:M21" si="3">COUNTIF(C2:C17,"&gt;0.1")</f>
+      <c r="C22">
+        <f t="shared" ref="C22:M22" si="3">COUNTIF(C2:C17,"&gt;0.1")</f>
         <v>5</v>
       </c>
-      <c r="D21">
+      <c r="D22">
         <f t="shared" si="3"/>
         <v>6</v>
       </c>
-      <c r="E21">
+      <c r="E22">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F21">
+      <c r="F22">
         <f t="shared" si="3"/>
         <v>3</v>
       </c>
-      <c r="G21">
+      <c r="G22">
+        <f>COUNTIF(G2:G17,"&gt;0.1")</f>
+        <v>4</v>
+      </c>
+      <c r="H22">
+        <f t="shared" si="3"/>
+        <v>8</v>
+      </c>
+      <c r="I22">
+        <f t="shared" si="3"/>
+        <v>8</v>
+      </c>
+      <c r="J22">
         <f t="shared" si="3"/>
         <v>4</v>
       </c>
-      <c r="H21">
-        <f t="shared" si="3"/>
-        <v>8</v>
-      </c>
-      <c r="I21">
-        <f t="shared" si="3"/>
-        <v>8</v>
-      </c>
-      <c r="J21">
-        <f t="shared" si="3"/>
-        <v>4</v>
-      </c>
-      <c r="K21">
+      <c r="K22">
         <f t="shared" si="3"/>
         <v>3</v>
       </c>
-      <c r="L21">
+      <c r="L22">
         <f t="shared" si="3"/>
         <v>7</v>
       </c>
-      <c r="M21">
+      <c r="M22">
         <f t="shared" si="3"/>
         <v>5</v>
       </c>
     </row>
-    <row r="26" spans="1:17">
-      <c r="A26" t="s">
-        <v>17</v>
-      </c>
-      <c r="B26">
-        <v>1</v>
-      </c>
-      <c r="C26">
-        <v>2</v>
-      </c>
-      <c r="D26">
-        <v>3</v>
-      </c>
-      <c r="E26">
-        <v>4</v>
-      </c>
-      <c r="F26">
-        <v>5</v>
-      </c>
-      <c r="G26">
-        <v>6</v>
-      </c>
-      <c r="H26">
-        <v>7</v>
-      </c>
-      <c r="I26">
-        <v>8</v>
-      </c>
-      <c r="J26">
-        <v>9</v>
-      </c>
-      <c r="K26">
-        <v>10</v>
-      </c>
-      <c r="L26">
-        <v>11</v>
-      </c>
-      <c r="M26">
-        <v>12</v>
-      </c>
-      <c r="N26">
-        <v>13</v>
-      </c>
-      <c r="O26">
-        <v>14</v>
-      </c>
-      <c r="P26">
-        <v>15</v>
-      </c>
-      <c r="Q26">
-        <v>16</v>
+    <row r="24" s="1" customFormat="1" spans="1:15">
+      <c r="A24" s="1">
+        <v>2026</v>
+      </c>
+      <c r="B24" s="1">
+        <v>-0.0075</v>
+      </c>
+      <c r="C24" s="1">
+        <v>0.0046</v>
+      </c>
+      <c r="D24" s="1">
+        <v>-0.1137</v>
+      </c>
+      <c r="E24" s="1">
+        <v>0.042</v>
+      </c>
+      <c r="F24" s="1">
+        <v>-0.1464</v>
+      </c>
+      <c r="G24" s="1">
+        <v>-0.0434</v>
+      </c>
+      <c r="N24" s="10">
+        <f>(1+B24)*(1+C24)*(1+D24)*(1+E24)*(1+F24)*(1+G24)*(1+H24)*(1+I24)*(1+J24)*(1+K24)*(1+L24)*(1+M24)-1</f>
+        <v>-0.248105443831011</v>
+      </c>
+      <c r="O24" s="9">
+        <f>N24</f>
+        <v>-0.248105443831011</v>
       </c>
     </row>
     <row r="27" spans="1:17">
       <c r="A27" t="s">
-        <v>18</v>
-      </c>
-      <c r="B27" s="5" cm="1">
-        <f ca="1" t="array" ref="B27">PRODUCT(INDEX($N:$N,ROW($N$18)-B26):$N$17+1)-1</f>
-        <v>0.721324876500654</v>
-      </c>
-      <c r="C27" s="5" cm="1">
-        <f ca="1" t="array" ref="C27">PRODUCT(INDEX($N:$N,ROW($N$18)-C26):$N$17+1)-1</f>
-        <v>4.4123815164883</v>
-      </c>
-      <c r="D27" s="5" cm="1">
-        <f ca="1" t="array" ref="D27">PRODUCT(INDEX($N:$N,ROW($N$18)-D26):$N$17+1)-1</f>
-        <v>7.09182204737543</v>
-      </c>
-      <c r="E27" s="5" cm="1">
-        <f ca="1" t="array" ref="E27">PRODUCT(INDEX($N:$N,ROW($N$18)-E26):$N$17+1)-1</f>
-        <v>23.2500956572222</v>
-      </c>
-      <c r="F27" s="5" cm="1">
-        <f ca="1" t="array" ref="F27">PRODUCT(INDEX($N:$N,ROW($N$18)-F26):$N$17+1)-1</f>
-        <v>39.2784596885555</v>
-      </c>
-      <c r="G27" s="5" cm="1">
-        <f ca="1" t="array" ref="G27">PRODUCT(INDEX($N:$N,ROW($N$18)-G26):$N$17+1)-1</f>
-        <v>59.4933235390029</v>
-      </c>
-      <c r="H27" s="5" cm="1">
-        <f ca="1" t="array" ref="H27">PRODUCT(INDEX($N:$N,ROW($N$18)-H26):$N$17+1)-1</f>
-        <v>104.612172595413</v>
-      </c>
-      <c r="I27" s="5" cm="1">
-        <f ca="1" t="array" ref="I27">PRODUCT(INDEX($N:$N,ROW($N$18)-I26):$N$17+1)-1</f>
-        <v>154.5482718522</v>
-      </c>
-      <c r="J27" s="5" cm="1">
-        <f ca="1" t="array" ref="J27">PRODUCT(INDEX($N:$N,ROW($N$18)-J26):$N$17+1)-1</f>
-        <v>166.614078638372</v>
-      </c>
-      <c r="K27" s="5" cm="1">
-        <f ca="1" t="array" ref="K27">PRODUCT(INDEX($N:$N,ROW($N$18)-K26):$N$17+1)-1</f>
-        <v>350.476982655267</v>
-      </c>
-      <c r="L27" s="5" cm="1">
-        <f ca="1" t="array" ref="L27">PRODUCT(INDEX($N:$N,ROW($N$18)-L26):$N$17+1)-1</f>
-        <v>2453.29759661859</v>
-      </c>
-      <c r="M27" s="5" cm="1">
-        <f ca="1" t="array" ref="M27">PRODUCT(INDEX($N:$N,ROW($N$18)-M26):$N$17+1)-1</f>
-        <v>5396.87710210919</v>
-      </c>
-      <c r="N27" s="5" cm="1">
-        <f ca="1" t="array" ref="N27">PRODUCT(INDEX($N:$N,ROW($N$18)-N26):$N$17+1)-1</f>
-        <v>9528.43923907489</v>
-      </c>
-      <c r="O27" s="5" cm="1">
-        <f ca="1" t="array" ref="O27">PRODUCT(INDEX($N:$N,ROW($N$18)-O26):$N$17+1)-1</f>
-        <v>9894.91665610194</v>
-      </c>
-      <c r="P27" s="5" cm="1">
-        <f ca="1" t="array" ref="P27">PRODUCT(INDEX($N:$N,ROW($N$18)-P26):$N$17+1)-1</f>
-        <v>9048.15849161137</v>
-      </c>
-      <c r="Q27" s="5" cm="1">
-        <f ca="1" t="array" ref="Q27">PRODUCT(INDEX($N:$N,ROW($N$18)-Q26):$N$17+1)-1</f>
-        <v>14962.8167474189</v>
+        <v>17</v>
+      </c>
+      <c r="B27">
+        <v>1</v>
+      </c>
+      <c r="C27">
+        <v>2</v>
+      </c>
+      <c r="D27">
+        <v>3</v>
+      </c>
+      <c r="E27">
+        <v>4</v>
+      </c>
+      <c r="F27">
+        <v>5</v>
+      </c>
+      <c r="G27">
+        <v>6</v>
+      </c>
+      <c r="H27">
+        <v>7</v>
+      </c>
+      <c r="I27">
+        <v>8</v>
+      </c>
+      <c r="J27">
+        <v>9</v>
+      </c>
+      <c r="K27">
+        <v>10</v>
+      </c>
+      <c r="L27">
+        <v>11</v>
+      </c>
+      <c r="M27">
+        <v>12</v>
+      </c>
+      <c r="N27">
+        <v>13</v>
+      </c>
+      <c r="O27">
+        <v>14</v>
+      </c>
+      <c r="P27">
+        <v>15</v>
+      </c>
+      <c r="Q27">
+        <v>16</v>
       </c>
     </row>
     <row r="28" spans="1:17">
       <c r="A28" t="s">
+        <v>18</v>
+      </c>
+      <c r="B28" s="8" cm="1">
+        <f ca="1" t="array" ref="B28">PRODUCT(INDEX($N:$N,ROW($N$19)-B27):$N$17+1)-1</f>
+        <v>0.721324876500654</v>
+      </c>
+      <c r="C28" s="8" cm="1">
+        <f ca="1" t="array" ref="C28">PRODUCT(INDEX($N:$N,ROW($N$19)-C27):$N$17+1)-1</f>
+        <v>0.721324876500654</v>
+      </c>
+      <c r="D28" s="8" cm="1">
+        <f ca="1" t="array" ref="D28">PRODUCT(INDEX($N:$N,ROW($N$19)-D27):$N$17+1)-1</f>
+        <v>4.41238151648831</v>
+      </c>
+      <c r="E28" s="8" cm="1">
+        <f ca="1" t="array" ref="E28">PRODUCT(INDEX($N:$N,ROW($N$19)-E27):$N$17+1)-1</f>
+        <v>7.09182204737544</v>
+      </c>
+      <c r="F28" s="8" cm="1">
+        <f ca="1" t="array" ref="F28">PRODUCT(INDEX($N:$N,ROW($N$19)-F27):$N$17+1)-1</f>
+        <v>23.2500956572223</v>
+      </c>
+      <c r="G28" s="8" cm="1">
+        <f ca="1" t="array" ref="G28">PRODUCT(INDEX($N:$N,ROW($N$19)-G27):$N$17+1)-1</f>
+        <v>39.2784596885556</v>
+      </c>
+      <c r="H28" s="8" cm="1">
+        <f ca="1" t="array" ref="H28">PRODUCT(INDEX($N:$N,ROW($N$19)-H27):$N$17+1)-1</f>
+        <v>59.4933235390031</v>
+      </c>
+      <c r="I28" s="8" cm="1">
+        <f ca="1" t="array" ref="I28">PRODUCT(INDEX($N:$N,ROW($N$19)-I27):$N$17+1)-1</f>
+        <v>104.612172595413</v>
+      </c>
+      <c r="J28" s="8" cm="1">
+        <f ca="1" t="array" ref="J28">PRODUCT(INDEX($N:$N,ROW($N$19)-J27):$N$17+1)-1</f>
+        <v>154.5482718522</v>
+      </c>
+      <c r="K28" s="8" cm="1">
+        <f ca="1" t="array" ref="K28">PRODUCT(INDEX($N:$N,ROW($N$19)-K27):$N$17+1)-1</f>
+        <v>166.614078638373</v>
+      </c>
+      <c r="L28" s="8" cm="1">
+        <f ca="1" t="array" ref="L28">PRODUCT(INDEX($N:$N,ROW($N$19)-L27):$N$17+1)-1</f>
+        <v>350.476982655268</v>
+      </c>
+      <c r="M28" s="8" cm="1">
+        <f ca="1" t="array" ref="M28">PRODUCT(INDEX($N:$N,ROW($N$19)-M27):$N$17+1)-1</f>
+        <v>2453.2975966186</v>
+      </c>
+      <c r="N28" s="8" cm="1">
+        <f ca="1" t="array" ref="N28">PRODUCT(INDEX($N:$N,ROW($N$19)-N27):$N$17+1)-1</f>
+        <v>5396.87710210921</v>
+      </c>
+      <c r="O28" s="8" cm="1">
+        <f ca="1" t="array" ref="O28">PRODUCT(INDEX($N:$N,ROW($N$19)-O27):$N$17+1)-1</f>
+        <v>9528.43923907493</v>
+      </c>
+      <c r="P28" s="8" cm="1">
+        <f ca="1" t="array" ref="P28">PRODUCT(INDEX($N:$N,ROW($N$19)-P27):$N$17+1)-1</f>
+        <v>9894.91665610199</v>
+      </c>
+      <c r="Q28" s="8" cm="1">
+        <f ca="1" t="array" ref="Q28">PRODUCT(INDEX($N:$N,ROW($N$19)-Q27):$N$17+1)-1</f>
+        <v>9048.15849161141</v>
+      </c>
+    </row>
+    <row r="29" spans="1:17">
+      <c r="A29" t="s">
         <v>19</v>
       </c>
-      <c r="B28" s="6">
-        <f ca="1">POWER(B27+1,1/B26)-1</f>
+      <c r="B29" s="9">
+        <f ca="1">POWER(B28+1,1/B27)-1</f>
         <v>0.721324876500654</v>
       </c>
-      <c r="C28" s="6">
-        <f ca="1">POWER(C27+1,1/C26)-1</f>
-        <v>1.32645256054971</v>
-      </c>
-      <c r="D28" s="6">
-        <f ca="1" t="shared" ref="D28:Q28" si="4">POWER(D27+1,1/D26)-1</f>
-        <v>1.00762274723281</v>
-      </c>
-      <c r="E28" s="6">
+      <c r="C29" s="9">
+        <f ca="1">POWER(C28+1,1/C27)-1</f>
+        <v>0.3119927120608</v>
+      </c>
+      <c r="D29" s="9">
+        <f ca="1" t="shared" ref="D29:Q29" si="4">POWER(D28+1,1/D27)-1</f>
+        <v>0.75575049992058</v>
+      </c>
+      <c r="E29" s="9">
         <f ca="1" t="shared" si="4"/>
-        <v>1.21910761645483</v>
-      </c>
-      <c r="F28" s="6">
+        <v>0.686597999377588</v>
+      </c>
+      <c r="F29" s="9">
         <f ca="1" t="shared" si="4"/>
-        <v>1.09418271565768</v>
-      </c>
-      <c r="G28" s="6">
+        <v>0.892093924562005</v>
+      </c>
+      <c r="G29" s="9">
         <f ca="1" t="shared" si="4"/>
-        <v>0.98130456845761</v>
-      </c>
-      <c r="H28" s="6">
+        <v>0.851450657807452</v>
+      </c>
+      <c r="H29" s="9">
         <f ca="1" t="shared" si="4"/>
-        <v>0.945817014845787</v>
-      </c>
-      <c r="I28" s="6">
+        <v>0.796923693198646</v>
+      </c>
+      <c r="I29" s="9">
         <f ca="1" t="shared" si="4"/>
-        <v>0.879243898263695</v>
-      </c>
-      <c r="J28" s="6">
+        <v>0.790458450087202</v>
+      </c>
+      <c r="J29" s="9">
         <f ca="1" t="shared" si="4"/>
-        <v>0.766630037947978</v>
-      </c>
-      <c r="K28" s="6">
+        <v>0.752026120711281</v>
+      </c>
+      <c r="K29" s="9">
         <f ca="1" t="shared" si="4"/>
-        <v>0.797172187425214</v>
-      </c>
-      <c r="L28" s="6">
+        <v>0.668902823492491</v>
+      </c>
+      <c r="L29" s="9">
         <f ca="1" t="shared" si="4"/>
-        <v>1.03317706479</v>
-      </c>
-      <c r="M28" s="6">
+        <v>0.703904193500895</v>
+      </c>
+      <c r="M29" s="9">
         <f ca="1" t="shared" si="4"/>
-        <v>1.04653220237664</v>
-      </c>
-      <c r="N28" s="6">
+        <v>0.916434299972187</v>
+      </c>
+      <c r="N29" s="9">
         <f ca="1" t="shared" si="4"/>
-        <v>1.02340166712687</v>
-      </c>
-      <c r="O28" s="6">
+        <v>0.936841474732953</v>
+      </c>
+      <c r="O29" s="9">
         <f ca="1" t="shared" si="4"/>
-        <v>0.929255363746949</v>
-      </c>
-      <c r="P28" s="6">
+        <v>0.924062149207631</v>
+      </c>
+      <c r="P29" s="9">
         <f ca="1" t="shared" si="4"/>
-        <v>0.835582377705406</v>
-      </c>
-      <c r="Q28" s="6">
+        <v>0.846561324809914</v>
+      </c>
+      <c r="Q29" s="9">
         <f ca="1" t="shared" si="4"/>
-        <v>0.823644364105827</v>
+        <v>0.767209396894281</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B18:N18">
-    <cfRule type="expression" dxfId="0" priority="3">
-      <formula>B18&gt;2</formula>
+  <conditionalFormatting sqref="B19:N19">
+    <cfRule type="expression" dxfId="1" priority="4">
+      <formula>B19&lt;2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="1" priority="2">
-      <formula>B18&lt;2</formula>
+    <cfRule type="expression" dxfId="0" priority="5">
+      <formula>B19&gt;2</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:M18 N18">
-    <cfRule type="expression" dxfId="3" priority="6">
+  <conditionalFormatting sqref="N24">
+    <cfRule type="expression" dxfId="4" priority="2">
+      <formula>N24&gt;1.5</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="O24">
+    <cfRule type="expression" dxfId="4" priority="1">
+      <formula>O24&gt;1.5</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B2:M18 B19:N19">
+    <cfRule type="expression" dxfId="2" priority="7">
+      <formula>B2&lt;0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="3" priority="8">
       <formula>B2&gt;0.1</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="2" priority="5">
-      <formula>B2&lt;0</formula>
-    </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:O17 O18">
-    <cfRule type="expression" dxfId="4" priority="1">
+  <conditionalFormatting sqref="N2:O18 O19">
+    <cfRule type="expression" dxfId="4" priority="3">
       <formula>N2&gt;1.5</formula>
     </cfRule>
   </conditionalFormatting>

--- a/JoinQuant/profit.xlsx
+++ b/JoinQuant/profit.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24750" windowHeight="10480" activeTab="2"/>
+    <workbookView windowWidth="27950" windowHeight="12280" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -110,7 +110,7 @@
     <t>总收益率</t>
   </si>
   <si>
-    <t>年化收益率</t>
+    <t>年化</t>
   </si>
 </sst>
 </file>
@@ -305,18 +305,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="38">
+  <fills count="37">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -718,7 +712,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -742,16 +736,16 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="10" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="10" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="11" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="10" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -760,115 +754,112 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="17" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="176" fontId="0" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="176" fontId="0" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="17" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="17" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="2"/>
     </xf>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
@@ -876,25 +867,25 @@
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="3" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="176" fontId="3" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="10" fontId="3" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="10" fontId="3" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="17" fontId="4" fillId="7" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="17" fontId="4" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1464,8 +1455,8 @@
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
       <c:layout/>
-      <c:lineChart>
-        <c:grouping val="standard"/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
         <c:varyColors val="0"/>
         <c:ser>
           <c:idx val="0"/>
@@ -1480,68 +1471,143 @@
             <a:effectLst/>
           </c:spPr>
           <c:marker>
-            <c:symbol val="none"/>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
           </c:marker>
           <c:dLbls>
             <c:delete val="1"/>
           </c:dLbls>
-          <c:val>
+          <c:xVal>
             <c:numRef>
-              <c:f>Sheet3!$B$29:$Q$29</c:f>
+              <c:f>Sheet3!$A$29:$A$45</c:f>
               <c:numCache>
-                <c:formatCode>0.00%</c:formatCode>
-                <c:ptCount val="16"/>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="17"/>
                 <c:pt idx="0">
-                  <c:v>0.721324876500654</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.3119927120608</c:v>
+                  <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.75575049992058</c:v>
+                  <c:v>3</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.686597999377588</c:v>
+                  <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.892093924562005</c:v>
+                  <c:v>5</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.851450657807452</c:v>
+                  <c:v>6</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.796923693198646</c:v>
+                  <c:v>7</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.790458450087202</c:v>
+                  <c:v>8</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.752026120711281</c:v>
+                  <c:v>9</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.668902823492491</c:v>
+                  <c:v>10</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.703904193500895</c:v>
+                  <c:v>11</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.916434299972187</c:v>
+                  <c:v>12</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.936841474732953</c:v>
+                  <c:v>13</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.924062149207631</c:v>
+                  <c:v>14</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0.846561324809914</c:v>
+                  <c:v>15</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>0.767209396894281</c:v>
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>17</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
-          </c:val>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Sheet3!$C$29:$C$45</c:f>
+              <c:numCache>
+                <c:formatCode>0.00%</c:formatCode>
+                <c:ptCount val="17"/>
+                <c:pt idx="0">
+                  <c:v>-0.248105443831011</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.137653200250014</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.596547267811532</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.570546560194028</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.787203800526058</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.765515897213793</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.725193326188861</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.727761787783006</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.697384518586593</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.621984663460095</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.66030055015333</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.871430400967408</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.894818809104917</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.885268292014252</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.811788635887162</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0.735992405611589</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0.731034973797034</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
           <c:smooth val="0"/>
         </c:ser>
         <c:dLbls>
@@ -1552,36 +1618,29 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:marker val="0"/>
-        <c:smooth val="0"/>
         <c:axId val="604726011"/>
         <c:axId val="769988795"/>
-      </c:lineChart>
-      <c:catAx>
+      </c:scatterChart>
+      <c:valAx>
         <c:axId val="604726011"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:spPr>
           <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="15000"/>
-                <a:lumOff val="85000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
+          <a:ln>
+            <a:noFill/>
           </a:ln>
           <a:effectLst/>
         </c:spPr>
         <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1" forceAA="0"/>
           <a:lstStyle/>
           <a:p>
             <a:pPr>
@@ -1601,11 +1660,8 @@
         </c:txPr>
         <c:crossAx val="769988795"/>
         <c:crosses val="autoZero"/>
-        <c:auto val="1"/>
-        <c:lblAlgn val="ctr"/>
-        <c:lblOffset val="100"/>
-        <c:noMultiLvlLbl val="0"/>
-      </c:catAx>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
       <c:valAx>
         <c:axId val="769988795"/>
         <c:scaling>
@@ -1658,7 +1714,7 @@
         </c:txPr>
         <c:crossAx val="604726011"/>
         <c:crosses val="autoZero"/>
-        <c:crossBetween val="between"/>
+        <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:spPr>
         <a:noFill/>
@@ -2856,8 +2912,8 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="10638155" y="384175"/>
-        <a:ext cx="4864100" cy="2933700"/>
+        <a:off x="10708005" y="384175"/>
+        <a:ext cx="4902200" cy="2933700"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -2869,16 +2925,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>41910</xdr:colOff>
-      <xdr:row>29</xdr:row>
-      <xdr:rowOff>31115</xdr:rowOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>572135</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>77470</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>92710</xdr:colOff>
-      <xdr:row>44</xdr:row>
-      <xdr:rowOff>110490</xdr:rowOff>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>765175</xdr:colOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>56515</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -2886,8 +2942,8 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="917575" y="5333365"/>
-        <a:ext cx="4826000" cy="2746375"/>
+        <a:off x="3238500" y="5024120"/>
+        <a:ext cx="5565140" cy="2823845"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -3158,10 +3214,10 @@
   <sheetData>
     <row r="1" ht="14.75"/>
     <row r="2" ht="14.75" spans="1:22">
-      <c r="A2" s="2">
+      <c r="A2" s="1">
         <v>40179</v>
       </c>
-      <c r="B2" s="15">
+      <c r="B2" s="14">
         <v>0</v>
       </c>
       <c r="C2">
@@ -3238,10 +3294,10 @@
       </c>
     </row>
     <row r="3" ht="14.75" spans="1:22">
-      <c r="A3" s="2">
+      <c r="A3" s="1">
         <v>40210</v>
       </c>
-      <c r="B3" s="15">
+      <c r="B3" s="14">
         <v>0.0651</v>
       </c>
       <c r="C3">
@@ -3318,10 +3374,10 @@
       </c>
     </row>
     <row r="4" ht="14.75" spans="1:22">
-      <c r="A4" s="2">
+      <c r="A4" s="1">
         <v>40238</v>
       </c>
-      <c r="B4" s="15">
+      <c r="B4" s="14">
         <v>0.0813</v>
       </c>
       <c r="C4">
@@ -3398,10 +3454,10 @@
       </c>
     </row>
     <row r="5" ht="14.75" spans="1:22">
-      <c r="A5" s="2">
+      <c r="A5" s="1">
         <v>40269</v>
       </c>
-      <c r="B5" s="15">
+      <c r="B5" s="14">
         <v>0.0008</v>
       </c>
       <c r="C5">
@@ -3478,10 +3534,10 @@
       </c>
     </row>
     <row r="6" ht="14.75" spans="1:22">
-      <c r="A6" s="2">
+      <c r="A6" s="1">
         <v>40299</v>
       </c>
-      <c r="B6" s="15">
+      <c r="B6" s="14">
         <v>-0.0608</v>
       </c>
       <c r="C6">
@@ -3558,10 +3614,10 @@
       </c>
     </row>
     <row r="7" ht="14.75" spans="1:22">
-      <c r="A7" s="2">
+      <c r="A7" s="1">
         <v>40330</v>
       </c>
-      <c r="B7" s="15">
+      <c r="B7" s="14">
         <v>-0.073</v>
       </c>
       <c r="C7">
@@ -3638,10 +3694,10 @@
       </c>
     </row>
     <row r="8" ht="14.75" spans="1:22">
-      <c r="A8" s="2">
+      <c r="A8" s="1">
         <v>40360</v>
       </c>
-      <c r="B8" s="15">
+      <c r="B8" s="14">
         <v>0.1977</v>
       </c>
       <c r="C8">
@@ -3718,10 +3774,10 @@
       </c>
     </row>
     <row r="9" ht="14.75" spans="1:22">
-      <c r="A9" s="2">
+      <c r="A9" s="1">
         <v>40391</v>
       </c>
-      <c r="B9" s="15">
+      <c r="B9" s="14">
         <v>0.1303</v>
       </c>
       <c r="C9">
@@ -3798,10 +3854,10 @@
       </c>
     </row>
     <row r="10" ht="14.75" spans="1:22">
-      <c r="A10" s="2">
+      <c r="A10" s="1">
         <v>40422</v>
       </c>
-      <c r="B10" s="15">
+      <c r="B10" s="14">
         <v>0.11</v>
       </c>
       <c r="C10">
@@ -3878,10 +3934,10 @@
       </c>
     </row>
     <row r="11" ht="14.75" spans="1:22">
-      <c r="A11" s="2">
+      <c r="A11" s="1">
         <v>40452</v>
       </c>
-      <c r="B11" s="15">
+      <c r="B11" s="14">
         <v>0.1099</v>
       </c>
       <c r="C11">
@@ -3958,10 +4014,10 @@
       </c>
     </row>
     <row r="12" ht="14.75" spans="1:22">
-      <c r="A12" s="2">
+      <c r="A12" s="1">
         <v>40483</v>
       </c>
-      <c r="B12" s="15">
+      <c r="B12" s="14">
         <v>0.0089</v>
       </c>
       <c r="C12">
@@ -4038,10 +4094,10 @@
       </c>
     </row>
     <row r="13" ht="14.75" spans="1:22">
-      <c r="A13" s="2">
+      <c r="A13" s="1">
         <v>40513</v>
       </c>
-      <c r="B13" s="15">
+      <c r="B13" s="14">
         <v>-0.0207</v>
       </c>
       <c r="C13">
@@ -4118,1804 +4174,1804 @@
       </c>
     </row>
     <row r="14" ht="14.75" spans="1:4">
-      <c r="A14" s="2">
+      <c r="A14" s="1">
         <v>40544</v>
       </c>
-      <c r="B14" s="15">
+      <c r="B14" s="14">
         <v>-0.0016</v>
       </c>
-      <c r="C14" s="15"/>
-      <c r="D14" s="15"/>
+      <c r="C14" s="14"/>
+      <c r="D14" s="14"/>
     </row>
     <row r="15" ht="14.75" spans="1:4">
-      <c r="A15" s="2">
+      <c r="A15" s="1">
         <v>40575</v>
       </c>
-      <c r="B15" s="15">
+      <c r="B15" s="14">
         <v>0.1456</v>
       </c>
-      <c r="C15" s="15"/>
-      <c r="D15" s="15"/>
+      <c r="C15" s="14"/>
+      <c r="D15" s="14"/>
     </row>
     <row r="16" ht="14.75" spans="1:4">
-      <c r="A16" s="2">
+      <c r="A16" s="1">
         <v>40603</v>
       </c>
-      <c r="B16" s="15">
+      <c r="B16" s="14">
         <v>0.0526</v>
       </c>
-      <c r="C16" s="15"/>
-      <c r="D16" s="15"/>
+      <c r="C16" s="14"/>
+      <c r="D16" s="14"/>
     </row>
     <row r="17" ht="14.75" spans="1:4">
-      <c r="A17" s="2">
+      <c r="A17" s="1">
         <v>40634</v>
       </c>
-      <c r="B17" s="15">
+      <c r="B17" s="14">
         <v>-0.0008</v>
       </c>
-      <c r="C17" s="15"/>
-      <c r="D17" s="15"/>
+      <c r="C17" s="14"/>
+      <c r="D17" s="14"/>
     </row>
     <row r="18" ht="14.75" spans="1:4">
-      <c r="A18" s="2">
+      <c r="A18" s="1">
         <v>40664</v>
       </c>
-      <c r="B18" s="15">
+      <c r="B18" s="14">
         <v>-0.0644</v>
       </c>
-      <c r="C18" s="15"/>
-      <c r="D18" s="15"/>
+      <c r="C18" s="14"/>
+      <c r="D18" s="14"/>
     </row>
     <row r="19" ht="14.75" spans="1:4">
-      <c r="A19" s="2">
+      <c r="A19" s="1">
         <v>40695</v>
       </c>
-      <c r="B19" s="15">
+      <c r="B19" s="14">
         <v>0.0828</v>
       </c>
-      <c r="C19" s="15"/>
-      <c r="D19" s="15"/>
+      <c r="C19" s="14"/>
+      <c r="D19" s="14"/>
     </row>
     <row r="20" ht="14.75" spans="1:4">
-      <c r="A20" s="2">
+      <c r="A20" s="1">
         <v>40725</v>
       </c>
-      <c r="B20" s="15">
+      <c r="B20" s="14">
         <v>-0.0211</v>
       </c>
-      <c r="C20" s="15"/>
-      <c r="D20" s="15"/>
+      <c r="C20" s="14"/>
+      <c r="D20" s="14"/>
     </row>
     <row r="21" ht="14.75" spans="1:4">
-      <c r="A21" s="2">
+      <c r="A21" s="1">
         <v>40756</v>
       </c>
-      <c r="B21" s="15">
+      <c r="B21" s="14">
         <v>-0.0006</v>
       </c>
-      <c r="C21" s="15"/>
-      <c r="D21" s="15"/>
+      <c r="C21" s="14"/>
+      <c r="D21" s="14"/>
     </row>
     <row r="22" ht="14.75" spans="1:4">
-      <c r="A22" s="2">
+      <c r="A22" s="1">
         <v>40787</v>
       </c>
-      <c r="B22" s="15">
+      <c r="B22" s="14">
         <v>-0.0886</v>
       </c>
-      <c r="C22" s="15"/>
-      <c r="D22" s="15"/>
+      <c r="C22" s="14"/>
+      <c r="D22" s="14"/>
     </row>
     <row r="23" ht="14.75" spans="1:4">
-      <c r="A23" s="2">
+      <c r="A23" s="1">
         <v>40817</v>
       </c>
-      <c r="B23" s="15">
+      <c r="B23" s="14">
         <v>0.0186</v>
       </c>
-      <c r="C23" s="15"/>
-      <c r="D23" s="15"/>
+      <c r="C23" s="14"/>
+      <c r="D23" s="14"/>
     </row>
     <row r="24" ht="14.75" spans="1:4">
-      <c r="A24" s="2">
+      <c r="A24" s="1">
         <v>40848</v>
       </c>
-      <c r="B24" s="15">
+      <c r="B24" s="14">
         <v>-0.0239</v>
       </c>
-      <c r="C24" s="15"/>
-      <c r="D24" s="15"/>
+      <c r="C24" s="14"/>
+      <c r="D24" s="14"/>
     </row>
     <row r="25" ht="14.75" spans="1:4">
-      <c r="A25" s="2">
+      <c r="A25" s="1">
         <v>40878</v>
       </c>
-      <c r="B25" s="15">
+      <c r="B25" s="14">
         <v>-0.1536</v>
       </c>
-      <c r="C25" s="15"/>
-      <c r="D25" s="15"/>
+      <c r="C25" s="14"/>
+      <c r="D25" s="14"/>
     </row>
     <row r="26" ht="14.75" spans="1:4">
-      <c r="A26" s="2">
+      <c r="A26" s="1">
         <v>40909</v>
       </c>
-      <c r="B26" s="15">
+      <c r="B26" s="14">
         <v>0.0301</v>
       </c>
-      <c r="C26" s="15"/>
-      <c r="D26" s="15"/>
+      <c r="C26" s="14"/>
+      <c r="D26" s="14"/>
     </row>
     <row r="27" ht="14.75" spans="1:4">
-      <c r="A27" s="2">
+      <c r="A27" s="1">
         <v>40940</v>
       </c>
-      <c r="B27" s="15">
+      <c r="B27" s="14">
         <v>0.0984</v>
       </c>
-      <c r="C27" s="15"/>
-      <c r="D27" s="15"/>
+      <c r="C27" s="14"/>
+      <c r="D27" s="14"/>
     </row>
     <row r="28" ht="14.75" spans="1:4">
-      <c r="A28" s="2">
+      <c r="A28" s="1">
         <v>40969</v>
       </c>
-      <c r="B28" s="15">
+      <c r="B28" s="14">
         <v>-0.065</v>
       </c>
-      <c r="C28" s="15"/>
-      <c r="D28" s="15"/>
+      <c r="C28" s="14"/>
+      <c r="D28" s="14"/>
     </row>
     <row r="29" ht="14.75" spans="1:4">
-      <c r="A29" s="2">
+      <c r="A29" s="1">
         <v>41000</v>
       </c>
-      <c r="B29" s="15">
+      <c r="B29" s="14">
         <v>0.0104</v>
       </c>
-      <c r="C29" s="15"/>
-      <c r="D29" s="15"/>
+      <c r="C29" s="14"/>
+      <c r="D29" s="14"/>
     </row>
     <row r="30" ht="14.75" spans="1:4">
-      <c r="A30" s="2">
+      <c r="A30" s="1">
         <v>41030</v>
       </c>
-      <c r="B30" s="15">
+      <c r="B30" s="14">
         <v>0.0008</v>
       </c>
-      <c r="C30" s="15"/>
-      <c r="D30" s="15"/>
+      <c r="C30" s="14"/>
+      <c r="D30" s="14"/>
     </row>
     <row r="31" ht="14.75" spans="1:4">
-      <c r="A31" s="2">
+      <c r="A31" s="1">
         <v>41061</v>
       </c>
-      <c r="B31" s="15">
+      <c r="B31" s="14">
         <v>-0.0436</v>
       </c>
-      <c r="C31" s="15"/>
-      <c r="D31" s="15"/>
+      <c r="C31" s="14"/>
+      <c r="D31" s="14"/>
     </row>
     <row r="32" ht="14.75" spans="1:4">
-      <c r="A32" s="2">
+      <c r="A32" s="1">
         <v>41091</v>
       </c>
-      <c r="B32" s="15">
+      <c r="B32" s="14">
         <v>-0.1551</v>
       </c>
-      <c r="C32" s="15"/>
-      <c r="D32" s="15"/>
+      <c r="C32" s="14"/>
+      <c r="D32" s="14"/>
     </row>
     <row r="33" ht="14.75" spans="1:4">
-      <c r="A33" s="2">
+      <c r="A33" s="1">
         <v>41122</v>
       </c>
-      <c r="B33" s="15">
+      <c r="B33" s="14">
         <v>0.0543</v>
       </c>
-      <c r="C33" s="15"/>
-      <c r="D33" s="15"/>
+      <c r="C33" s="14"/>
+      <c r="D33" s="14"/>
     </row>
     <row r="34" ht="14.75" spans="1:4">
-      <c r="A34" s="2">
+      <c r="A34" s="1">
         <v>41153</v>
       </c>
-      <c r="B34" s="15">
+      <c r="B34" s="14">
         <v>0.019</v>
       </c>
-      <c r="C34" s="15"/>
-      <c r="D34" s="15"/>
+      <c r="C34" s="14"/>
+      <c r="D34" s="14"/>
     </row>
     <row r="35" ht="14.75" spans="1:4">
-      <c r="A35" s="2">
+      <c r="A35" s="1">
         <v>41183</v>
       </c>
-      <c r="B35" s="15">
+      <c r="B35" s="14">
         <v>0.0012</v>
       </c>
-      <c r="C35" s="15"/>
-      <c r="D35" s="15"/>
+      <c r="C35" s="14"/>
+      <c r="D35" s="14"/>
     </row>
     <row r="36" ht="14.75" spans="1:4">
-      <c r="A36" s="2">
+      <c r="A36" s="1">
         <v>41214</v>
       </c>
-      <c r="B36" s="15">
+      <c r="B36" s="14">
         <v>-0.0975</v>
       </c>
-      <c r="C36" s="15"/>
-      <c r="D36" s="15"/>
+      <c r="C36" s="14"/>
+      <c r="D36" s="14"/>
     </row>
     <row r="37" ht="14.75" spans="1:4">
-      <c r="A37" s="2">
+      <c r="A37" s="1">
         <v>41244</v>
       </c>
-      <c r="B37" s="15">
+      <c r="B37" s="14">
         <v>0.2375</v>
       </c>
-      <c r="C37" s="15"/>
-      <c r="D37" s="15"/>
+      <c r="C37" s="14"/>
+      <c r="D37" s="14"/>
     </row>
     <row r="38" ht="14.75" spans="1:4">
-      <c r="A38" s="2">
+      <c r="A38" s="1">
         <v>41275</v>
       </c>
-      <c r="B38" s="15">
+      <c r="B38" s="14">
         <v>0.0057</v>
       </c>
-      <c r="C38" s="15"/>
-      <c r="D38" s="15"/>
+      <c r="C38" s="14"/>
+      <c r="D38" s="14"/>
     </row>
     <row r="39" ht="14.75" spans="1:4">
-      <c r="A39" s="2">
+      <c r="A39" s="1">
         <v>41306</v>
       </c>
-      <c r="B39" s="15">
+      <c r="B39" s="14">
         <v>0.0547</v>
       </c>
-      <c r="C39" s="15"/>
-      <c r="D39" s="15"/>
+      <c r="C39" s="14"/>
+      <c r="D39" s="14"/>
     </row>
     <row r="40" ht="14.75" spans="1:4">
-      <c r="A40" s="2">
+      <c r="A40" s="1">
         <v>41334</v>
       </c>
-      <c r="B40" s="15">
+      <c r="B40" s="14">
         <v>-0.0189</v>
       </c>
-      <c r="C40" s="15"/>
-      <c r="D40" s="15"/>
+      <c r="C40" s="14"/>
+      <c r="D40" s="14"/>
     </row>
     <row r="41" ht="14.75" spans="1:4">
-      <c r="A41" s="2">
+      <c r="A41" s="1">
         <v>41365</v>
       </c>
-      <c r="B41" s="15">
+      <c r="B41" s="14">
         <v>-0.0003</v>
       </c>
-      <c r="C41" s="15"/>
-      <c r="D41" s="15"/>
+      <c r="C41" s="14"/>
+      <c r="D41" s="14"/>
     </row>
     <row r="42" ht="14.75" spans="1:4">
-      <c r="A42" s="2">
+      <c r="A42" s="1">
         <v>41395</v>
       </c>
-      <c r="B42" s="15">
+      <c r="B42" s="14">
         <v>0.1792</v>
       </c>
-      <c r="C42" s="15"/>
-      <c r="D42" s="15"/>
+      <c r="C42" s="14"/>
+      <c r="D42" s="14"/>
     </row>
     <row r="43" ht="14.75" spans="1:4">
-      <c r="A43" s="2">
+      <c r="A43" s="1">
         <v>41426</v>
       </c>
-      <c r="B43" s="15">
+      <c r="B43" s="14">
         <v>-0.1098</v>
       </c>
-      <c r="C43" s="15"/>
-      <c r="D43" s="15"/>
+      <c r="C43" s="14"/>
+      <c r="D43" s="14"/>
     </row>
     <row r="44" ht="14.75" spans="1:4">
-      <c r="A44" s="2">
+      <c r="A44" s="1">
         <v>41456</v>
       </c>
-      <c r="B44" s="15">
+      <c r="B44" s="14">
         <v>0.1573</v>
       </c>
-      <c r="C44" s="15"/>
-      <c r="D44" s="15"/>
+      <c r="C44" s="14"/>
+      <c r="D44" s="14"/>
     </row>
     <row r="45" ht="14.75" spans="1:4">
-      <c r="A45" s="2">
+      <c r="A45" s="1">
         <v>41487</v>
       </c>
-      <c r="B45" s="15">
+      <c r="B45" s="14">
         <v>0.1024</v>
       </c>
-      <c r="C45" s="15"/>
-      <c r="D45" s="15"/>
+      <c r="C45" s="14"/>
+      <c r="D45" s="14"/>
     </row>
     <row r="46" ht="14.75" spans="1:4">
-      <c r="A46" s="2">
+      <c r="A46" s="1">
         <v>41518</v>
       </c>
-      <c r="B46" s="15">
+      <c r="B46" s="14">
         <v>0.0868</v>
       </c>
-      <c r="C46" s="15"/>
-      <c r="D46" s="15"/>
+      <c r="C46" s="14"/>
+      <c r="D46" s="14"/>
     </row>
     <row r="47" ht="14.75" spans="1:4">
-      <c r="A47" s="2">
+      <c r="A47" s="1">
         <v>41548</v>
       </c>
-      <c r="B47" s="15">
+      <c r="B47" s="14">
         <v>-0.0176</v>
       </c>
-      <c r="C47" s="15"/>
-      <c r="D47" s="15"/>
+      <c r="C47" s="14"/>
+      <c r="D47" s="14"/>
     </row>
     <row r="48" ht="14.75" spans="1:4">
-      <c r="A48" s="2">
+      <c r="A48" s="1">
         <v>41579</v>
       </c>
-      <c r="B48" s="15">
+      <c r="B48" s="14">
         <v>0.1627</v>
       </c>
-      <c r="C48" s="15"/>
-      <c r="D48" s="15"/>
+      <c r="C48" s="14"/>
+      <c r="D48" s="14"/>
     </row>
     <row r="49" ht="14.75" spans="1:4">
-      <c r="A49" s="2">
+      <c r="A49" s="1">
         <v>41609</v>
       </c>
-      <c r="B49" s="15">
+      <c r="B49" s="14">
         <v>0.0207</v>
       </c>
-      <c r="C49" s="15"/>
-      <c r="D49" s="15"/>
+      <c r="C49" s="14"/>
+      <c r="D49" s="14"/>
     </row>
     <row r="50" ht="14.75" spans="1:4">
-      <c r="A50" s="2">
+      <c r="A50" s="1">
         <v>41640</v>
       </c>
-      <c r="B50" s="15">
+      <c r="B50" s="14">
         <v>-0.0057</v>
       </c>
-      <c r="C50" s="15"/>
-      <c r="D50" s="15"/>
+      <c r="C50" s="14"/>
+      <c r="D50" s="14"/>
     </row>
     <row r="51" ht="14.75" spans="1:4">
-      <c r="A51" s="2">
+      <c r="A51" s="1">
         <v>41671</v>
       </c>
-      <c r="B51" s="15">
+      <c r="B51" s="14">
         <v>0.0822</v>
       </c>
-      <c r="C51" s="15"/>
-      <c r="D51" s="15"/>
+      <c r="C51" s="14"/>
+      <c r="D51" s="14"/>
     </row>
     <row r="52" ht="14.75" spans="1:4">
-      <c r="A52" s="2">
+      <c r="A52" s="1">
         <v>41699</v>
       </c>
-      <c r="B52" s="15">
+      <c r="B52" s="14">
         <v>0.0133</v>
       </c>
-      <c r="C52" s="15"/>
-      <c r="D52" s="15"/>
+      <c r="C52" s="14"/>
+      <c r="D52" s="14"/>
     </row>
     <row r="53" ht="14.75" spans="1:4">
-      <c r="A53" s="2">
+      <c r="A53" s="1">
         <v>41730</v>
       </c>
-      <c r="B53" s="15">
+      <c r="B53" s="14">
         <v>0.0346</v>
       </c>
-      <c r="C53" s="15"/>
-      <c r="D53" s="15"/>
+      <c r="C53" s="14"/>
+      <c r="D53" s="14"/>
     </row>
     <row r="54" ht="14.75" spans="1:4">
-      <c r="A54" s="2">
+      <c r="A54" s="1">
         <v>41760</v>
       </c>
-      <c r="B54" s="15">
+      <c r="B54" s="14">
         <v>0.0267</v>
       </c>
-      <c r="C54" s="15"/>
-      <c r="D54" s="15"/>
+      <c r="C54" s="14"/>
+      <c r="D54" s="14"/>
     </row>
     <row r="55" ht="14.75" spans="1:4">
-      <c r="A55" s="2">
+      <c r="A55" s="1">
         <v>41791</v>
       </c>
-      <c r="B55" s="15">
+      <c r="B55" s="14">
         <v>0.2214</v>
       </c>
-      <c r="C55" s="15"/>
-      <c r="D55" s="15"/>
+      <c r="C55" s="14"/>
+      <c r="D55" s="14"/>
     </row>
     <row r="56" ht="14.75" spans="1:4">
-      <c r="A56" s="2">
+      <c r="A56" s="1">
         <v>41821</v>
       </c>
-      <c r="B56" s="15">
+      <c r="B56" s="14">
         <v>0.1535</v>
       </c>
-      <c r="C56" s="15"/>
-      <c r="D56" s="15"/>
+      <c r="C56" s="14"/>
+      <c r="D56" s="14"/>
     </row>
     <row r="57" ht="14.75" spans="1:4">
-      <c r="A57" s="2">
+      <c r="A57" s="1">
         <v>41852</v>
       </c>
-      <c r="B57" s="15">
+      <c r="B57" s="14">
         <v>0.1294</v>
       </c>
-      <c r="C57" s="15"/>
-      <c r="D57" s="15"/>
+      <c r="C57" s="14"/>
+      <c r="D57" s="14"/>
     </row>
     <row r="58" ht="14.75" spans="1:4">
-      <c r="A58" s="2">
+      <c r="A58" s="1">
         <v>41883</v>
       </c>
-      <c r="B58" s="15">
+      <c r="B58" s="14">
         <v>0.2618</v>
       </c>
-      <c r="C58" s="15"/>
-      <c r="D58" s="15"/>
+      <c r="C58" s="14"/>
+      <c r="D58" s="14"/>
     </row>
     <row r="59" ht="14.75" spans="1:4">
-      <c r="A59" s="2">
+      <c r="A59" s="1">
         <v>41913</v>
       </c>
-      <c r="B59" s="15">
+      <c r="B59" s="14">
         <v>0.044</v>
       </c>
-      <c r="C59" s="15"/>
-      <c r="D59" s="15"/>
+      <c r="C59" s="14"/>
+      <c r="D59" s="14"/>
     </row>
     <row r="60" ht="14.75" spans="1:4">
-      <c r="A60" s="2">
+      <c r="A60" s="1">
         <v>41944</v>
       </c>
-      <c r="B60" s="15">
+      <c r="B60" s="14">
         <v>0.0477</v>
       </c>
-      <c r="C60" s="15"/>
-      <c r="D60" s="15"/>
+      <c r="C60" s="14"/>
+      <c r="D60" s="14"/>
     </row>
     <row r="61" ht="14.75" spans="1:4">
-      <c r="A61" s="2">
+      <c r="A61" s="1">
         <v>41974</v>
       </c>
-      <c r="B61" s="15">
+      <c r="B61" s="14">
         <v>-0.1353</v>
       </c>
-      <c r="C61" s="15"/>
-      <c r="D61" s="15"/>
+      <c r="C61" s="14"/>
+      <c r="D61" s="14"/>
     </row>
     <row r="62" ht="14.75" spans="1:4">
-      <c r="A62" s="2">
+      <c r="A62" s="1">
         <v>42005</v>
       </c>
-      <c r="B62" s="15">
+      <c r="B62" s="14">
         <v>0.0227</v>
       </c>
-      <c r="C62" s="15"/>
-      <c r="D62" s="15"/>
+      <c r="C62" s="14"/>
+      <c r="D62" s="14"/>
     </row>
     <row r="63" ht="14.75" spans="1:4">
-      <c r="A63" s="2">
+      <c r="A63" s="1">
         <v>42036</v>
       </c>
-      <c r="B63" s="15">
+      <c r="B63" s="14">
         <v>0.0675</v>
       </c>
-      <c r="C63" s="15"/>
-      <c r="D63" s="15"/>
+      <c r="C63" s="14"/>
+      <c r="D63" s="14"/>
     </row>
     <row r="64" ht="14.75" spans="1:4">
-      <c r="A64" s="16">
+      <c r="A64" s="15">
         <v>42064</v>
       </c>
-      <c r="B64" s="17">
+      <c r="B64" s="16">
         <v>0.2462</v>
       </c>
-      <c r="C64" s="17"/>
-      <c r="D64" s="17"/>
+      <c r="C64" s="16"/>
+      <c r="D64" s="16"/>
     </row>
     <row r="65" ht="14.75" spans="1:4">
-      <c r="A65" s="2">
+      <c r="A65" s="1">
         <v>42095</v>
       </c>
-      <c r="B65" s="15">
+      <c r="B65" s="14">
         <v>0.079</v>
       </c>
-      <c r="C65" s="15"/>
-      <c r="D65" s="15"/>
+      <c r="C65" s="14"/>
+      <c r="D65" s="14"/>
     </row>
     <row r="66" ht="14.75" spans="1:4">
-      <c r="A66" s="2">
+      <c r="A66" s="1">
         <v>42125</v>
       </c>
-      <c r="B66" s="15">
+      <c r="B66" s="14">
         <v>0.415</v>
       </c>
-      <c r="C66" s="15"/>
-      <c r="D66" s="15"/>
+      <c r="C66" s="14"/>
+      <c r="D66" s="14"/>
     </row>
     <row r="67" ht="14.75" spans="1:4">
-      <c r="A67" s="2">
+      <c r="A67" s="1">
         <v>42156</v>
       </c>
-      <c r="B67" s="15">
+      <c r="B67" s="14">
         <v>0.0212</v>
       </c>
-      <c r="C67" s="15"/>
-      <c r="D67" s="15"/>
+      <c r="C67" s="14"/>
+      <c r="D67" s="14"/>
     </row>
     <row r="68" ht="14.75" spans="1:4">
-      <c r="A68" s="2">
+      <c r="A68" s="1">
         <v>42186</v>
       </c>
-      <c r="B68" s="15">
+      <c r="B68" s="14">
         <v>0.3626</v>
       </c>
-      <c r="C68" s="15"/>
-      <c r="D68" s="15"/>
+      <c r="C68" s="14"/>
+      <c r="D68" s="14"/>
     </row>
     <row r="69" ht="14.75" spans="1:4">
-      <c r="A69" s="2">
+      <c r="A69" s="1">
         <v>42217</v>
       </c>
-      <c r="B69" s="15">
+      <c r="B69" s="14">
         <v>0.283</v>
       </c>
-      <c r="C69" s="15"/>
-      <c r="D69" s="15"/>
+      <c r="C69" s="14"/>
+      <c r="D69" s="14"/>
     </row>
     <row r="70" ht="14.75" spans="1:4">
-      <c r="A70" s="2">
+      <c r="A70" s="1">
         <v>42248</v>
       </c>
-      <c r="B70" s="15">
+      <c r="B70" s="14">
         <v>-0.0678</v>
       </c>
-      <c r="C70" s="15"/>
-      <c r="D70" s="15"/>
+      <c r="C70" s="14"/>
+      <c r="D70" s="14"/>
     </row>
     <row r="71" ht="14.75" spans="1:4">
-      <c r="A71" s="2">
+      <c r="A71" s="1">
         <v>42278</v>
       </c>
-      <c r="B71" s="15">
+      <c r="B71" s="14">
         <v>0.2277</v>
       </c>
-      <c r="C71" s="15"/>
-      <c r="D71" s="15"/>
+      <c r="C71" s="14"/>
+      <c r="D71" s="14"/>
     </row>
     <row r="72" ht="14.75" spans="1:4">
-      <c r="A72" s="2">
+      <c r="A72" s="1">
         <v>42309</v>
       </c>
-      <c r="B72" s="15">
+      <c r="B72" s="14">
         <v>0.3277</v>
       </c>
-      <c r="C72" s="15"/>
-      <c r="D72" s="15"/>
+      <c r="C72" s="14"/>
+      <c r="D72" s="14"/>
     </row>
     <row r="73" ht="14.75" spans="1:4">
-      <c r="A73" s="2">
+      <c r="A73" s="1">
         <v>42339</v>
       </c>
-      <c r="B73" s="15">
+      <c r="B73" s="14">
         <v>0.2392</v>
       </c>
-      <c r="C73" s="15"/>
-      <c r="D73" s="15"/>
+      <c r="C73" s="14"/>
+      <c r="D73" s="14"/>
     </row>
     <row r="74" ht="14.75" spans="1:4">
-      <c r="A74" s="16">
+      <c r="A74" s="15">
         <v>42370</v>
       </c>
-      <c r="B74" s="17">
+      <c r="B74" s="16">
         <v>-0.0084</v>
       </c>
-      <c r="C74" s="17"/>
-      <c r="D74" s="17"/>
+      <c r="C74" s="16"/>
+      <c r="D74" s="16"/>
     </row>
     <row r="75" ht="14.75" spans="1:4">
-      <c r="A75" s="2">
+      <c r="A75" s="1">
         <v>42401</v>
       </c>
-      <c r="B75" s="15">
+      <c r="B75" s="14">
         <v>0.0011</v>
       </c>
-      <c r="C75" s="15"/>
-      <c r="D75" s="15"/>
+      <c r="C75" s="14"/>
+      <c r="D75" s="14"/>
     </row>
     <row r="76" ht="14.75" spans="1:4">
-      <c r="A76" s="2">
+      <c r="A76" s="1">
         <v>42430</v>
       </c>
-      <c r="B76" s="15">
+      <c r="B76" s="14">
         <v>0.4005</v>
       </c>
-      <c r="C76" s="15"/>
-      <c r="D76" s="15"/>
+      <c r="C76" s="14"/>
+      <c r="D76" s="14"/>
     </row>
     <row r="77" ht="14.75" spans="1:4">
-      <c r="A77" s="2">
+      <c r="A77" s="1">
         <v>42461</v>
       </c>
-      <c r="B77" s="15">
+      <c r="B77" s="14">
         <v>0.0084</v>
       </c>
-      <c r="C77" s="15"/>
-      <c r="D77" s="15"/>
+      <c r="C77" s="14"/>
+      <c r="D77" s="14"/>
     </row>
     <row r="78" ht="14.75" spans="1:4">
-      <c r="A78" s="2">
+      <c r="A78" s="1">
         <v>42491</v>
       </c>
-      <c r="B78" s="15">
+      <c r="B78" s="14">
         <v>-0.0213</v>
       </c>
-      <c r="C78" s="15"/>
-      <c r="D78" s="15"/>
+      <c r="C78" s="14"/>
+      <c r="D78" s="14"/>
     </row>
     <row r="79" ht="14.75" spans="1:4">
-      <c r="A79" s="2">
+      <c r="A79" s="1">
         <v>42522</v>
       </c>
-      <c r="B79" s="15">
+      <c r="B79" s="14">
         <v>0.1059</v>
       </c>
-      <c r="C79" s="15"/>
-      <c r="D79" s="15"/>
+      <c r="C79" s="14"/>
+      <c r="D79" s="14"/>
     </row>
     <row r="80" ht="14.75" spans="1:4">
-      <c r="A80" s="2">
+      <c r="A80" s="1">
         <v>42552</v>
       </c>
-      <c r="B80" s="15">
+      <c r="B80" s="14">
         <v>0.0296</v>
       </c>
-      <c r="C80" s="15"/>
-      <c r="D80" s="15"/>
+      <c r="C80" s="14"/>
+      <c r="D80" s="14"/>
     </row>
     <row r="81" ht="14.75" spans="1:4">
-      <c r="A81" s="2">
+      <c r="A81" s="1">
         <v>42583</v>
       </c>
-      <c r="B81" s="15">
+      <c r="B81" s="14">
         <v>0.0412</v>
       </c>
-      <c r="C81" s="15"/>
-      <c r="D81" s="15"/>
+      <c r="C81" s="14"/>
+      <c r="D81" s="14"/>
     </row>
     <row r="82" ht="14.75" spans="1:4">
-      <c r="A82" s="2">
+      <c r="A82" s="1">
         <v>42614</v>
       </c>
-      <c r="B82" s="15">
+      <c r="B82" s="14">
         <v>0.0455</v>
       </c>
-      <c r="C82" s="15"/>
-      <c r="D82" s="15"/>
+      <c r="C82" s="14"/>
+      <c r="D82" s="14"/>
     </row>
     <row r="83" ht="14.75" spans="1:4">
-      <c r="A83" s="2">
+      <c r="A83" s="1">
         <v>42644</v>
       </c>
-      <c r="B83" s="15">
+      <c r="B83" s="14">
         <v>0.0609</v>
       </c>
-      <c r="C83" s="15"/>
-      <c r="D83" s="15"/>
+      <c r="C83" s="14"/>
+      <c r="D83" s="14"/>
     </row>
     <row r="84" ht="14.75" spans="1:4">
-      <c r="A84" s="2">
+      <c r="A84" s="1">
         <v>42675</v>
       </c>
-      <c r="B84" s="15">
+      <c r="B84" s="14">
         <v>0.0377</v>
       </c>
-      <c r="C84" s="15"/>
-      <c r="D84" s="15"/>
+      <c r="C84" s="14"/>
+      <c r="D84" s="14"/>
     </row>
     <row r="85" ht="14.75" spans="1:4">
-      <c r="A85" s="2">
+      <c r="A85" s="1">
         <v>42705</v>
       </c>
-      <c r="B85" s="15">
+      <c r="B85" s="14">
         <v>0.12</v>
       </c>
-      <c r="C85" s="15"/>
-      <c r="D85" s="15"/>
+      <c r="C85" s="14"/>
+      <c r="D85" s="14"/>
     </row>
     <row r="86" ht="14.75" spans="1:4">
-      <c r="A86" s="2">
+      <c r="A86" s="1">
         <v>42736</v>
       </c>
-      <c r="B86" s="15">
+      <c r="B86" s="14">
         <v>0.0177</v>
       </c>
-      <c r="C86" s="15"/>
-      <c r="D86" s="15"/>
+      <c r="C86" s="14"/>
+      <c r="D86" s="14"/>
     </row>
     <row r="87" ht="14.75" spans="1:4">
-      <c r="A87" s="2">
+      <c r="A87" s="1">
         <v>42767</v>
       </c>
-      <c r="B87" s="15">
+      <c r="B87" s="14">
         <v>0.0514</v>
       </c>
-      <c r="C87" s="15"/>
-      <c r="D87" s="15"/>
+      <c r="C87" s="14"/>
+      <c r="D87" s="14"/>
     </row>
     <row r="88" ht="14.75" spans="1:4">
-      <c r="A88" s="2">
+      <c r="A88" s="1">
         <v>42795</v>
       </c>
-      <c r="B88" s="15">
+      <c r="B88" s="14">
         <v>-0.0782</v>
       </c>
-      <c r="C88" s="15"/>
-      <c r="D88" s="15"/>
+      <c r="C88" s="14"/>
+      <c r="D88" s="14"/>
     </row>
     <row r="89" ht="14.75" spans="1:4">
-      <c r="A89" s="2">
+      <c r="A89" s="1">
         <v>42826</v>
       </c>
-      <c r="B89" s="15">
+      <c r="B89" s="14">
         <v>0.0085</v>
       </c>
-      <c r="C89" s="15"/>
-      <c r="D89" s="15"/>
+      <c r="C89" s="14"/>
+      <c r="D89" s="14"/>
     </row>
     <row r="90" ht="14.75" spans="1:4">
-      <c r="A90" s="2">
+      <c r="A90" s="1">
         <v>42856</v>
       </c>
-      <c r="B90" s="15">
+      <c r="B90" s="14">
         <v>-0.0614</v>
       </c>
-      <c r="C90" s="15"/>
-      <c r="D90" s="15"/>
+      <c r="C90" s="14"/>
+      <c r="D90" s="14"/>
     </row>
     <row r="91" ht="14.75" spans="1:4">
-      <c r="A91" s="2">
+      <c r="A91" s="1">
         <v>42887</v>
       </c>
-      <c r="B91" s="15">
+      <c r="B91" s="14">
         <v>0.0901</v>
       </c>
-      <c r="C91" s="15"/>
-      <c r="D91" s="15"/>
+      <c r="C91" s="14"/>
+      <c r="D91" s="14"/>
     </row>
     <row r="92" ht="14.75" spans="1:4">
-      <c r="A92" s="2">
+      <c r="A92" s="1">
         <v>42917</v>
       </c>
-      <c r="B92" s="15">
+      <c r="B92" s="14">
         <v>-0.0132</v>
       </c>
-      <c r="C92" s="15"/>
-      <c r="D92" s="15"/>
+      <c r="C92" s="14"/>
+      <c r="D92" s="14"/>
     </row>
     <row r="93" ht="14.75" spans="1:4">
-      <c r="A93" s="2">
+      <c r="A93" s="1">
         <v>42948</v>
       </c>
-      <c r="B93" s="15">
+      <c r="B93" s="14">
         <v>0.1779</v>
       </c>
-      <c r="C93" s="15"/>
-      <c r="D93" s="15"/>
+      <c r="C93" s="14"/>
+      <c r="D93" s="14"/>
     </row>
     <row r="94" ht="14.75" spans="1:4">
-      <c r="A94" s="2">
+      <c r="A94" s="1">
         <v>42979</v>
       </c>
-      <c r="B94" s="15">
+      <c r="B94" s="14">
         <v>0.0209</v>
       </c>
-      <c r="C94" s="15"/>
-      <c r="D94" s="15"/>
+      <c r="C94" s="14"/>
+      <c r="D94" s="14"/>
     </row>
     <row r="95" ht="14.75" spans="1:4">
-      <c r="A95" s="2">
+      <c r="A95" s="1">
         <v>43009</v>
       </c>
-      <c r="B95" s="15">
+      <c r="B95" s="14">
         <v>-0.0084</v>
       </c>
-      <c r="C95" s="15"/>
-      <c r="D95" s="15"/>
+      <c r="C95" s="14"/>
+      <c r="D95" s="14"/>
     </row>
     <row r="96" ht="14.75" spans="1:4">
-      <c r="A96" s="2">
+      <c r="A96" s="1">
         <v>43040</v>
       </c>
-      <c r="B96" s="15">
+      <c r="B96" s="14">
         <v>-0.0635</v>
       </c>
-      <c r="C96" s="15"/>
-      <c r="D96" s="15"/>
+      <c r="C96" s="14"/>
+      <c r="D96" s="14"/>
     </row>
     <row r="97" ht="14.75" spans="1:4">
-      <c r="A97" s="2">
+      <c r="A97" s="1">
         <v>43070</v>
       </c>
-      <c r="B97" s="15">
+      <c r="B97" s="14">
         <v>-0.0392</v>
       </c>
-      <c r="C97" s="15"/>
-      <c r="D97" s="15"/>
+      <c r="C97" s="14"/>
+      <c r="D97" s="14"/>
     </row>
     <row r="98" ht="14.75" spans="1:4">
-      <c r="A98" s="2">
+      <c r="A98" s="1">
         <v>43101</v>
       </c>
-      <c r="B98" s="15">
+      <c r="B98" s="14">
         <v>0.0243</v>
       </c>
-      <c r="C98" s="15"/>
-      <c r="D98" s="15"/>
+      <c r="C98" s="14"/>
+      <c r="D98" s="14"/>
     </row>
     <row r="99" ht="14.75" spans="1:4">
-      <c r="A99" s="2">
+      <c r="A99" s="1">
         <v>43132</v>
       </c>
-      <c r="B99" s="15">
+      <c r="B99" s="14">
         <v>0.0119</v>
       </c>
-      <c r="C99" s="15"/>
-      <c r="D99" s="15"/>
+      <c r="C99" s="14"/>
+      <c r="D99" s="14"/>
     </row>
     <row r="100" ht="14.75" spans="1:4">
-      <c r="A100" s="2">
+      <c r="A100" s="1">
         <v>43160</v>
       </c>
-      <c r="B100" s="15">
+      <c r="B100" s="14">
         <v>0.1099</v>
       </c>
-      <c r="C100" s="15"/>
-      <c r="D100" s="15"/>
+      <c r="C100" s="14"/>
+      <c r="D100" s="14"/>
     </row>
     <row r="101" ht="14.75" spans="1:4">
-      <c r="A101" s="2">
+      <c r="A101" s="1">
         <v>43191</v>
       </c>
-      <c r="B101" s="15">
+      <c r="B101" s="14">
         <v>0.0021</v>
       </c>
-      <c r="C101" s="15"/>
-      <c r="D101" s="15"/>
+      <c r="C101" s="14"/>
+      <c r="D101" s="14"/>
     </row>
     <row r="102" ht="14.75" spans="1:4">
-      <c r="A102" s="2">
+      <c r="A102" s="1">
         <v>43221</v>
       </c>
-      <c r="B102" s="15">
+      <c r="B102" s="14">
         <v>0.0257</v>
       </c>
-      <c r="C102" s="15"/>
-      <c r="D102" s="15"/>
+      <c r="C102" s="14"/>
+      <c r="D102" s="14"/>
     </row>
     <row r="103" ht="14.75" spans="1:4">
-      <c r="A103" s="2">
+      <c r="A103" s="1">
         <v>43252</v>
       </c>
-      <c r="B103" s="15">
+      <c r="B103" s="14">
         <v>-0.0844</v>
       </c>
-      <c r="C103" s="15"/>
-      <c r="D103" s="15"/>
+      <c r="C103" s="14"/>
+      <c r="D103" s="14"/>
     </row>
     <row r="104" ht="14.75" spans="1:4">
-      <c r="A104" s="2">
+      <c r="A104" s="1">
         <v>43282</v>
       </c>
-      <c r="B104" s="15">
+      <c r="B104" s="14">
         <v>0.1728</v>
       </c>
-      <c r="C104" s="15"/>
-      <c r="D104" s="15"/>
+      <c r="C104" s="14"/>
+      <c r="D104" s="14"/>
     </row>
     <row r="105" ht="14.75" spans="1:4">
-      <c r="A105" s="2">
+      <c r="A105" s="1">
         <v>43313</v>
       </c>
-      <c r="B105" s="15">
+      <c r="B105" s="14">
         <v>-0.071</v>
       </c>
-      <c r="C105" s="15"/>
-      <c r="D105" s="15"/>
+      <c r="C105" s="14"/>
+      <c r="D105" s="14"/>
     </row>
     <row r="106" ht="14.75" spans="1:4">
-      <c r="A106" s="2">
+      <c r="A106" s="1">
         <v>43344</v>
       </c>
-      <c r="B106" s="15">
+      <c r="B106" s="14">
         <v>0.0614</v>
       </c>
-      <c r="C106" s="15"/>
-      <c r="D106" s="15"/>
+      <c r="C106" s="14"/>
+      <c r="D106" s="14"/>
     </row>
     <row r="107" ht="14.75" spans="1:4">
-      <c r="A107" s="2">
+      <c r="A107" s="1">
         <v>43374</v>
       </c>
-      <c r="B107" s="15">
+      <c r="B107" s="14">
         <v>0.0711</v>
       </c>
-      <c r="C107" s="15"/>
-      <c r="D107" s="15"/>
+      <c r="C107" s="14"/>
+      <c r="D107" s="14"/>
     </row>
     <row r="108" ht="14.75" spans="1:4">
-      <c r="A108" s="2">
+      <c r="A108" s="1">
         <v>43405</v>
       </c>
-      <c r="B108" s="15">
+      <c r="B108" s="14">
         <v>0.1498</v>
       </c>
-      <c r="C108" s="15"/>
-      <c r="D108" s="15"/>
+      <c r="C108" s="14"/>
+      <c r="D108" s="14"/>
     </row>
     <row r="109" ht="14.75" spans="1:4">
-      <c r="A109" s="2">
+      <c r="A109" s="1">
         <v>43435</v>
       </c>
-      <c r="B109" s="15">
+      <c r="B109" s="14">
         <v>-0.0448</v>
       </c>
-      <c r="C109" s="15"/>
-      <c r="D109" s="15"/>
+      <c r="C109" s="14"/>
+      <c r="D109" s="14"/>
     </row>
     <row r="110" ht="14.75" spans="1:4">
-      <c r="A110" s="2">
+      <c r="A110" s="1">
         <v>43466</v>
       </c>
-      <c r="B110" s="15">
+      <c r="B110" s="14">
         <v>0.0143</v>
       </c>
-      <c r="C110" s="15"/>
-      <c r="D110" s="15"/>
+      <c r="C110" s="14"/>
+      <c r="D110" s="14"/>
     </row>
     <row r="111" ht="14.75" spans="1:4">
-      <c r="A111" s="2">
+      <c r="A111" s="1">
         <v>43497</v>
       </c>
-      <c r="B111" s="15">
+      <c r="B111" s="14">
         <v>0.1369</v>
       </c>
-      <c r="C111" s="15"/>
-      <c r="D111" s="15"/>
+      <c r="C111" s="14"/>
+      <c r="D111" s="14"/>
     </row>
     <row r="112" ht="14.75" spans="1:4">
-      <c r="A112" s="2">
+      <c r="A112" s="1">
         <v>43525</v>
       </c>
-      <c r="B112" s="15">
+      <c r="B112" s="14">
         <v>0.1862</v>
       </c>
-      <c r="C112" s="15"/>
-      <c r="D112" s="15"/>
+      <c r="C112" s="14"/>
+      <c r="D112" s="14"/>
     </row>
     <row r="113" ht="14.75" spans="1:4">
-      <c r="A113" s="2">
+      <c r="A113" s="1">
         <v>43556</v>
       </c>
-      <c r="B113" s="15">
+      <c r="B113" s="14">
         <v>0.0276</v>
       </c>
-      <c r="C113" s="15"/>
-      <c r="D113" s="15"/>
+      <c r="C113" s="14"/>
+      <c r="D113" s="14"/>
     </row>
     <row r="114" ht="14.75" spans="1:4">
-      <c r="A114" s="2">
+      <c r="A114" s="1">
         <v>43586</v>
       </c>
-      <c r="B114" s="15">
+      <c r="B114" s="14">
         <v>0.0582</v>
       </c>
-      <c r="C114" s="15"/>
-      <c r="D114" s="15"/>
+      <c r="C114" s="14"/>
+      <c r="D114" s="14"/>
     </row>
     <row r="115" ht="14.75" spans="1:4">
-      <c r="A115" s="2">
+      <c r="A115" s="1">
         <v>43617</v>
       </c>
-      <c r="B115" s="15">
+      <c r="B115" s="14">
         <v>0.0329</v>
       </c>
-      <c r="C115" s="15"/>
-      <c r="D115" s="15"/>
+      <c r="C115" s="14"/>
+      <c r="D115" s="14"/>
     </row>
     <row r="116" ht="14.75" spans="1:4">
-      <c r="A116" s="2">
+      <c r="A116" s="1">
         <v>43647</v>
       </c>
-      <c r="B116" s="15">
+      <c r="B116" s="14">
         <v>-0.0096</v>
       </c>
-      <c r="C116" s="15"/>
-      <c r="D116" s="15"/>
+      <c r="C116" s="14"/>
+      <c r="D116" s="14"/>
     </row>
     <row r="117" ht="14.75" spans="1:4">
-      <c r="A117" s="2">
+      <c r="A117" s="1">
         <v>43678</v>
       </c>
-      <c r="B117" s="15">
+      <c r="B117" s="14">
         <v>-0.0119</v>
       </c>
-      <c r="C117" s="15"/>
-      <c r="D117" s="15"/>
+      <c r="C117" s="14"/>
+      <c r="D117" s="14"/>
     </row>
     <row r="118" ht="14.75" spans="1:4">
-      <c r="A118" s="2">
+      <c r="A118" s="1">
         <v>43709</v>
       </c>
-      <c r="B118" s="15">
+      <c r="B118" s="14">
         <v>0.0449</v>
       </c>
-      <c r="C118" s="15"/>
-      <c r="D118" s="15"/>
+      <c r="C118" s="14"/>
+      <c r="D118" s="14"/>
     </row>
     <row r="119" ht="14.75" spans="1:4">
-      <c r="A119" s="2">
+      <c r="A119" s="1">
         <v>43739</v>
       </c>
-      <c r="B119" s="15">
+      <c r="B119" s="14">
         <v>-0.0117</v>
       </c>
-      <c r="C119" s="15"/>
-      <c r="D119" s="15"/>
+      <c r="C119" s="14"/>
+      <c r="D119" s="14"/>
     </row>
     <row r="120" ht="14.75" spans="1:4">
-      <c r="A120" s="2">
+      <c r="A120" s="1">
         <v>43770</v>
       </c>
-      <c r="B120" s="15">
+      <c r="B120" s="14">
         <v>-0.0051</v>
       </c>
-      <c r="C120" s="15"/>
-      <c r="D120" s="15"/>
+      <c r="C120" s="14"/>
+      <c r="D120" s="14"/>
     </row>
     <row r="121" ht="14.75" spans="1:4">
-      <c r="A121" s="2">
+      <c r="A121" s="1">
         <v>43800</v>
       </c>
-      <c r="B121" s="15">
+      <c r="B121" s="14">
         <v>0.1302</v>
       </c>
-      <c r="C121" s="15"/>
-      <c r="D121" s="15"/>
+      <c r="C121" s="14"/>
+      <c r="D121" s="14"/>
     </row>
     <row r="122" ht="14.75" spans="1:4">
-      <c r="A122" s="2">
+      <c r="A122" s="1">
         <v>43831</v>
       </c>
-      <c r="B122" s="15">
+      <c r="B122" s="14">
         <v>0.0099</v>
       </c>
-      <c r="C122" s="15"/>
-      <c r="D122" s="15"/>
+      <c r="C122" s="14"/>
+      <c r="D122" s="14"/>
     </row>
     <row r="123" ht="14.75" spans="1:4">
-      <c r="A123" s="2">
+      <c r="A123" s="1">
         <v>43862</v>
       </c>
-      <c r="B123" s="15">
+      <c r="B123" s="14">
         <v>0.0369</v>
       </c>
-      <c r="C123" s="15"/>
-      <c r="D123" s="15"/>
+      <c r="C123" s="14"/>
+      <c r="D123" s="14"/>
     </row>
     <row r="124" ht="14.75" spans="1:4">
-      <c r="A124" s="2">
+      <c r="A124" s="1">
         <v>43891</v>
       </c>
-      <c r="B124" s="15">
+      <c r="B124" s="14">
         <v>0.0595</v>
       </c>
-      <c r="C124" s="15"/>
-      <c r="D124" s="15"/>
+      <c r="C124" s="14"/>
+      <c r="D124" s="14"/>
     </row>
     <row r="125" ht="14.75" spans="1:4">
-      <c r="A125" s="2">
+      <c r="A125" s="1">
         <v>43922</v>
       </c>
-      <c r="B125" s="15">
+      <c r="B125" s="14">
         <v>0.0314</v>
       </c>
-      <c r="C125" s="15"/>
-      <c r="D125" s="15"/>
+      <c r="C125" s="14"/>
+      <c r="D125" s="14"/>
     </row>
     <row r="126" ht="14.75" spans="1:4">
-      <c r="A126" s="2">
+      <c r="A126" s="1">
         <v>43952</v>
       </c>
-      <c r="B126" s="15">
+      <c r="B126" s="14">
         <v>0.0684</v>
       </c>
-      <c r="C126" s="15"/>
-      <c r="D126" s="15"/>
+      <c r="C126" s="14"/>
+      <c r="D126" s="14"/>
     </row>
     <row r="127" ht="14.75" spans="1:4">
-      <c r="A127" s="2">
+      <c r="A127" s="1">
         <v>43983</v>
       </c>
-      <c r="B127" s="15">
+      <c r="B127" s="14">
         <v>0.0866</v>
       </c>
-      <c r="C127" s="15"/>
-      <c r="D127" s="15"/>
+      <c r="C127" s="14"/>
+      <c r="D127" s="14"/>
     </row>
     <row r="128" ht="14.75" spans="1:4">
-      <c r="A128" s="2">
+      <c r="A128" s="1">
         <v>44013</v>
       </c>
-      <c r="B128" s="15">
+      <c r="B128" s="14">
         <v>0.0961</v>
       </c>
-      <c r="C128" s="15"/>
-      <c r="D128" s="15"/>
+      <c r="C128" s="14"/>
+      <c r="D128" s="14"/>
     </row>
     <row r="129" ht="14.75" spans="1:4">
-      <c r="A129" s="2">
+      <c r="A129" s="1">
         <v>44044</v>
       </c>
-      <c r="B129" s="15">
+      <c r="B129" s="14">
         <v>0.1462</v>
       </c>
-      <c r="C129" s="15"/>
-      <c r="D129" s="15"/>
+      <c r="C129" s="14"/>
+      <c r="D129" s="14"/>
     </row>
     <row r="130" ht="14.75" spans="1:4">
-      <c r="A130" s="2">
+      <c r="A130" s="1">
         <v>44075</v>
       </c>
-      <c r="B130" s="15">
+      <c r="B130" s="14">
         <v>-0.0312</v>
       </c>
-      <c r="C130" s="15"/>
-      <c r="D130" s="15"/>
+      <c r="C130" s="14"/>
+      <c r="D130" s="14"/>
     </row>
     <row r="131" ht="14.75" spans="1:4">
-      <c r="A131" s="2">
+      <c r="A131" s="1">
         <v>44105</v>
       </c>
-      <c r="B131" s="15">
+      <c r="B131" s="14">
         <v>0.0274</v>
       </c>
-      <c r="C131" s="15"/>
-      <c r="D131" s="15"/>
+      <c r="C131" s="14"/>
+      <c r="D131" s="14"/>
     </row>
     <row r="132" ht="14.75" spans="1:4">
-      <c r="A132" s="2">
+      <c r="A132" s="1">
         <v>44136</v>
       </c>
-      <c r="B132" s="15">
+      <c r="B132" s="14">
         <v>0.0181</v>
       </c>
-      <c r="C132" s="15"/>
-      <c r="D132" s="15"/>
+      <c r="C132" s="14"/>
+      <c r="D132" s="14"/>
     </row>
     <row r="133" ht="14.75" spans="1:4">
-      <c r="A133" s="2">
+      <c r="A133" s="1">
         <v>44166</v>
       </c>
-      <c r="B133" s="15">
+      <c r="B133" s="14">
         <v>-0.112</v>
       </c>
-      <c r="C133" s="15"/>
-      <c r="D133" s="15"/>
+      <c r="C133" s="14"/>
+      <c r="D133" s="14"/>
     </row>
     <row r="134" ht="14.75" spans="1:4">
-      <c r="A134" s="2">
+      <c r="A134" s="1">
         <v>44197</v>
       </c>
-      <c r="B134" s="15">
+      <c r="B134" s="14">
         <v>0.0077</v>
       </c>
-      <c r="C134" s="15"/>
-      <c r="D134" s="15"/>
+      <c r="C134" s="14"/>
+      <c r="D134" s="14"/>
     </row>
     <row r="135" ht="14.75" spans="1:4">
-      <c r="A135" s="2">
+      <c r="A135" s="1">
         <v>44228</v>
       </c>
-      <c r="B135" s="15">
+      <c r="B135" s="14">
         <v>0.1271</v>
       </c>
-      <c r="C135" s="15"/>
-      <c r="D135" s="15"/>
+      <c r="C135" s="14"/>
+      <c r="D135" s="14"/>
     </row>
     <row r="136" ht="14.75" spans="1:4">
-      <c r="A136" s="2">
+      <c r="A136" s="1">
         <v>44256</v>
       </c>
-      <c r="B136" s="15">
+      <c r="B136" s="14">
         <v>0.1564</v>
       </c>
-      <c r="C136" s="15"/>
-      <c r="D136" s="15"/>
+      <c r="C136" s="14"/>
+      <c r="D136" s="14"/>
     </row>
     <row r="137" ht="14.75" spans="1:4">
-      <c r="A137" s="2">
+      <c r="A137" s="1">
         <v>44287</v>
       </c>
-      <c r="B137" s="15">
+      <c r="B137" s="14">
         <v>-0.0061</v>
       </c>
-      <c r="C137" s="15"/>
-      <c r="D137" s="15"/>
+      <c r="C137" s="14"/>
+      <c r="D137" s="14"/>
     </row>
     <row r="138" ht="14.75" spans="1:4">
-      <c r="A138" s="2">
+      <c r="A138" s="1">
         <v>44317</v>
       </c>
-      <c r="B138" s="15">
+      <c r="B138" s="14">
         <v>0.0562</v>
       </c>
-      <c r="C138" s="15"/>
-      <c r="D138" s="15"/>
+      <c r="C138" s="14"/>
+      <c r="D138" s="14"/>
     </row>
     <row r="139" ht="14.75" spans="1:4">
-      <c r="A139" s="2">
+      <c r="A139" s="1">
         <v>44348</v>
       </c>
-      <c r="B139" s="15">
+      <c r="B139" s="14">
         <v>0.0235</v>
       </c>
-      <c r="C139" s="15"/>
-      <c r="D139" s="15"/>
+      <c r="C139" s="14"/>
+      <c r="D139" s="14"/>
     </row>
     <row r="140" ht="14.75" spans="1:4">
-      <c r="A140" s="2">
+      <c r="A140" s="1">
         <v>44378</v>
       </c>
-      <c r="B140" s="15">
+      <c r="B140" s="14">
         <v>-0.0538</v>
       </c>
-      <c r="C140" s="15"/>
-      <c r="D140" s="15"/>
+      <c r="C140" s="14"/>
+      <c r="D140" s="14"/>
     </row>
     <row r="141" ht="14.75" spans="1:4">
-      <c r="A141" s="2">
+      <c r="A141" s="1">
         <v>44409</v>
       </c>
-      <c r="B141" s="15">
+      <c r="B141" s="14">
         <v>0.0861</v>
       </c>
-      <c r="C141" s="15"/>
-      <c r="D141" s="15"/>
+      <c r="C141" s="14"/>
+      <c r="D141" s="14"/>
     </row>
     <row r="142" ht="14.75" spans="1:4">
-      <c r="A142" s="2">
+      <c r="A142" s="1">
         <v>44440</v>
       </c>
-      <c r="B142" s="15">
+      <c r="B142" s="14">
         <v>-0.0215</v>
       </c>
-      <c r="C142" s="15"/>
-      <c r="D142" s="15"/>
+      <c r="C142" s="14"/>
+      <c r="D142" s="14"/>
     </row>
     <row r="143" ht="14.75" spans="1:4">
-      <c r="A143" s="2">
+      <c r="A143" s="1">
         <v>44470</v>
       </c>
-      <c r="B143" s="15">
+      <c r="B143" s="14">
         <v>-0.0512</v>
       </c>
-      <c r="C143" s="15"/>
-      <c r="D143" s="15"/>
+      <c r="C143" s="14"/>
+      <c r="D143" s="14"/>
     </row>
     <row r="144" ht="14.75" spans="1:4">
-      <c r="A144" s="2">
+      <c r="A144" s="1">
         <v>44501</v>
       </c>
-      <c r="B144" s="15">
+      <c r="B144" s="14">
         <v>0.1091</v>
       </c>
-      <c r="C144" s="15"/>
-      <c r="D144" s="15"/>
+      <c r="C144" s="14"/>
+      <c r="D144" s="14"/>
     </row>
     <row r="145" ht="14.75" spans="1:4">
-      <c r="A145" s="2">
+      <c r="A145" s="1">
         <v>44531</v>
       </c>
-      <c r="B145" s="15">
+      <c r="B145" s="14">
         <v>0.1123</v>
       </c>
-      <c r="C145" s="15"/>
-      <c r="D145" s="15"/>
+      <c r="C145" s="14"/>
+      <c r="D145" s="14"/>
     </row>
     <row r="146" ht="14.75" spans="1:4">
-      <c r="A146" s="2">
+      <c r="A146" s="1">
         <v>44562</v>
       </c>
-      <c r="B146" s="15">
+      <c r="B146" s="14">
         <v>-0.0016</v>
       </c>
-      <c r="C146" s="15"/>
-      <c r="D146" s="15"/>
+      <c r="C146" s="14"/>
+      <c r="D146" s="14"/>
     </row>
     <row r="147" ht="14.75" spans="1:4">
-      <c r="A147" s="2">
+      <c r="A147" s="1">
         <v>44593</v>
       </c>
-      <c r="B147" s="15">
+      <c r="B147" s="14">
         <v>0.0797</v>
       </c>
-      <c r="C147" s="15"/>
-      <c r="D147" s="15"/>
+      <c r="C147" s="14"/>
+      <c r="D147" s="14"/>
     </row>
     <row r="148" ht="14.75" spans="1:4">
-      <c r="A148" s="2">
+      <c r="A148" s="1">
         <v>44621</v>
       </c>
-      <c r="B148" s="15">
+      <c r="B148" s="14">
         <v>0.0547</v>
       </c>
-      <c r="C148" s="15"/>
-      <c r="D148" s="15"/>
+      <c r="C148" s="14"/>
+      <c r="D148" s="14"/>
     </row>
     <row r="149" ht="14.75" spans="1:4">
-      <c r="A149" s="2">
+      <c r="A149" s="1">
         <v>44652</v>
       </c>
-      <c r="B149" s="15">
+      <c r="B149" s="14">
         <v>-0.0187</v>
       </c>
-      <c r="C149" s="15"/>
-      <c r="D149" s="15"/>
+      <c r="C149" s="14"/>
+      <c r="D149" s="14"/>
     </row>
     <row r="150" ht="14.75" spans="1:4">
-      <c r="A150" s="2">
+      <c r="A150" s="1">
         <v>44682</v>
       </c>
-      <c r="B150" s="15">
+      <c r="B150" s="14">
         <v>0.2725</v>
       </c>
-      <c r="C150" s="15"/>
-      <c r="D150" s="15"/>
+      <c r="C150" s="14"/>
+      <c r="D150" s="14"/>
     </row>
     <row r="151" ht="14.75" spans="1:4">
-      <c r="A151" s="2">
+      <c r="A151" s="1">
         <v>44713</v>
       </c>
-      <c r="B151" s="15">
+      <c r="B151" s="14">
         <v>0.1417</v>
       </c>
-      <c r="C151" s="15"/>
-      <c r="D151" s="15"/>
+      <c r="C151" s="14"/>
+      <c r="D151" s="14"/>
     </row>
     <row r="152" ht="14.75" spans="1:4">
-      <c r="A152" s="2">
+      <c r="A152" s="1">
         <v>44743</v>
       </c>
-      <c r="B152" s="15">
+      <c r="B152" s="14">
         <v>0.2166</v>
       </c>
-      <c r="C152" s="15"/>
-      <c r="D152" s="15"/>
+      <c r="C152" s="14"/>
+      <c r="D152" s="14"/>
     </row>
     <row r="153" ht="14.75" spans="1:4">
-      <c r="A153" s="2">
+      <c r="A153" s="1">
         <v>44774</v>
       </c>
-      <c r="B153" s="15">
+      <c r="B153" s="14">
         <v>0.1873</v>
       </c>
-      <c r="C153" s="15"/>
-      <c r="D153" s="15"/>
+      <c r="C153" s="14"/>
+      <c r="D153" s="14"/>
     </row>
     <row r="154" ht="14.75" spans="1:4">
-      <c r="A154" s="2">
+      <c r="A154" s="1">
         <v>44805</v>
       </c>
-      <c r="B154" s="15">
+      <c r="B154" s="14">
         <v>0.0367</v>
       </c>
-      <c r="C154" s="15"/>
-      <c r="D154" s="15"/>
+      <c r="C154" s="14"/>
+      <c r="D154" s="14"/>
     </row>
     <row r="155" ht="14.75" spans="1:4">
-      <c r="A155" s="2">
+      <c r="A155" s="1">
         <v>44835</v>
       </c>
-      <c r="B155" s="15">
+      <c r="B155" s="14">
         <v>0.0711</v>
       </c>
-      <c r="C155" s="15"/>
-      <c r="D155" s="15"/>
+      <c r="C155" s="14"/>
+      <c r="D155" s="14"/>
     </row>
     <row r="156" ht="14.75" spans="1:4">
-      <c r="A156" s="2">
+      <c r="A156" s="1">
         <v>44866</v>
       </c>
-      <c r="B156" s="15">
+      <c r="B156" s="14">
         <v>0.1051</v>
       </c>
-      <c r="C156" s="15"/>
-      <c r="D156" s="15"/>
+      <c r="C156" s="14"/>
+      <c r="D156" s="14"/>
     </row>
     <row r="157" ht="14.75" spans="1:4">
-      <c r="A157" s="2">
+      <c r="A157" s="1">
         <v>44896</v>
       </c>
-      <c r="B157" s="15">
+      <c r="B157" s="14">
         <v>0.0431</v>
       </c>
-      <c r="C157" s="15"/>
-      <c r="D157" s="15"/>
+      <c r="C157" s="14"/>
+      <c r="D157" s="14"/>
     </row>
     <row r="158" ht="14.75" spans="1:4">
-      <c r="A158" s="2">
+      <c r="A158" s="1">
         <v>44927</v>
       </c>
-      <c r="B158" s="15">
+      <c r="B158" s="14">
         <v>0.0148</v>
       </c>
-      <c r="C158" s="15"/>
-      <c r="D158" s="15"/>
+      <c r="C158" s="14"/>
+      <c r="D158" s="14"/>
     </row>
     <row r="159" ht="14.75" spans="1:4">
-      <c r="A159" s="2">
+      <c r="A159" s="1">
         <v>44958</v>
       </c>
-      <c r="B159" s="15">
+      <c r="B159" s="14">
         <v>0.0113</v>
       </c>
-      <c r="C159" s="15"/>
-      <c r="D159" s="15"/>
+      <c r="C159" s="14"/>
+      <c r="D159" s="14"/>
     </row>
     <row r="160" ht="14.75" spans="1:4">
-      <c r="A160" s="2">
+      <c r="A160" s="1">
         <v>44986</v>
       </c>
-      <c r="B160" s="15">
+      <c r="B160" s="14">
         <v>-0.0182</v>
       </c>
-      <c r="C160" s="15"/>
-      <c r="D160" s="15"/>
+      <c r="C160" s="14"/>
+      <c r="D160" s="14"/>
     </row>
     <row r="161" ht="14.75" spans="1:4">
-      <c r="A161" s="2">
+      <c r="A161" s="1">
         <v>45017</v>
       </c>
-      <c r="B161" s="15">
+      <c r="B161" s="14">
         <v>0.0234</v>
       </c>
-      <c r="C161" s="15"/>
-      <c r="D161" s="15"/>
+      <c r="C161" s="14"/>
+      <c r="D161" s="14"/>
     </row>
     <row r="162" ht="14.75" spans="1:4">
-      <c r="A162" s="2">
+      <c r="A162" s="1">
         <v>45047</v>
       </c>
-      <c r="B162" s="15">
+      <c r="B162" s="14">
         <v>0.0327</v>
       </c>
-      <c r="C162" s="15"/>
-      <c r="D162" s="15"/>
+      <c r="C162" s="14"/>
+      <c r="D162" s="14"/>
     </row>
     <row r="163" ht="14.75" spans="1:4">
-      <c r="A163" s="2">
+      <c r="A163" s="1">
         <v>45078</v>
       </c>
-      <c r="B163" s="15">
+      <c r="B163" s="14">
         <v>0.047</v>
       </c>
-      <c r="C163" s="15"/>
-      <c r="D163" s="15"/>
+      <c r="C163" s="14"/>
+      <c r="D163" s="14"/>
     </row>
     <row r="164" ht="14.75" spans="1:4">
-      <c r="A164" s="2">
+      <c r="A164" s="1">
         <v>45108</v>
       </c>
-      <c r="B164" s="15">
+      <c r="B164" s="14">
         <v>0.1586</v>
       </c>
-      <c r="C164" s="15"/>
-      <c r="D164" s="15"/>
+      <c r="C164" s="14"/>
+      <c r="D164" s="14"/>
     </row>
     <row r="165" ht="14.75" spans="1:4">
-      <c r="A165" s="2">
+      <c r="A165" s="1">
         <v>45139</v>
       </c>
-      <c r="B165" s="15">
+      <c r="B165" s="14">
         <v>-0.021</v>
       </c>
-      <c r="C165" s="15"/>
-      <c r="D165" s="15"/>
+      <c r="C165" s="14"/>
+      <c r="D165" s="14"/>
     </row>
     <row r="166" ht="14.75" spans="1:4">
-      <c r="A166" s="2">
+      <c r="A166" s="1">
         <v>45170</v>
       </c>
-      <c r="B166" s="15">
+      <c r="B166" s="14">
         <v>0.024</v>
       </c>
-      <c r="C166" s="15"/>
-      <c r="D166" s="15"/>
+      <c r="C166" s="14"/>
+      <c r="D166" s="14"/>
     </row>
     <row r="167" ht="14.75" spans="1:4">
-      <c r="A167" s="2">
+      <c r="A167" s="1">
         <v>45200</v>
       </c>
-      <c r="B167" s="15">
+      <c r="B167" s="14">
         <v>0.0474</v>
       </c>
-      <c r="C167" s="15"/>
-      <c r="D167" s="15"/>
+      <c r="C167" s="14"/>
+      <c r="D167" s="14"/>
     </row>
     <row r="168" ht="14.75" spans="1:4">
-      <c r="A168" s="2">
+      <c r="A168" s="1">
         <v>45231</v>
       </c>
-      <c r="B168" s="15">
+      <c r="B168" s="14">
         <v>0.1049</v>
       </c>
-      <c r="C168" s="15"/>
-      <c r="D168" s="15"/>
+      <c r="C168" s="14"/>
+      <c r="D168" s="14"/>
     </row>
     <row r="169" ht="14.75" spans="1:4">
-      <c r="A169" s="2">
+      <c r="A169" s="1">
         <v>45261</v>
       </c>
-      <c r="B169" s="15">
+      <c r="B169" s="14">
         <v>-0.0024</v>
       </c>
-      <c r="C169" s="15"/>
-      <c r="D169" s="15"/>
+      <c r="C169" s="14"/>
+      <c r="D169" s="14"/>
     </row>
     <row r="170" ht="14.75" spans="1:4">
-      <c r="A170" s="2">
+      <c r="A170" s="1">
         <v>45292</v>
       </c>
-      <c r="B170" s="15">
+      <c r="B170" s="14">
         <v>0.0587</v>
       </c>
-      <c r="C170" s="15"/>
-      <c r="D170" s="15"/>
+      <c r="C170" s="14"/>
+      <c r="D170" s="14"/>
     </row>
     <row r="171" ht="14.75" spans="1:4">
-      <c r="A171" s="2">
+      <c r="A171" s="1">
         <v>45323</v>
       </c>
-      <c r="B171" s="15">
+      <c r="B171" s="14">
         <v>0.1895</v>
       </c>
-      <c r="C171" s="15"/>
-      <c r="D171" s="15"/>
+      <c r="C171" s="14"/>
+      <c r="D171" s="14"/>
     </row>
     <row r="172" ht="14.75" spans="1:4">
-      <c r="A172" s="2">
+      <c r="A172" s="1">
         <v>45352</v>
       </c>
-      <c r="B172" s="15">
+      <c r="B172" s="14">
         <v>0.2207</v>
       </c>
-      <c r="C172" s="15"/>
-      <c r="D172" s="15"/>
+      <c r="C172" s="14"/>
+      <c r="D172" s="14"/>
     </row>
     <row r="173" ht="14.75" spans="1:4">
-      <c r="A173" s="2">
+      <c r="A173" s="1">
         <v>45383</v>
       </c>
-      <c r="B173" s="15">
+      <c r="B173" s="14">
         <v>0.0343</v>
       </c>
-      <c r="C173" s="15"/>
-      <c r="D173" s="15"/>
+      <c r="C173" s="14"/>
+      <c r="D173" s="14"/>
     </row>
     <row r="174" ht="14.75" spans="1:4">
-      <c r="A174" s="2">
+      <c r="A174" s="1">
         <v>45413</v>
       </c>
-      <c r="B174" s="15">
+      <c r="B174" s="14">
         <v>-0.0156</v>
       </c>
-      <c r="C174" s="15"/>
-      <c r="D174" s="15"/>
+      <c r="C174" s="14"/>
+      <c r="D174" s="14"/>
     </row>
     <row r="175" ht="14.75" spans="1:4">
-      <c r="A175" s="2">
+      <c r="A175" s="1">
         <v>45444</v>
       </c>
-      <c r="B175" s="15">
+      <c r="B175" s="14">
         <v>-0.1354</v>
       </c>
-      <c r="C175" s="15"/>
-      <c r="D175" s="15"/>
+      <c r="C175" s="14"/>
+      <c r="D175" s="14"/>
     </row>
     <row r="176" ht="14.75" spans="1:4">
-      <c r="A176" s="2">
+      <c r="A176" s="1">
         <v>45474</v>
       </c>
-      <c r="B176" s="15">
+      <c r="B176" s="14">
         <v>0.1169</v>
       </c>
-      <c r="C176" s="15"/>
-      <c r="D176" s="15"/>
+      <c r="C176" s="14"/>
+      <c r="D176" s="14"/>
     </row>
     <row r="177" ht="14.75" spans="1:4">
-      <c r="A177" s="2">
+      <c r="A177" s="1">
         <v>45505</v>
       </c>
-      <c r="B177" s="15">
+      <c r="B177" s="14">
         <v>0.1481</v>
       </c>
-      <c r="C177" s="15"/>
-      <c r="D177" s="15"/>
+      <c r="C177" s="14"/>
+      <c r="D177" s="14"/>
     </row>
     <row r="178" ht="14.75" spans="1:4">
-      <c r="A178" s="2">
+      <c r="A178" s="1">
         <v>45536</v>
       </c>
-      <c r="B178" s="15">
+      <c r="B178" s="14">
         <v>0.2549</v>
       </c>
-      <c r="C178" s="15"/>
-      <c r="D178" s="15"/>
+      <c r="C178" s="14"/>
+      <c r="D178" s="14"/>
     </row>
     <row r="179" ht="14.75" spans="1:4">
-      <c r="A179" s="2">
+      <c r="A179" s="1">
         <v>45566</v>
       </c>
-      <c r="B179" s="15">
+      <c r="B179" s="14">
         <v>0.2231</v>
       </c>
-      <c r="C179" s="15"/>
-      <c r="D179" s="15"/>
+      <c r="C179" s="14"/>
+      <c r="D179" s="14"/>
     </row>
     <row r="180" ht="14.75" spans="1:4">
-      <c r="A180" s="2">
+      <c r="A180" s="1">
         <v>45597</v>
       </c>
-      <c r="B180" s="15">
+      <c r="B180" s="14">
         <v>0.1335</v>
       </c>
-      <c r="C180" s="15"/>
-      <c r="D180" s="15"/>
+      <c r="C180" s="14"/>
+      <c r="D180" s="14"/>
     </row>
     <row r="181" ht="14.75" spans="1:4">
-      <c r="A181" s="2">
+      <c r="A181" s="1">
         <v>45627</v>
       </c>
-      <c r="B181" s="15">
+      <c r="B181" s="14">
         <v>0.0415</v>
       </c>
-      <c r="C181" s="15"/>
-      <c r="D181" s="15"/>
+      <c r="C181" s="14"/>
+      <c r="D181" s="14"/>
     </row>
     <row r="182" ht="14.75" spans="1:4">
-      <c r="A182" s="2">
+      <c r="A182" s="1">
         <v>45658</v>
       </c>
-      <c r="B182" s="15">
+      <c r="B182" s="14">
         <v>-0.0074</v>
       </c>
-      <c r="C182" s="15"/>
-      <c r="D182" s="15"/>
+      <c r="C182" s="14"/>
+      <c r="D182" s="14"/>
     </row>
     <row r="183" ht="14.75" spans="1:4">
-      <c r="A183" s="2">
+      <c r="A183" s="1">
         <v>45689</v>
       </c>
-      <c r="B183" s="15">
+      <c r="B183" s="14">
         <v>0.2489</v>
       </c>
-      <c r="C183" s="15"/>
-      <c r="D183" s="15"/>
+      <c r="C183" s="14"/>
+      <c r="D183" s="14"/>
     </row>
     <row r="184" ht="14.75" spans="1:4">
-      <c r="A184" s="2">
+      <c r="A184" s="1">
         <v>45717</v>
       </c>
-      <c r="B184" s="15">
+      <c r="B184" s="14">
         <v>-0.0711</v>
       </c>
-      <c r="C184" s="15"/>
-      <c r="D184" s="15"/>
+      <c r="C184" s="14"/>
+      <c r="D184" s="14"/>
     </row>
     <row r="185" ht="14.75" spans="1:4">
-      <c r="A185" s="2">
+      <c r="A185" s="1">
         <v>45748</v>
       </c>
-      <c r="B185" s="15">
+      <c r="B185" s="14">
         <v>0.0526</v>
       </c>
-      <c r="C185" s="15"/>
-      <c r="D185" s="15"/>
+      <c r="C185" s="14"/>
+      <c r="D185" s="14"/>
     </row>
     <row r="186" ht="14.75" spans="1:4">
-      <c r="A186" s="2">
+      <c r="A186" s="1">
         <v>45778</v>
       </c>
-      <c r="B186" s="15">
+      <c r="B186" s="14">
         <v>0.0431</v>
       </c>
-      <c r="C186" s="15"/>
-      <c r="D186" s="15"/>
+      <c r="C186" s="14"/>
+      <c r="D186" s="14"/>
     </row>
     <row r="187" ht="14.75" spans="1:4">
-      <c r="A187" s="2">
+      <c r="A187" s="1">
         <v>45809</v>
       </c>
-      <c r="B187" s="15">
+      <c r="B187" s="14">
         <v>0.1423</v>
       </c>
-      <c r="C187" s="15"/>
-      <c r="D187" s="15"/>
+      <c r="C187" s="14"/>
+      <c r="D187" s="14"/>
     </row>
     <row r="188" ht="14.75" spans="1:4">
-      <c r="A188" s="2">
+      <c r="A188" s="1">
         <v>45839</v>
       </c>
-      <c r="B188" s="15">
+      <c r="B188" s="14">
         <v>0.0876</v>
       </c>
-      <c r="C188" s="15"/>
-      <c r="D188" s="15"/>
+      <c r="C188" s="14"/>
+      <c r="D188" s="14"/>
     </row>
     <row r="189" ht="14.75" spans="1:4">
-      <c r="A189" s="2">
+      <c r="A189" s="1">
         <v>45870</v>
       </c>
-      <c r="B189" s="15">
+      <c r="B189" s="14">
         <v>-0.0326</v>
       </c>
-      <c r="C189" s="15"/>
-      <c r="D189" s="15"/>
+      <c r="C189" s="14"/>
+      <c r="D189" s="14"/>
     </row>
     <row r="190" ht="14.75" spans="1:4">
-      <c r="A190" s="2">
+      <c r="A190" s="1">
         <v>45901</v>
       </c>
-      <c r="B190" s="15">
+      <c r="B190" s="14">
         <v>0.1218</v>
       </c>
-      <c r="C190" s="15"/>
-      <c r="D190" s="15"/>
+      <c r="C190" s="14"/>
+      <c r="D190" s="14"/>
     </row>
     <row r="191" ht="14.75" spans="1:4">
-      <c r="A191" s="2">
+      <c r="A191" s="1">
         <v>45931</v>
       </c>
-      <c r="B191" s="15">
+      <c r="B191" s="14">
         <v>0.0044</v>
       </c>
-      <c r="C191" s="15"/>
-      <c r="D191" s="15"/>
+      <c r="C191" s="14"/>
+      <c r="D191" s="14"/>
     </row>
     <row r="192" ht="14.75" spans="1:4">
-      <c r="A192" s="2">
+      <c r="A192" s="1">
         <v>45962</v>
       </c>
-      <c r="B192" s="15">
+      <c r="B192" s="14">
         <v>0.0793</v>
       </c>
-      <c r="C192" s="15"/>
-      <c r="D192" s="15"/>
+      <c r="C192" s="14"/>
+      <c r="D192" s="14"/>
     </row>
     <row r="193" ht="14.75" spans="1:4">
-      <c r="A193" s="16">
+      <c r="A193" s="15">
         <v>45992</v>
       </c>
-      <c r="B193" s="17">
+      <c r="B193" s="16">
         <v>-0.0685</v>
       </c>
-      <c r="C193" s="17"/>
-      <c r="D193" s="17"/>
+      <c r="C193" s="16"/>
+      <c r="D193" s="16"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5985,7 +6041,7 @@
       </c>
     </row>
     <row r="2" ht="14.75" spans="1:21">
-      <c r="A2" s="2">
+      <c r="A2" s="1">
         <v>40179</v>
       </c>
       <c r="B2">
@@ -6036,7 +6092,7 @@
       <c r="Q2">
         <v>-0.0074</v>
       </c>
-      <c r="R2" s="13" cm="1">
+      <c r="R2" s="12" cm="1">
         <f t="array" ref="R2">PRODUCT(B2:Q2+1)-1</f>
         <v>0.194840242744342</v>
       </c>
@@ -6044,7 +6100,7 @@
         <f>SUM(B2:Q2)</f>
         <v>0.1812</v>
       </c>
-      <c r="T2" s="2">
+      <c r="T2" s="1">
         <v>40179</v>
       </c>
       <c r="U2">
@@ -6053,7 +6109,7 @@
       </c>
     </row>
     <row r="3" ht="14.75" spans="1:21">
-      <c r="A3" s="2">
+      <c r="A3" s="1">
         <v>40210</v>
       </c>
       <c r="B3">
@@ -6112,7 +6168,7 @@
         <f t="shared" ref="S3:S13" si="0">SUM(B3:Q3)</f>
         <v>1.4082</v>
       </c>
-      <c r="T3" s="2">
+      <c r="T3" s="1">
         <v>40210</v>
       </c>
       <c r="U3">
@@ -6121,7 +6177,7 @@
       </c>
     </row>
     <row r="4" ht="14.75" spans="1:21">
-      <c r="A4" s="2">
+      <c r="A4" s="1">
         <v>40238</v>
       </c>
       <c r="B4">
@@ -6180,7 +6236,7 @@
         <f t="shared" si="0"/>
         <v>1.3299</v>
       </c>
-      <c r="T4" s="2">
+      <c r="T4" s="1">
         <v>40238</v>
       </c>
       <c r="U4">
@@ -6189,7 +6245,7 @@
       </c>
     </row>
     <row r="5" ht="14.75" spans="1:21">
-      <c r="A5" s="2">
+      <c r="A5" s="1">
         <v>40269</v>
       </c>
       <c r="B5">
@@ -6240,7 +6296,7 @@
       <c r="Q5">
         <v>0.0526</v>
       </c>
-      <c r="R5" s="14" cm="1">
+      <c r="R5" s="13" cm="1">
         <f t="array" ref="R5">PRODUCT(B5:Q5+1)-1</f>
         <v>0.323510793037694</v>
       </c>
@@ -6248,7 +6304,7 @@
         <f t="shared" si="0"/>
         <v>0.2872</v>
       </c>
-      <c r="T5" s="2">
+      <c r="T5" s="1">
         <v>40269</v>
       </c>
       <c r="U5">
@@ -6257,7 +6313,7 @@
       </c>
     </row>
     <row r="6" ht="14.75" spans="1:21">
-      <c r="A6" s="2">
+      <c r="A6" s="1">
         <v>40299</v>
       </c>
       <c r="B6">
@@ -6308,7 +6364,7 @@
       <c r="Q6">
         <v>0.0431</v>
       </c>
-      <c r="R6" s="14" cm="1">
+      <c r="R6" s="13" cm="1">
         <f t="array" ref="R6">PRODUCT(B6:Q6+1)-1</f>
         <v>1.28723547337183</v>
       </c>
@@ -6316,7 +6372,7 @@
         <f t="shared" si="0"/>
         <v>0.955</v>
       </c>
-      <c r="T6" s="2">
+      <c r="T6" s="1">
         <v>40299</v>
       </c>
       <c r="U6">
@@ -6325,7 +6381,7 @@
       </c>
     </row>
     <row r="7" ht="14.75" spans="1:21">
-      <c r="A7" s="2">
+      <c r="A7" s="1">
         <v>40330</v>
       </c>
       <c r="B7">
@@ -6376,7 +6432,7 @@
       <c r="Q7">
         <v>0.1423</v>
       </c>
-      <c r="R7" s="14" cm="1">
+      <c r="R7" s="13" cm="1">
         <f t="array" ref="R7">PRODUCT(B7:Q7+1)-1</f>
         <v>0.595591661283158</v>
       </c>
@@ -6384,7 +6440,7 @@
         <f t="shared" si="0"/>
         <v>0.5492</v>
       </c>
-      <c r="T7" s="2">
+      <c r="T7" s="1">
         <v>40330</v>
       </c>
       <c r="U7">
@@ -6393,7 +6449,7 @@
       </c>
     </row>
     <row r="8" ht="14.75" spans="1:21">
-      <c r="A8" s="2">
+      <c r="A8" s="1">
         <v>40360</v>
       </c>
       <c r="B8">
@@ -6452,7 +6508,7 @@
         <f t="shared" si="0"/>
         <v>1.4965</v>
       </c>
-      <c r="T8" s="2">
+      <c r="T8" s="1">
         <v>40360</v>
       </c>
       <c r="U8">
@@ -6461,7 +6517,7 @@
       </c>
     </row>
     <row r="9" ht="14.75" spans="1:21">
-      <c r="A9" s="2">
+      <c r="A9" s="1">
         <v>40391</v>
       </c>
       <c r="B9">
@@ -6520,7 +6576,7 @@
         <f t="shared" si="0"/>
         <v>1.3491</v>
       </c>
-      <c r="T9" s="2">
+      <c r="T9" s="1">
         <v>40391</v>
       </c>
       <c r="U9">
@@ -6529,7 +6585,7 @@
       </c>
     </row>
     <row r="10" ht="14.75" spans="1:21">
-      <c r="A10" s="2">
+      <c r="A10" s="1">
         <v>40422</v>
       </c>
       <c r="B10">
@@ -6588,7 +6644,7 @@
         <f t="shared" si="0"/>
         <v>0.8786</v>
       </c>
-      <c r="T10" s="2">
+      <c r="T10" s="1">
         <v>40422</v>
       </c>
       <c r="U10">
@@ -6597,7 +6653,7 @@
       </c>
     </row>
     <row r="11" ht="14.75" spans="1:21">
-      <c r="A11" s="2">
+      <c r="A11" s="1">
         <v>40452</v>
       </c>
       <c r="B11">
@@ -6656,7 +6712,7 @@
         <f t="shared" si="0"/>
         <v>0.8179</v>
       </c>
-      <c r="T11" s="2">
+      <c r="T11" s="1">
         <v>40452</v>
       </c>
       <c r="U11">
@@ -6665,7 +6721,7 @@
       </c>
     </row>
     <row r="12" ht="14.75" spans="1:21">
-      <c r="A12" s="2">
+      <c r="A12" s="1">
         <v>40483</v>
       </c>
       <c r="B12">
@@ -6724,7 +6780,7 @@
         <f t="shared" si="0"/>
         <v>1.0945</v>
       </c>
-      <c r="T12" s="2">
+      <c r="T12" s="1">
         <v>40483</v>
       </c>
       <c r="U12">
@@ -6733,7 +6789,7 @@
       </c>
     </row>
     <row r="13" spans="1:21">
-      <c r="A13" s="2">
+      <c r="A13" s="1">
         <v>40513</v>
       </c>
       <c r="B13">
@@ -6792,7 +6848,7 @@
         <f t="shared" si="0"/>
         <v>0.368</v>
       </c>
-      <c r="T13" s="2">
+      <c r="T13" s="1">
         <v>40513</v>
       </c>
       <c r="U13">
@@ -6801,71 +6857,71 @@
       </c>
     </row>
     <row r="14" spans="2:18">
-      <c r="B14" s="10">
+      <c r="B14" s="9">
         <f>(1+B2)*(1+B3)*(1+B4)*(1+B5)*(1+B6)*(1+B7)*(1+B8)*(1+B9)*(1+B10)*(1+B11)*(1+B12)*(1+B13)-1</f>
         <v>0.653614174322446</v>
       </c>
-      <c r="C14" s="10">
+      <c r="C14" s="9">
         <f t="shared" ref="C14:Q14" si="2">(1+C2)*(1+C3)*(1+C4)*(1+C5)*(1+C6)*(1+C7)*(1+C8)*(1+C9)*(1+C10)*(1+C11)*(1+C12)*(1+C13)-1</f>
         <v>-0.0855664203647523</v>
       </c>
-      <c r="D14" s="10">
+      <c r="D14" s="9">
         <f t="shared" si="2"/>
         <v>0.0384573958480514</v>
       </c>
-      <c r="E14" s="10">
+      <c r="E14" s="9">
         <f t="shared" si="2"/>
         <v>0.765405002524292</v>
       </c>
-      <c r="F14" s="10">
+      <c r="F14" s="9">
         <f t="shared" si="2"/>
         <v>1.19935720490706</v>
       </c>
-      <c r="G14" s="10">
+      <c r="G14" s="9">
         <f t="shared" si="2"/>
         <v>5.98281172803228</v>
       </c>
-      <c r="H14" s="10">
+      <c r="H14" s="9">
         <f t="shared" si="2"/>
         <v>1.09694188883488</v>
       </c>
-      <c r="I14" s="10">
+      <c r="I14" s="9">
         <f t="shared" si="2"/>
         <v>0.0775695328691113</v>
       </c>
-      <c r="J14" s="10">
+      <c r="J14" s="9">
         <f t="shared" si="2"/>
         <v>0.472825224873327</v>
       </c>
-      <c r="K14" s="10">
+      <c r="K14" s="9">
         <f t="shared" si="2"/>
         <v>0.745848408003567</v>
       </c>
-      <c r="L14" s="10">
+      <c r="L14" s="9">
         <f t="shared" si="2"/>
         <v>0.501877778017195</v>
       </c>
-      <c r="M14" s="10">
+      <c r="M14" s="9">
         <f t="shared" si="2"/>
         <v>0.660960857965097</v>
       </c>
-      <c r="N14" s="10">
+      <c r="N14" s="9">
         <f t="shared" si="2"/>
         <v>1.99686467587207</v>
       </c>
-      <c r="O14" s="10">
+      <c r="O14" s="9">
         <f t="shared" si="2"/>
         <v>0.495057586521658</v>
       </c>
-      <c r="P14" s="10">
+      <c r="P14" s="9">
         <f t="shared" si="2"/>
         <v>2.14431144891796</v>
       </c>
-      <c r="Q14" s="10">
+      <c r="Q14" s="9">
         <f t="shared" si="2"/>
         <v>0.721324876500654</v>
       </c>
-      <c r="R14" s="10"/>
+      <c r="R14" s="9"/>
     </row>
     <row r="15" spans="2:17">
       <c r="B15">
@@ -6964,52 +7020,52 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Q29"/>
+  <dimension ref="A1:P45"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="12.5363636363636" customWidth="1"/>
     <col min="2" max="13" width="8.54545454545454" customWidth="1"/>
     <col min="14" max="14" width="13.9636363636364" customWidth="1"/>
     <col min="15" max="15" width="12.2727272727273" customWidth="1"/>
-    <col min="16" max="16" width="7.08181818181818" customWidth="1"/>
-    <col min="17" max="17" width="9.54545454545454"/>
+    <col min="16" max="16" width="8.08181818181818" customWidth="1"/>
+    <col min="17" max="18" width="9.54545454545454"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:15">
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="K1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="L1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="M1" s="1" t="s">
         <v>11</v>
       </c>
       <c r="N1" t="s">
@@ -7020,7 +7076,7 @@
       </c>
     </row>
     <row r="2" spans="1:16">
-      <c r="A2" s="3">
+      <c r="A2" s="2">
         <v>2010</v>
       </c>
       <c r="B2">
@@ -7059,20 +7115,20 @@
       <c r="M2">
         <v>-0.0207</v>
       </c>
-      <c r="N2" s="10">
+      <c r="N2" s="9">
         <f>(1+B2)*(1+C2)*(1+D2)*(1+E2)*(1+F2)*(1+G2)*(1+H2)*(1+I2)*(1+J2)*(1+K2)*(1+L2)*(1+M2)-1</f>
         <v>0.653614174322446</v>
       </c>
-      <c r="O2" s="9">
+      <c r="O2" s="8">
         <f>N2</f>
         <v>0.653614174322446</v>
       </c>
-      <c r="P2" s="3">
+      <c r="P2" s="2">
         <v>2010</v>
       </c>
     </row>
     <row r="3" spans="1:16">
-      <c r="A3" s="3">
+      <c r="A3" s="2">
         <v>2011</v>
       </c>
       <c r="B3">
@@ -7111,20 +7167,20 @@
       <c r="M3">
         <v>-0.1536</v>
       </c>
-      <c r="N3" s="10">
+      <c r="N3" s="9">
         <f>(1+B3)*(1+C3)*(1+D3)*(1+E3)*(1+F3)*(1+G3)*(1+H3)*(1+I3)*(1+J3)*(1+K3)*(1+L3)*(1+M3)-1</f>
         <v>-0.0855664203647523</v>
       </c>
-      <c r="O3" s="9">
+      <c r="O3" s="8">
         <f t="shared" ref="O3:O18" si="0">N3</f>
         <v>-0.0855664203647523</v>
       </c>
-      <c r="P3" s="3">
+      <c r="P3" s="2">
         <v>2011</v>
       </c>
     </row>
     <row r="4" spans="1:16">
-      <c r="A4" s="3">
+      <c r="A4" s="2">
         <v>2012</v>
       </c>
       <c r="B4">
@@ -7163,20 +7219,20 @@
       <c r="M4">
         <v>0.2375</v>
       </c>
-      <c r="N4" s="10">
+      <c r="N4" s="9">
         <f t="shared" ref="N2:N17" si="1">(1+B4)*(1+C4)*(1+D4)*(1+E4)*(1+F4)*(1+G4)*(1+H4)*(1+I4)*(1+J4)*(1+K4)*(1+L4)*(1+M4)-1</f>
         <v>0.0384573958480514</v>
       </c>
-      <c r="O4" s="9">
+      <c r="O4" s="8">
         <f t="shared" si="0"/>
         <v>0.0384573958480514</v>
       </c>
-      <c r="P4" s="3">
+      <c r="P4" s="2">
         <v>2012</v>
       </c>
     </row>
     <row r="5" spans="1:16">
-      <c r="A5" s="3">
+      <c r="A5" s="2">
         <v>2013</v>
       </c>
       <c r="B5">
@@ -7215,20 +7271,20 @@
       <c r="M5">
         <v>0.0207</v>
       </c>
-      <c r="N5" s="10">
+      <c r="N5" s="9">
         <f t="shared" si="1"/>
         <v>0.765405002524292</v>
       </c>
-      <c r="O5" s="9">
+      <c r="O5" s="8">
         <f t="shared" si="0"/>
         <v>0.765405002524292</v>
       </c>
-      <c r="P5" s="3">
+      <c r="P5" s="2">
         <v>2013</v>
       </c>
     </row>
     <row r="6" spans="1:16">
-      <c r="A6" s="3">
+      <c r="A6" s="2">
         <v>2014</v>
       </c>
       <c r="B6">
@@ -7267,20 +7323,20 @@
       <c r="M6">
         <v>-0.1353</v>
       </c>
-      <c r="N6" s="10">
+      <c r="N6" s="9">
         <f t="shared" si="1"/>
         <v>1.19935720490706</v>
       </c>
-      <c r="O6" s="9">
+      <c r="O6" s="8">
         <f t="shared" si="0"/>
         <v>1.19935720490706</v>
       </c>
-      <c r="P6" s="3">
+      <c r="P6" s="2">
         <v>2014</v>
       </c>
     </row>
     <row r="7" spans="1:16">
-      <c r="A7" s="3">
+      <c r="A7" s="2">
         <v>2015</v>
       </c>
       <c r="B7">
@@ -7319,20 +7375,20 @@
       <c r="M7">
         <v>0.2392</v>
       </c>
-      <c r="N7" s="10">
+      <c r="N7" s="9">
         <f t="shared" si="1"/>
         <v>5.98281172803228</v>
       </c>
-      <c r="O7" s="9">
+      <c r="O7" s="8">
         <f t="shared" si="0"/>
         <v>5.98281172803228</v>
       </c>
-      <c r="P7" s="3">
+      <c r="P7" s="2">
         <v>2015</v>
       </c>
     </row>
     <row r="8" spans="1:16">
-      <c r="A8" s="3">
+      <c r="A8" s="2">
         <v>2016</v>
       </c>
       <c r="B8">
@@ -7371,20 +7427,20 @@
       <c r="M8">
         <v>0.12</v>
       </c>
-      <c r="N8" s="10">
+      <c r="N8" s="9">
         <f t="shared" si="1"/>
         <v>1.09694188883488</v>
       </c>
-      <c r="O8" s="9">
+      <c r="O8" s="8">
         <f t="shared" si="0"/>
         <v>1.09694188883488</v>
       </c>
-      <c r="P8" s="3">
+      <c r="P8" s="2">
         <v>2016</v>
       </c>
     </row>
     <row r="9" spans="1:16">
-      <c r="A9" s="3">
+      <c r="A9" s="2">
         <v>2017</v>
       </c>
       <c r="B9">
@@ -7423,20 +7479,20 @@
       <c r="M9">
         <v>-0.0392</v>
       </c>
-      <c r="N9" s="10">
+      <c r="N9" s="9">
         <f t="shared" si="1"/>
         <v>0.0775695328691113</v>
       </c>
-      <c r="O9" s="9">
+      <c r="O9" s="8">
         <f t="shared" si="0"/>
         <v>0.0775695328691113</v>
       </c>
-      <c r="P9" s="3">
+      <c r="P9" s="2">
         <v>2017</v>
       </c>
     </row>
     <row r="10" spans="1:16">
-      <c r="A10" s="3">
+      <c r="A10" s="2">
         <v>2018</v>
       </c>
       <c r="B10">
@@ -7475,20 +7531,20 @@
       <c r="M10">
         <v>-0.0448</v>
       </c>
-      <c r="N10" s="10">
+      <c r="N10" s="9">
         <f t="shared" si="1"/>
         <v>0.472825224873327</v>
       </c>
-      <c r="O10" s="9">
+      <c r="O10" s="8">
         <f t="shared" si="0"/>
         <v>0.472825224873327</v>
       </c>
-      <c r="P10" s="3">
+      <c r="P10" s="2">
         <v>2018</v>
       </c>
     </row>
     <row r="11" spans="1:16">
-      <c r="A11" s="3">
+      <c r="A11" s="2">
         <v>2019</v>
       </c>
       <c r="B11">
@@ -7527,20 +7583,20 @@
       <c r="M11">
         <v>0.1302</v>
       </c>
-      <c r="N11" s="10">
+      <c r="N11" s="9">
         <f t="shared" si="1"/>
         <v>0.745848408003567</v>
       </c>
-      <c r="O11" s="9">
+      <c r="O11" s="8">
         <f t="shared" si="0"/>
         <v>0.745848408003567</v>
       </c>
-      <c r="P11" s="3">
+      <c r="P11" s="2">
         <v>2019</v>
       </c>
     </row>
     <row r="12" spans="1:16">
-      <c r="A12" s="3">
+      <c r="A12" s="2">
         <v>2020</v>
       </c>
       <c r="B12">
@@ -7579,20 +7635,20 @@
       <c r="M12">
         <v>-0.112</v>
       </c>
-      <c r="N12" s="10">
+      <c r="N12" s="9">
         <f t="shared" si="1"/>
         <v>0.501877778017195</v>
       </c>
-      <c r="O12" s="9">
+      <c r="O12" s="8">
         <f t="shared" si="0"/>
         <v>0.501877778017195</v>
       </c>
-      <c r="P12" s="3">
+      <c r="P12" s="2">
         <v>2020</v>
       </c>
     </row>
     <row r="13" spans="1:16">
-      <c r="A13" s="3">
+      <c r="A13" s="2">
         <v>2021</v>
       </c>
       <c r="B13">
@@ -7631,20 +7687,20 @@
       <c r="M13">
         <v>0.1123</v>
       </c>
-      <c r="N13" s="10">
+      <c r="N13" s="9">
         <f t="shared" si="1"/>
         <v>0.660960857965097</v>
       </c>
-      <c r="O13" s="9">
+      <c r="O13" s="8">
         <f t="shared" si="0"/>
         <v>0.660960857965097</v>
       </c>
-      <c r="P13" s="3">
+      <c r="P13" s="2">
         <v>2021</v>
       </c>
     </row>
     <row r="14" spans="1:16">
-      <c r="A14" s="3">
+      <c r="A14" s="2">
         <v>2022</v>
       </c>
       <c r="B14">
@@ -7683,20 +7739,20 @@
       <c r="M14">
         <v>0.0431</v>
       </c>
-      <c r="N14" s="10">
+      <c r="N14" s="9">
         <f t="shared" si="1"/>
         <v>1.99686467587207</v>
       </c>
-      <c r="O14" s="9">
+      <c r="O14" s="8">
         <f t="shared" si="0"/>
         <v>1.99686467587207</v>
       </c>
-      <c r="P14" s="3">
+      <c r="P14" s="2">
         <v>2022</v>
       </c>
     </row>
     <row r="15" spans="1:16">
-      <c r="A15" s="3">
+      <c r="A15" s="2">
         <v>2023</v>
       </c>
       <c r="B15">
@@ -7735,20 +7791,20 @@
       <c r="M15">
         <v>-0.0024</v>
       </c>
-      <c r="N15" s="10">
+      <c r="N15" s="9">
         <f t="shared" si="1"/>
         <v>0.495057586521658</v>
       </c>
-      <c r="O15" s="9">
+      <c r="O15" s="8">
         <f t="shared" si="0"/>
         <v>0.495057586521658</v>
       </c>
-      <c r="P15" s="3">
+      <c r="P15" s="2">
         <v>2023</v>
       </c>
     </row>
     <row r="16" spans="1:16">
-      <c r="A16" s="3">
+      <c r="A16" s="2">
         <v>2024</v>
       </c>
       <c r="B16">
@@ -7787,20 +7843,20 @@
       <c r="M16">
         <v>0.0415</v>
       </c>
-      <c r="N16" s="10">
+      <c r="N16" s="9">
         <f t="shared" si="1"/>
         <v>2.14431144891796</v>
       </c>
-      <c r="O16" s="9">
+      <c r="O16" s="8">
         <f t="shared" si="0"/>
         <v>2.14431144891796</v>
       </c>
-      <c r="P16" s="3">
+      <c r="P16" s="2">
         <v>2024</v>
       </c>
     </row>
     <row r="17" spans="1:16">
-      <c r="A17" s="3">
+      <c r="A17" s="2">
         <v>2025</v>
       </c>
       <c r="B17">
@@ -7839,120 +7895,148 @@
       <c r="M17">
         <v>-0.0685</v>
       </c>
-      <c r="N17" s="10">
-        <f>(1+B17)*(1+C17)*(1+D17)*(1+E17)*(1+F17)*(1+G17)*(1+H17)*(1+I17)*(1+J17)*(1+K17)*(1+L17)*(1+M17)-1</f>
+      <c r="N17" s="9">
+        <f t="shared" si="1"/>
         <v>0.721324876500654</v>
       </c>
-      <c r="O17" s="9">
-        <f>N17</f>
+      <c r="O17" s="8">
+        <f t="shared" si="0"/>
         <v>0.721324876500654</v>
       </c>
-      <c r="P17" s="3">
+      <c r="P17" s="2">
         <v>2025</v>
       </c>
     </row>
     <row r="18" ht="14.75" spans="1:16">
-      <c r="A18" s="3"/>
-      <c r="N18" s="10"/>
-      <c r="O18" s="9"/>
-      <c r="P18" s="3"/>
+      <c r="A18" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B18">
+        <v>-0.0075</v>
+      </c>
+      <c r="C18">
+        <v>0.0046</v>
+      </c>
+      <c r="D18">
+        <v>-0.1137</v>
+      </c>
+      <c r="E18">
+        <v>0.042</v>
+      </c>
+      <c r="F18">
+        <v>-0.1464</v>
+      </c>
+      <c r="G18">
+        <v>-0.0434</v>
+      </c>
+      <c r="N18" s="9">
+        <f>(1+B18)*(1+C18)*(1+D18)*(1+E18)*(1+F18)*(1+G18)*(1+H18)*(1+I18)*(1+J18)*(1+K18)*(1+L18)*(1+M18)-1</f>
+        <v>-0.248105443831011</v>
+      </c>
+      <c r="O18" s="8">
+        <f>N18</f>
+        <v>-0.248105443831011</v>
+      </c>
+      <c r="P18" s="2">
+        <v>2026</v>
+      </c>
     </row>
     <row r="19" ht="24" customHeight="1" spans="1:15">
       <c r="A19" t="s">
         <v>14</v>
       </c>
-      <c r="B19" s="4" cm="1">
+      <c r="B19" s="3" cm="1">
         <f t="array" ref="B19">PRODUCT(B2:B17+1)-1</f>
         <v>0.194840242744342</v>
       </c>
-      <c r="C19" s="5" cm="1">
+      <c r="C19" s="4" cm="1">
         <f t="array" ref="C19">PRODUCT(C2:C17+1)-1</f>
         <v>2.74859148623959</v>
       </c>
-      <c r="D19" s="5" cm="1">
+      <c r="D19" s="4" cm="1">
         <f t="array" ref="D19">PRODUCT(D2:D17+1)-1</f>
         <v>2.22374556844742</v>
       </c>
-      <c r="E19" s="6" cm="1">
+      <c r="E19" s="5" cm="1">
         <f t="array" ref="E19">PRODUCT(E2:E17+1)-1</f>
         <v>0.323510793037694</v>
       </c>
-      <c r="F19" s="6" cm="1">
+      <c r="F19" s="5" cm="1">
         <f t="array" ref="F19">PRODUCT(F2:F17+1)-1</f>
         <v>1.28723547337183</v>
       </c>
-      <c r="G19" s="6" cm="1">
+      <c r="G19" s="5" cm="1">
         <f t="array" ref="G19">PRODUCT(G2:G17+1)-1</f>
         <v>0.595591661283158</v>
       </c>
-      <c r="H19" s="5" cm="1">
+      <c r="H19" s="4" cm="1">
         <f t="array" ref="H19">PRODUCT(H2:H17+1)-1</f>
         <v>2.77618998463726</v>
       </c>
-      <c r="I19" s="5" cm="1">
+      <c r="I19" s="4" cm="1">
         <f t="array" ref="I19">PRODUCT(I2:I17+1)-1</f>
         <v>2.44214606607075</v>
       </c>
-      <c r="J19" s="5" cm="1">
+      <c r="J19" s="4" cm="1">
         <f t="array" ref="J19">PRODUCT(J2:J17+1)-1</f>
         <v>1.20998365758364</v>
       </c>
-      <c r="K19" s="5" cm="1">
+      <c r="K19" s="4" cm="1">
         <f t="array" ref="K19">PRODUCT(K2:K17+1)-1</f>
         <v>1.1322825420196</v>
       </c>
-      <c r="L19" s="5" cm="1">
+      <c r="L19" s="4" cm="1">
         <f t="array" ref="L19">PRODUCT(L2:L17+1)-1</f>
         <v>1.69541069581852</v>
       </c>
-      <c r="M19" s="5" cm="1">
+      <c r="M19" s="4" cm="1">
         <f t="array" ref="M19">PRODUCT(M2:M17+1)-1</f>
         <v>0.299575907581825</v>
       </c>
-      <c r="N19" s="11" cm="1">
+      <c r="N19" s="10" cm="1">
         <f t="array" ref="N19">PRODUCT(N2:N17+1)-1</f>
         <v>14962.816747419</v>
       </c>
-      <c r="O19" s="12">
+      <c r="O19" s="11">
         <f>N19</f>
         <v>14962.816747419</v>
       </c>
     </row>
     <row r="20" ht="14.75" spans="2:13">
-      <c r="B20" s="7" t="s">
+      <c r="B20" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="C20" s="7" t="s">
+      <c r="C20" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="D20" s="7" t="s">
+      <c r="D20" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="E20" s="7" t="s">
+      <c r="E20" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="F20" s="7" t="s">
+      <c r="F20" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="G20" s="7" t="s">
+      <c r="G20" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="H20" s="7" t="s">
+      <c r="H20" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="I20" s="7" t="s">
+      <c r="I20" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="J20" s="7" t="s">
+      <c r="J20" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="K20" s="7" t="s">
+      <c r="K20" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="L20" s="7" t="s">
+      <c r="L20" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="M20" s="7" t="s">
+      <c r="M20" s="6" t="s">
         <v>11</v>
       </c>
     </row>
@@ -8034,7 +8118,7 @@
         <v>3</v>
       </c>
       <c r="G22">
-        <f>COUNTIF(G2:G17,"&gt;0.1")</f>
+        <f t="shared" si="3"/>
         <v>4</v>
       </c>
       <c r="H22">
@@ -8062,226 +8146,236 @@
         <v>5</v>
       </c>
     </row>
-    <row r="24" s="1" customFormat="1" spans="1:15">
-      <c r="A24" s="1">
-        <v>2026</v>
-      </c>
-      <c r="B24" s="1">
-        <v>-0.0075</v>
-      </c>
-      <c r="C24" s="1">
-        <v>0.0046</v>
-      </c>
-      <c r="D24" s="1">
-        <v>-0.1137</v>
-      </c>
-      <c r="E24" s="1">
-        <v>0.042</v>
-      </c>
-      <c r="F24" s="1">
-        <v>-0.1464</v>
-      </c>
-      <c r="G24" s="1">
-        <v>-0.0434</v>
-      </c>
-      <c r="N24" s="10">
-        <f>(1+B24)*(1+C24)*(1+D24)*(1+E24)*(1+F24)*(1+G24)*(1+H24)*(1+I24)*(1+J24)*(1+K24)*(1+L24)*(1+M24)-1</f>
+    <row r="28" spans="1:3">
+      <c r="A28" t="s">
+        <v>17</v>
+      </c>
+      <c r="B28" t="s">
+        <v>18</v>
+      </c>
+      <c r="C28" s="7" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3">
+      <c r="A29">
+        <v>1</v>
+      </c>
+      <c r="B29" cm="1">
+        <f ca="1" t="array" ref="B29">PRODUCT(INDEX($N:$N,ROW($N$19)-A29):$N$18+1)-1</f>
         <v>-0.248105443831011</v>
       </c>
-      <c r="O24" s="9">
-        <f>N24</f>
+      <c r="C29" s="8">
+        <f ca="1">POWER(B29+1,1/A29)-1</f>
         <v>-0.248105443831011</v>
       </c>
     </row>
-    <row r="27" spans="1:17">
-      <c r="A27" t="s">
+    <row r="30" spans="1:3">
+      <c r="A30">
+        <v>2</v>
+      </c>
+      <c r="B30" cm="1">
+        <f ca="1" t="array" ref="B30">PRODUCT(INDEX($N:$N,ROW($N$19)-A30):$N$18+1)-1</f>
+        <v>0.294254804039099</v>
+      </c>
+      <c r="C30" s="8">
+        <f ca="1" t="shared" ref="C30:C45" si="4">POWER(B30+1,1/A30)-1</f>
+        <v>0.137653200250014</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3">
+      <c r="A31">
+        <v>3</v>
+      </c>
+      <c r="B31" cm="1">
+        <f ca="1" t="array" ref="B31">PRODUCT(INDEX($N:$N,ROW($N$19)-A31):$N$18+1)-1</f>
+        <v>3.06954019815721</v>
+      </c>
+      <c r="C31" s="8">
+        <f ca="1" t="shared" si="4"/>
+        <v>0.596547267811532</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3">
+      <c r="A32">
+        <v>4</v>
+      </c>
+      <c r="B32" cm="1">
+        <f ca="1" t="array" ref="B32">PRODUCT(INDEX($N:$N,ROW($N$19)-A32):$N$18+1)-1</f>
+        <v>5.08419694690979</v>
+      </c>
+      <c r="C32" s="8">
+        <f ca="1" t="shared" si="4"/>
+        <v>0.570546560194028</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3">
+      <c r="A33">
+        <v>5</v>
+      </c>
+      <c r="B33" cm="1">
+        <f ca="1" t="array" ref="B33">PRODUCT(INDEX($N:$N,ROW($N$19)-A33):$N$18+1)-1</f>
+        <v>17.2335149112427</v>
+      </c>
+      <c r="C33" s="8">
+        <f ca="1" t="shared" si="4"/>
+        <v>0.787203800526058</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3">
+      <c r="A34">
+        <v>6</v>
+      </c>
+      <c r="B34" cm="1">
+        <f ca="1" t="array" ref="B34">PRODUCT(INDEX($N:$N,ROW($N$19)-A34):$N$18+1)-1</f>
+        <v>29.285154570697</v>
+      </c>
+      <c r="C34" s="8">
+        <f ca="1" t="shared" si="4"/>
+        <v>0.765515897213793</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3">
+      <c r="A35">
+        <v>7</v>
+      </c>
+      <c r="B35" cm="1">
+        <f ca="1" t="array" ref="B35">PRODUCT(INDEX($N:$N,ROW($N$19)-A35):$N$18+1)-1</f>
+        <v>44.4846006535458</v>
+      </c>
+      <c r="C35" s="8">
+        <f ca="1" t="shared" si="4"/>
+        <v>0.725193326188861</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3">
+      <c r="A36">
+        <v>8</v>
+      </c>
+      <c r="B36" cm="1">
+        <f ca="1" t="array" ref="B36">PRODUCT(INDEX($N:$N,ROW($N$19)-A36):$N$18+1)-1</f>
+        <v>78.4092176396709</v>
+      </c>
+      <c r="C36" s="8">
+        <f ca="1" t="shared" si="4"/>
+        <v>0.727761787783006</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3">
+      <c r="A37">
+        <v>9</v>
+      </c>
+      <c r="B37" cm="1">
+        <f ca="1" t="array" ref="B37">PRODUCT(INDEX($N:$N,ROW($N$19)-A37):$N$18+1)-1</f>
+        <v>115.955898827163</v>
+      </c>
+      <c r="C37" s="8">
+        <f ca="1" t="shared" si="4"/>
+        <v>0.697384518586593</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3">
+      <c r="A38">
+        <v>10</v>
+      </c>
+      <c r="B38" cm="1">
+        <f ca="1" t="array" ref="B38">PRODUCT(INDEX($N:$N,ROW($N$19)-A38):$N$18+1)-1</f>
+        <v>125.028113265473</v>
+      </c>
+      <c r="C38" s="8">
+        <f ca="1" t="shared" si="4"/>
+        <v>0.621984663460095</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3">
+      <c r="A39">
+        <v>11</v>
+      </c>
+      <c r="B39" cm="1">
+        <f ca="1" t="array" ref="B39">PRODUCT(INDEX($N:$N,ROW($N$19)-A39):$N$18+1)-1</f>
+        <v>263.273629877198</v>
+      </c>
+      <c r="C39" s="8">
+        <f ca="1" t="shared" si="4"/>
+        <v>0.66030055015333</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3">
+      <c r="A40">
+        <v>12</v>
+      </c>
+      <c r="B40" cm="1">
+        <f ca="1" t="array" ref="B40">PRODUCT(INDEX($N:$N,ROW($N$19)-A40):$N$18+1)-1</f>
+        <v>1844.37300211616</v>
+      </c>
+      <c r="C40" s="8">
+        <f ca="1" t="shared" si="4"/>
+        <v>0.871430400967408</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3">
+      <c r="A41">
+        <v>13</v>
+      </c>
+      <c r="B41" cm="1">
+        <f ca="1" t="array" ref="B41">PRODUCT(INDEX($N:$N,ROW($N$19)-A41):$N$18+1)-1</f>
+        <v>4057.63440794515</v>
+      </c>
+      <c r="C41" s="8">
+        <f ca="1" t="shared" si="4"/>
+        <v>0.894818809104917</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3">
+      <c r="A42">
+        <v>14</v>
+      </c>
+      <c r="B42" cm="1">
+        <f ca="1" t="array" ref="B42">PRODUCT(INDEX($N:$N,ROW($N$19)-A42):$N$18+1)-1</f>
+        <v>7164.13348720359</v>
+      </c>
+      <c r="C42" s="8">
+        <f ca="1" t="shared" si="4"/>
+        <v>0.885268292014252</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3">
+      <c r="A43">
+        <v>15</v>
+      </c>
+      <c r="B43" cm="1">
+        <f ca="1" t="array" ref="B43">PRODUCT(INDEX($N:$N,ROW($N$19)-A43):$N$18+1)-1</f>
+        <v>7439.68586202511</v>
+      </c>
+      <c r="C43" s="8">
+        <f ca="1" t="shared" si="4"/>
+        <v>0.811788635887162</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3">
+      <c r="A44">
+        <v>16</v>
+      </c>
+      <c r="B44" cm="1">
+        <f ca="1" t="array" ref="B44">PRODUCT(INDEX($N:$N,ROW($N$19)-A44):$N$18+1)-1</f>
+        <v>6803.013007753</v>
+      </c>
+      <c r="C44" s="8">
+        <f ca="1" t="shared" si="4"/>
+        <v>0.735992405611589</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3">
+      <c r="A45">
         <v>17</v>
       </c>
-      <c r="B27">
-        <v>1</v>
-      </c>
-      <c r="C27">
-        <v>2</v>
-      </c>
-      <c r="D27">
-        <v>3</v>
-      </c>
-      <c r="E27">
-        <v>4</v>
-      </c>
-      <c r="F27">
-        <v>5</v>
-      </c>
-      <c r="G27">
-        <v>6</v>
-      </c>
-      <c r="H27">
-        <v>7</v>
-      </c>
-      <c r="I27">
-        <v>8</v>
-      </c>
-      <c r="J27">
-        <v>9</v>
-      </c>
-      <c r="K27">
-        <v>10</v>
-      </c>
-      <c r="L27">
-        <v>11</v>
-      </c>
-      <c r="M27">
-        <v>12</v>
-      </c>
-      <c r="N27">
-        <v>13</v>
-      </c>
-      <c r="O27">
-        <v>14</v>
-      </c>
-      <c r="P27">
-        <v>15</v>
-      </c>
-      <c r="Q27">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="28" spans="1:17">
-      <c r="A28" t="s">
-        <v>18</v>
-      </c>
-      <c r="B28" s="8" cm="1">
-        <f ca="1" t="array" ref="B28">PRODUCT(INDEX($N:$N,ROW($N$19)-B27):$N$17+1)-1</f>
-        <v>0.721324876500654</v>
-      </c>
-      <c r="C28" s="8" cm="1">
-        <f ca="1" t="array" ref="C28">PRODUCT(INDEX($N:$N,ROW($N$19)-C27):$N$17+1)-1</f>
-        <v>0.721324876500654</v>
-      </c>
-      <c r="D28" s="8" cm="1">
-        <f ca="1" t="array" ref="D28">PRODUCT(INDEX($N:$N,ROW($N$19)-D27):$N$17+1)-1</f>
-        <v>4.41238151648831</v>
-      </c>
-      <c r="E28" s="8" cm="1">
-        <f ca="1" t="array" ref="E28">PRODUCT(INDEX($N:$N,ROW($N$19)-E27):$N$17+1)-1</f>
-        <v>7.09182204737544</v>
-      </c>
-      <c r="F28" s="8" cm="1">
-        <f ca="1" t="array" ref="F28">PRODUCT(INDEX($N:$N,ROW($N$19)-F27):$N$17+1)-1</f>
-        <v>23.2500956572223</v>
-      </c>
-      <c r="G28" s="8" cm="1">
-        <f ca="1" t="array" ref="G28">PRODUCT(INDEX($N:$N,ROW($N$19)-G27):$N$17+1)-1</f>
-        <v>39.2784596885556</v>
-      </c>
-      <c r="H28" s="8" cm="1">
-        <f ca="1" t="array" ref="H28">PRODUCT(INDEX($N:$N,ROW($N$19)-H27):$N$17+1)-1</f>
-        <v>59.4933235390031</v>
-      </c>
-      <c r="I28" s="8" cm="1">
-        <f ca="1" t="array" ref="I28">PRODUCT(INDEX($N:$N,ROW($N$19)-I27):$N$17+1)-1</f>
-        <v>104.612172595413</v>
-      </c>
-      <c r="J28" s="8" cm="1">
-        <f ca="1" t="array" ref="J28">PRODUCT(INDEX($N:$N,ROW($N$19)-J27):$N$17+1)-1</f>
-        <v>154.5482718522</v>
-      </c>
-      <c r="K28" s="8" cm="1">
-        <f ca="1" t="array" ref="K28">PRODUCT(INDEX($N:$N,ROW($N$19)-K27):$N$17+1)-1</f>
-        <v>166.614078638373</v>
-      </c>
-      <c r="L28" s="8" cm="1">
-        <f ca="1" t="array" ref="L28">PRODUCT(INDEX($N:$N,ROW($N$19)-L27):$N$17+1)-1</f>
-        <v>350.476982655268</v>
-      </c>
-      <c r="M28" s="8" cm="1">
-        <f ca="1" t="array" ref="M28">PRODUCT(INDEX($N:$N,ROW($N$19)-M27):$N$17+1)-1</f>
-        <v>2453.2975966186</v>
-      </c>
-      <c r="N28" s="8" cm="1">
-        <f ca="1" t="array" ref="N28">PRODUCT(INDEX($N:$N,ROW($N$19)-N27):$N$17+1)-1</f>
-        <v>5396.87710210921</v>
-      </c>
-      <c r="O28" s="8" cm="1">
-        <f ca="1" t="array" ref="O28">PRODUCT(INDEX($N:$N,ROW($N$19)-O27):$N$17+1)-1</f>
-        <v>9528.43923907493</v>
-      </c>
-      <c r="P28" s="8" cm="1">
-        <f ca="1" t="array" ref="P28">PRODUCT(INDEX($N:$N,ROW($N$19)-P27):$N$17+1)-1</f>
-        <v>9894.91665610199</v>
-      </c>
-      <c r="Q28" s="8" cm="1">
-        <f ca="1" t="array" ref="Q28">PRODUCT(INDEX($N:$N,ROW($N$19)-Q27):$N$17+1)-1</f>
-        <v>9048.15849161141</v>
-      </c>
-    </row>
-    <row r="29" spans="1:17">
-      <c r="A29" t="s">
-        <v>19</v>
-      </c>
-      <c r="B29" s="9">
-        <f ca="1">POWER(B28+1,1/B27)-1</f>
-        <v>0.721324876500654</v>
-      </c>
-      <c r="C29" s="9">
-        <f ca="1">POWER(C28+1,1/C27)-1</f>
-        <v>0.3119927120608</v>
-      </c>
-      <c r="D29" s="9">
-        <f ca="1" t="shared" ref="D29:Q29" si="4">POWER(D28+1,1/D27)-1</f>
-        <v>0.75575049992058</v>
-      </c>
-      <c r="E29" s="9">
+      <c r="B45" cm="1">
+        <f ca="1" t="array" ref="B45">PRODUCT(INDEX($N:$N,ROW($N$19)-A45):$N$18+1)-1</f>
+        <v>11250.2123518947</v>
+      </c>
+      <c r="C45" s="8">
         <f ca="1" t="shared" si="4"/>
-        <v>0.686597999377588</v>
-      </c>
-      <c r="F29" s="9">
-        <f ca="1" t="shared" si="4"/>
-        <v>0.892093924562005</v>
-      </c>
-      <c r="G29" s="9">
-        <f ca="1" t="shared" si="4"/>
-        <v>0.851450657807452</v>
-      </c>
-      <c r="H29" s="9">
-        <f ca="1" t="shared" si="4"/>
-        <v>0.796923693198646</v>
-      </c>
-      <c r="I29" s="9">
-        <f ca="1" t="shared" si="4"/>
-        <v>0.790458450087202</v>
-      </c>
-      <c r="J29" s="9">
-        <f ca="1" t="shared" si="4"/>
-        <v>0.752026120711281</v>
-      </c>
-      <c r="K29" s="9">
-        <f ca="1" t="shared" si="4"/>
-        <v>0.668902823492491</v>
-      </c>
-      <c r="L29" s="9">
-        <f ca="1" t="shared" si="4"/>
-        <v>0.703904193500895</v>
-      </c>
-      <c r="M29" s="9">
-        <f ca="1" t="shared" si="4"/>
-        <v>0.916434299972187</v>
-      </c>
-      <c r="N29" s="9">
-        <f ca="1" t="shared" si="4"/>
-        <v>0.936841474732953</v>
-      </c>
-      <c r="O29" s="9">
-        <f ca="1" t="shared" si="4"/>
-        <v>0.924062149207631</v>
-      </c>
-      <c r="P29" s="9">
-        <f ca="1" t="shared" si="4"/>
-        <v>0.846561324809914</v>
-      </c>
-      <c r="Q29" s="9">
-        <f ca="1" t="shared" si="4"/>
-        <v>0.767209396894281</v>
+        <v>0.731034973797034</v>
       </c>
     </row>
   </sheetData>
@@ -8291,16 +8385,6 @@
     </cfRule>
     <cfRule type="expression" dxfId="0" priority="5">
       <formula>B19&gt;2</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N24">
-    <cfRule type="expression" dxfId="4" priority="2">
-      <formula>N24&gt;1.5</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="O24">
-    <cfRule type="expression" dxfId="4" priority="1">
-      <formula>O24&gt;1.5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:M18 B19:N19">
